--- a/Excel Files/Dataset.xlsx
+++ b/Excel Files/Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\Code\Code\Python\Data_Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\Code\Code\Python\Data_Project\Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{312E4475-A9C3-42A6-BAA7-1EC7E3B6F540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA625E34-3705-4A43-88AA-95F467CDEBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{369E4836-92E2-44AD-8257-2B7A8DF32B0E}"/>
   </bookViews>
@@ -413,16 +413,16 @@
     <t>Support</t>
   </si>
   <si>
+    <t>Legal / Compliance</t>
+  </si>
+  <si>
+    <t>R/D</t>
+  </si>
+  <si>
     <t>Maintanience</t>
   </si>
   <si>
     <t>Customer Service</t>
-  </si>
-  <si>
-    <t>Research</t>
-  </si>
-  <si>
-    <t>Compliance</t>
   </si>
 </sst>
 </file>
@@ -468,8 +468,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -810,23 +810,22 @@
   <cols>
     <col min="2" max="2" width="19.609375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.94140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.94140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="23.1640625" customWidth="1"/>
-    <col min="6" max="6" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.94140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.27734375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.94140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.0546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.609375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.609375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.0546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.27734375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="8.0546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.1640625" customWidth="1"/>
-    <col min="16" max="16" width="15.0546875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="25" width="20.0546875" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.0546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.1640625" customWidth="1"/>
+    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="27" width="18.5" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="19.21875" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="15.38671875" bestFit="1" customWidth="1"/>
   </cols>
@@ -870,10 +869,10 @@
         <v>51</v>
       </c>
       <c r="O1" t="s">
+        <v>114</v>
+      </c>
+      <c r="P1" t="s">
         <v>117</v>
-      </c>
-      <c r="P1" t="s">
-        <v>114</v>
       </c>
       <c r="Q1" t="s">
         <v>118</v>
@@ -885,7 +884,7 @@
         <v>120</v>
       </c>
       <c r="T1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U1" t="s">
         <v>121</v>
@@ -894,13 +893,13 @@
         <v>122</v>
       </c>
       <c r="W1" t="s">
+        <v>123</v>
+      </c>
+      <c r="X1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Y1" t="s">
         <v>126</v>
-      </c>
-      <c r="X1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>124</v>
       </c>
       <c r="AC1">
         <v>0.11501694819952127</v>
@@ -928,37 +927,37 @@
       <c r="A2" t="s">
         <v>29</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>422</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="3">
         <v>2626.72</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>267.34000000000003</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>-33.17</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>-7.1952277657266812</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>-0.84999999999999787</v>
       </c>
-      <c r="I2" s="2">
+      <c r="I2" s="3">
         <v>3414.3399999999997</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>-142.78</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>-47.75</v>
       </c>
-      <c r="L2">
+      <c r="L2" s="3">
         <v>164.7</v>
       </c>
       <c r="M2" s="3">
@@ -967,133 +966,133 @@
       <c r="N2" t="s">
         <v>115</v>
       </c>
-      <c r="O2" s="4">
-        <f t="shared" ref="O2:O33" si="0">F2/E2</f>
-        <v>-0.12407421261315178</v>
-      </c>
-      <c r="P2" s="2">
+      <c r="O2" s="3">
         <f>E2-F2</f>
         <v>300.51000000000005</v>
       </c>
-      <c r="Q2" s="2">
-        <f t="shared" ref="Q2:Q33" si="1">P2*10000000</f>
+      <c r="P2" s="4">
+        <f>F2/E2</f>
+        <v>-0.12407421261315178</v>
+      </c>
+      <c r="Q2" s="3">
+        <f>O2*10000000</f>
         <v>3005100000.0000005</v>
       </c>
-      <c r="R2" s="2">
+      <c r="R2" s="3">
         <f>Q2/B2</f>
         <v>7121090.0473933658</v>
       </c>
-      <c r="S2" s="2">
-        <f t="shared" ref="S2:S33" ca="1" si="2">Q2*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>324899185.17231846</v>
-      </c>
-      <c r="T2" s="2">
-        <f t="shared" ref="T2:T33" ca="1" si="3">Q2*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>329900678.03793305</v>
-      </c>
-      <c r="U2" s="2">
-        <f t="shared" ref="U2:U33" ca="1" si="4">Q2*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>345641374.89964306</v>
-      </c>
-      <c r="V2" s="2">
-        <f t="shared" ref="V2:V33" ca="1" si="5">Q2*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>338276438.2765696</v>
-      </c>
-      <c r="W2" s="2">
-        <f t="shared" ref="W2:W33" ca="1" si="6">Q2*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>301671687.64736223</v>
-      </c>
-      <c r="X2" s="2">
-        <f t="shared" ref="X2:X33" ca="1" si="7">Q2*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>333315251.92481554</v>
-      </c>
-      <c r="Y2" s="2">
-        <f t="shared" ref="Y2:Y33" ca="1" si="8">Q2*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>312225329.46285808</v>
+      <c r="S2" s="3">
+        <f ca="1">Q2*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>345637431.03438139</v>
+      </c>
+      <c r="T2" s="3">
+        <f ca="1">Q2*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>297557474.30872399</v>
+      </c>
+      <c r="U2" s="3">
+        <f ca="1">Q2*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
+        <v>312723148.71872467</v>
+      </c>
+      <c r="V2" s="3">
+        <f ca="1">Q2*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>315286777.42282212</v>
+      </c>
+      <c r="W2" s="3">
+        <f ca="1">Q2*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>350857288.89421475</v>
+      </c>
+      <c r="X2" s="3">
+        <f ca="1">Q2*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>297369489.46233547</v>
+      </c>
+      <c r="Y2" s="3">
+        <f ca="1">Q2*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>308794281.88634318</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>42</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3" s="3">
         <v>561</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="3">
         <v>494.26</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="3">
         <v>104.84</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>14.39</v>
       </c>
-      <c r="G3" s="2">
+      <c r="G3" s="3">
         <v>7.1950000000000003</v>
       </c>
-      <c r="H3" s="2">
+      <c r="H3" s="3">
         <v>23.81</v>
       </c>
-      <c r="I3" s="2">
+      <c r="I3" s="3">
         <v>234.58</v>
       </c>
-      <c r="J3" s="2">
+      <c r="J3" s="3">
         <v>23.67</v>
       </c>
-      <c r="K3" s="2">
+      <c r="K3" s="3">
         <v>-14.63</v>
       </c>
-      <c r="L3">
+      <c r="L3" s="3">
         <v>-2.78</v>
       </c>
       <c r="M3" s="3">
         <v>6.1343678062920966E-2</v>
       </c>
-      <c r="O3" s="4">
-        <f t="shared" si="0"/>
+      <c r="O3" s="3">
+        <f t="shared" ref="O3:O52" si="0">E3-F3</f>
+        <v>90.45</v>
+      </c>
+      <c r="P3" s="4">
+        <f t="shared" ref="P3:P51" si="1">F3/E3</f>
         <v>0.13725677222434185</v>
       </c>
-      <c r="P3" s="2">
-        <f>E3-F3</f>
-        <v>90.45</v>
-      </c>
-      <c r="Q3" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q3" s="3">
+        <f>O3*10000000</f>
         <v>904500000</v>
       </c>
-      <c r="R3" s="2">
+      <c r="R3" s="3">
         <f>Q3/B3</f>
         <v>1612299.4652406417</v>
       </c>
-      <c r="S3" s="2">
-        <f t="shared" ca="1" si="2"/>
-        <v>94669874.978284955</v>
-      </c>
-      <c r="T3" s="2">
-        <f t="shared" ca="1" si="3"/>
-        <v>97349265.492228702</v>
-      </c>
-      <c r="U3" s="2">
-        <f t="shared" ca="1" si="4"/>
-        <v>107006417.18109858</v>
-      </c>
-      <c r="V3" s="2">
-        <f t="shared" ca="1" si="5"/>
-        <v>102805773.86016698</v>
-      </c>
-      <c r="W3" s="2">
-        <f t="shared" ca="1" si="6"/>
-        <v>90799654.413177282</v>
-      </c>
-      <c r="X3" s="2">
-        <f t="shared" ca="1" si="7"/>
-        <v>94422586.032292739</v>
-      </c>
-      <c r="Y3" s="2">
-        <f t="shared" ca="1" si="8"/>
+      <c r="S3" s="3">
+        <f t="shared" ref="S3:S52" ca="1" si="2">Q3*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>106113486.23939633</v>
+      </c>
+      <c r="T3" s="3">
+        <f t="shared" ref="T3:T52" ca="1" si="3">Q3*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>104163714.07668471</v>
+      </c>
+      <c r="U3" s="3">
+        <f t="shared" ref="U3:U52" ca="1" si="4">Q3*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
+        <v>97098415.590256095</v>
+      </c>
+      <c r="V3" s="3">
+        <f t="shared" ref="V3:V52" ca="1" si="5">Q3*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>105771325.02921025</v>
+      </c>
+      <c r="W3" s="3">
+        <f t="shared" ref="W3:W52" ca="1" si="6">Q3*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>105603945.89358662</v>
+      </c>
+      <c r="X3" s="3">
+        <f t="shared" ref="X3:X52" ca="1" si="7">Q3*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>90488311.614280552</v>
+      </c>
+      <c r="Y3" s="3">
+        <f t="shared" ref="Y3:Y52" ca="1" si="8">Q3*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
         <v>97074293.067794189</v>
       </c>
     </row>
@@ -1101,338 +1100,338 @@
       <c r="A4" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>1285</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="3">
         <v>1693.75</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="3">
         <v>540.39</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>129.02000000000001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="G4" s="3">
         <v>86.590604026845639</v>
       </c>
-      <c r="H4" s="2">
+      <c r="H4" s="3">
         <v>215.92000000000002</v>
       </c>
-      <c r="I4" s="2">
+      <c r="I4" s="3">
         <v>277.68</v>
       </c>
-      <c r="J4" s="2">
+      <c r="J4" s="3">
         <v>144.56</v>
       </c>
-      <c r="K4" s="2">
+      <c r="K4" s="3">
         <v>-7.79</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="3">
         <v>-146.1</v>
       </c>
       <c r="M4" s="3">
         <v>0.4646355517142034</v>
       </c>
-      <c r="O4" s="4">
+      <c r="O4" s="3">
         <f t="shared" si="0"/>
+        <v>411.37</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="1"/>
         <v>0.23875349284775813</v>
       </c>
-      <c r="P4" s="2">
-        <f>E4-F4</f>
-        <v>411.37</v>
-      </c>
-      <c r="Q4" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q4" s="3">
+        <f>O4*10000000</f>
         <v>4113700000</v>
       </c>
-      <c r="R4" s="2">
+      <c r="R4" s="3">
         <f>Q4/B4</f>
         <v>3201322.9571984434</v>
       </c>
-      <c r="S4" s="2">
+      <c r="S4" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>449487958.8179521</v>
-      </c>
-      <c r="T4" s="2">
+        <v>477876672.00645435</v>
+      </c>
+      <c r="T4" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>460458043.55289823</v>
-      </c>
-      <c r="U4" s="2">
+        <v>425038194.04882914</v>
+      </c>
+      <c r="U4" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>455125833.11985749</v>
-      </c>
-      <c r="V4" s="2">
+        <v>428088654.91471744</v>
+      </c>
+      <c r="V4" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>436093834.85426688</v>
-      </c>
-      <c r="W4" s="2">
+        <v>409118958.47152877</v>
+      </c>
+      <c r="W4" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>493756810.38699752</v>
-      </c>
-      <c r="X4" s="2">
+        <v>462335922.4532795</v>
+      </c>
+      <c r="X4" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>447330698.54551625</v>
-      </c>
-      <c r="Y4" s="2">
+        <v>469697233.47279209</v>
+      </c>
+      <c r="Y4" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>450891098.4289729</v>
+        <v>432103969.3277657</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>55</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="3">
         <v>618</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="3">
         <v>19929.830000000002</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="3">
         <v>2360.08</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>381.87</v>
       </c>
-      <c r="G5" s="2">
+      <c r="G5" s="3">
         <v>27.179359430604983</v>
       </c>
-      <c r="H5" s="2">
+      <c r="H5" s="3">
         <v>597.76</v>
       </c>
-      <c r="I5" s="2">
+      <c r="I5" s="3">
         <v>2946.46</v>
       </c>
-      <c r="J5" s="2">
+      <c r="J5" s="3">
         <v>425.99</v>
       </c>
-      <c r="K5" s="2">
+      <c r="K5" s="3">
         <v>-91.8</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="3">
         <v>-91.81</v>
       </c>
       <c r="M5" s="3">
         <v>0.12960298120456412</v>
       </c>
-      <c r="O5" s="4">
+      <c r="O5" s="3">
         <f t="shared" si="0"/>
+        <v>1978.21</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="1"/>
         <v>0.16180383715806246</v>
       </c>
-      <c r="P5" s="2">
-        <f>E5-F5</f>
-        <v>1978.21</v>
-      </c>
-      <c r="Q5" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q5" s="3">
+        <f>O5*10000000</f>
         <v>19782100000</v>
       </c>
-      <c r="R5" s="2">
+      <c r="R5" s="3">
         <f>Q5/B5</f>
         <v>32009870.550161812</v>
       </c>
-      <c r="S5" s="2">
+      <c r="S5" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2161512932.4288621</v>
-      </c>
-      <c r="T5" s="2">
+        <v>2047749093.8799748</v>
+      </c>
+      <c r="T5" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>2086520118.0717978</v>
-      </c>
-      <c r="U5" s="2">
+        <v>2192975226.1366854</v>
+      </c>
+      <c r="U5" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>2383650482.0035939</v>
-      </c>
-      <c r="V5" s="2">
+        <v>1971929035.1120641</v>
+      </c>
+      <c r="V5" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2118722431.7489741</v>
-      </c>
-      <c r="W5" s="2">
+        <v>2075483198.4479744</v>
+      </c>
+      <c r="W5" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2352809081.9909348</v>
-      </c>
-      <c r="X5" s="2">
+        <v>2180125846.6154532</v>
+      </c>
+      <c r="X5" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>2108116245.585072</v>
-      </c>
-      <c r="Y5" s="2">
+        <v>2258695977.4125772</v>
+      </c>
+      <c r="Y5" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>2190846443.5617647</v>
+        <v>2484465039.090661</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>1834</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="3">
         <v>4123.6400000000003</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="3">
         <v>297.23</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>26.23</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6" s="3">
         <v>22.042016806722689</v>
       </c>
-      <c r="H6" s="2">
+      <c r="H6" s="3">
         <v>59.760000000000005</v>
       </c>
-      <c r="I6" s="2">
+      <c r="I6" s="3">
         <v>165.13</v>
       </c>
-      <c r="J6" s="2">
+      <c r="J6" s="3">
         <v>-23.48</v>
       </c>
-      <c r="K6" s="2">
+      <c r="K6" s="3">
         <v>32.700000000000003</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="3">
         <v>-9.14</v>
       </c>
       <c r="M6" s="3">
         <v>0.15884454672076548</v>
       </c>
-      <c r="O6" s="4">
+      <c r="O6" s="3">
         <f t="shared" si="0"/>
+        <v>271</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="1"/>
         <v>8.8248157992127305E-2</v>
       </c>
-      <c r="P6" s="2">
-        <f>E6-F6</f>
-        <v>271</v>
-      </c>
-      <c r="Q6" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q6" s="3">
+        <f>O6*10000000</f>
         <v>2710000000</v>
       </c>
-      <c r="R6" s="2">
+      <c r="R6" s="3">
         <f>Q6/B6</f>
         <v>1477644.4929116685</v>
       </c>
-      <c r="S6" s="2">
+      <c r="S6" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>280526336.6586324</v>
-      </c>
-      <c r="T6" s="2">
+        <v>324163766.80553073</v>
+      </c>
+      <c r="T6" s="3">
         <f t="shared" ca="1" si="3"/>
         <v>282920966.50018972</v>
       </c>
-      <c r="U6" s="2">
+      <c r="U6" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>290919520.45284027</v>
-      </c>
-      <c r="V6" s="2">
+        <v>296856653.52330643</v>
+      </c>
+      <c r="V6" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>266555345.54253012</v>
-      </c>
-      <c r="W6" s="2">
+        <v>308019510.40470147</v>
+      </c>
+      <c r="W6" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>310489120.37961882</v>
-      </c>
-      <c r="X6" s="2">
+        <v>272047610.23738027</v>
+      </c>
+      <c r="X6" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>277008586.3030479</v>
-      </c>
-      <c r="Y6" s="2">
+        <v>271114786.59447241</v>
+      </c>
+      <c r="Y6" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>309411964.07292414</v>
+        <v>318694322.99511188</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2">
+      <c r="B7" s="3">
         <v>3000</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="3">
         <v>4853.87</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="3">
         <v>1193.1400000000001</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>186.17</v>
       </c>
-      <c r="G7" s="2">
+      <c r="G7" s="3">
         <v>33.72644927536232</v>
       </c>
-      <c r="H7" s="2">
+      <c r="H7" s="3">
         <v>270.89</v>
       </c>
-      <c r="I7" s="2">
+      <c r="I7" s="3">
         <v>1503.26</v>
       </c>
-      <c r="J7" s="2">
+      <c r="J7" s="3">
         <v>157.1</v>
       </c>
-      <c r="K7" s="2">
+      <c r="K7" s="3">
         <v>-421.23</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="3">
         <v>283.11</v>
       </c>
       <c r="M7" s="3">
         <v>0.12384417865173024</v>
       </c>
-      <c r="O7" s="4">
+      <c r="O7" s="3">
         <f t="shared" si="0"/>
+        <v>1006.9700000000001</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="1"/>
         <v>0.15603365908443265</v>
       </c>
-      <c r="P7" s="2">
-        <f>E7-F7</f>
-        <v>1006.9700000000001</v>
-      </c>
-      <c r="Q7" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q7" s="3">
+        <f>O7*10000000</f>
         <v>10069700000.000002</v>
       </c>
-      <c r="R7" s="2">
+      <c r="R7" s="3">
         <f>Q7/B7</f>
         <v>3356566.6666666674</v>
       </c>
-      <c r="S7" s="2">
+      <c r="S7" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>1053949408.5890948</v>
-      </c>
-      <c r="T7" s="2">
+        <v>1146604301.6518722</v>
+      </c>
+      <c r="T7" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>975400894.25581646</v>
-      </c>
-      <c r="U7" s="2">
+        <v>1127129922.2511659</v>
+      </c>
+      <c r="U7" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>1114077497.5732381</v>
-      </c>
-      <c r="V7" s="2">
+        <v>1213351730.0302596</v>
+      </c>
+      <c r="V7" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>1144525484.8421488</v>
-      </c>
-      <c r="W7" s="2">
+        <v>1210555801.2753499</v>
+      </c>
+      <c r="W7" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1142714316.3964553</v>
-      </c>
-      <c r="X7" s="2">
+        <v>1098763765.7658224</v>
+      </c>
+      <c r="X7" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>1084046254.1732132</v>
-      </c>
-      <c r="Y7" s="2">
+        <v>1105946178.4999449</v>
+      </c>
+      <c r="Y7" s="3">
         <f t="shared" ca="1" si="8"/>
         <v>1264669453.9068773</v>
       </c>
@@ -1441,2587 +1440,2587 @@
       <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8" s="3">
         <v>12000</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="3">
         <v>10183.86</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="3">
         <v>5483.7199999999993</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>516.76</v>
       </c>
-      <c r="G8" s="2">
+      <c r="G8" s="3">
         <v>18.595178121626486</v>
       </c>
-      <c r="H8" s="2">
+      <c r="H8" s="3">
         <v>802.94</v>
       </c>
-      <c r="I8" s="2">
+      <c r="I8" s="3">
         <v>3478.23</v>
       </c>
-      <c r="J8" s="2">
+      <c r="J8" s="3">
         <v>587.52</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8" s="3">
         <v>-437.54</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="3">
         <v>-215.47</v>
       </c>
       <c r="M8" s="3">
         <v>0.14856981855713969</v>
       </c>
-      <c r="O8" s="4">
+      <c r="O8" s="3">
         <f t="shared" si="0"/>
+        <v>4966.9599999999991</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="1"/>
         <v>9.4235300124732857E-2</v>
       </c>
-      <c r="P8" s="2">
-        <f>E8-F8</f>
-        <v>4966.9599999999991</v>
-      </c>
-      <c r="Q8" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q8" s="3">
+        <f>O8*10000000</f>
         <v>49669599999.999992</v>
       </c>
-      <c r="R8" s="2">
+      <c r="R8" s="3">
         <f>Q8/B8</f>
         <v>4139133.3333333326</v>
       </c>
-      <c r="S8" s="2">
+      <c r="S8" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>5998488100.8054876</v>
-      </c>
-      <c r="T8" s="2">
+        <v>6055616558.9083967</v>
+      </c>
+      <c r="T8" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>5345825403.3087921</v>
-      </c>
-      <c r="U8" s="2">
+        <v>5880407943.6396713</v>
+      </c>
+      <c r="U8" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>5930545700.8291245</v>
-      </c>
-      <c r="V8" s="2">
+        <v>5876137024.6747293</v>
+      </c>
+      <c r="V8" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>5591180120.0032921</v>
-      </c>
-      <c r="W8" s="2">
+        <v>5102630400.7797031</v>
+      </c>
+      <c r="W8" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>5148753081.3309202</v>
-      </c>
-      <c r="X8" s="2">
+        <v>4986160878.7625761</v>
+      </c>
+      <c r="X8" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>5455167910.4264126</v>
-      </c>
-      <c r="Y8" s="2">
+        <v>5941271981.6525297</v>
+      </c>
+      <c r="Y8" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>5387435448.7751608</v>
+        <v>5274015755.1167355</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="3">
         <v>3436</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="3">
         <v>9142.02</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="3">
         <v>5898.7</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>204.78</v>
       </c>
-      <c r="G9" s="2">
+      <c r="G9" s="3">
         <v>12.09568812758417</v>
       </c>
-      <c r="H9" s="2">
+      <c r="H9" s="3">
         <v>469.53999999999996</v>
       </c>
-      <c r="I9" s="2">
+      <c r="I9" s="3">
         <v>758.74</v>
       </c>
-      <c r="J9" s="2">
+      <c r="J9" s="3">
         <v>-87.61</v>
       </c>
-      <c r="K9" s="2">
+      <c r="K9" s="3">
         <v>-104.85</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="3">
         <v>192.15</v>
       </c>
       <c r="M9" s="3">
         <v>0.26989482563196882</v>
       </c>
-      <c r="O9" s="4">
+      <c r="O9" s="3">
         <f t="shared" si="0"/>
+        <v>5693.92</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="1"/>
         <v>3.4716123891704954E-2</v>
       </c>
-      <c r="P9" s="2">
-        <f>E9-F9</f>
-        <v>5693.92</v>
-      </c>
-      <c r="Q9" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q9" s="3">
+        <f>O9*10000000</f>
         <v>56939200000</v>
       </c>
-      <c r="R9" s="2">
+      <c r="R9" s="3">
         <f>Q9/B9</f>
         <v>16571362.048894063</v>
       </c>
-      <c r="S9" s="2">
+      <c r="S9" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>7007401128.1067343</v>
-      </c>
-      <c r="T9" s="2">
+        <v>6221524366.0760717</v>
+      </c>
+      <c r="T9" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>6741059400.2063236</v>
-      </c>
-      <c r="U9" s="2">
+        <v>6373365251.1041603</v>
+      </c>
+      <c r="U9" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>5613469494.3412638</v>
-      </c>
-      <c r="V9" s="2">
+        <v>6112444560.5049314</v>
+      </c>
+      <c r="V9" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>6098359642.5981665</v>
-      </c>
-      <c r="W9" s="2">
+        <v>6658413079.1633043</v>
+      </c>
+      <c r="W9" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>6461487333.7002125</v>
-      </c>
-      <c r="X9" s="2">
+        <v>6772135763.2050314</v>
+      </c>
+      <c r="X9" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>6501248198.9824247</v>
-      </c>
-      <c r="Y9" s="2">
+        <v>6067831652.3835964</v>
+      </c>
+      <c r="Y9" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>6956054090.0638065</v>
+        <v>5915896469.1196852</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10" s="3">
         <v>935</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="3">
         <v>5079.7700000000004</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="3">
         <v>515.69000000000005</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>147.19</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G10" s="3">
         <v>27.056985294117645</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H10" s="3">
         <v>235.01</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I10" s="3">
         <v>790.74</v>
       </c>
-      <c r="J10" s="2">
+      <c r="J10" s="3">
         <v>113.15</v>
       </c>
-      <c r="K10" s="2">
+      <c r="K10" s="3">
         <v>-102.02</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="3">
         <v>-17.23</v>
       </c>
       <c r="M10" s="3">
         <v>0.18614209474669297</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="3">
         <f t="shared" si="0"/>
+        <v>368.50000000000006</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="1"/>
         <v>0.28542341329093057</v>
       </c>
-      <c r="P10" s="2">
-        <f>E10-F10</f>
-        <v>368.50000000000006</v>
-      </c>
-      <c r="Q10" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q10" s="3">
+        <f>O10*10000000</f>
         <v>3685000000.0000005</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R10" s="3">
         <f>Q10/B10</f>
         <v>3941176.4705882357</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S10" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>423837454.11523592</v>
-      </c>
-      <c r="T10" s="2">
+        <v>466221199.52675956</v>
+      </c>
+      <c r="T10" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>424370686.97908592</v>
-      </c>
-      <c r="U10" s="2">
+        <v>380743793.92516118</v>
+      </c>
+      <c r="U10" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>367329984.90493715</v>
       </c>
-      <c r="V10" s="2">
+      <c r="V10" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>438974796.50406063</v>
-      </c>
-      <c r="W10" s="2">
+        <v>382592712.54941058</v>
+      </c>
+      <c r="W10" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>442301054.10605687</v>
-      </c>
-      <c r="X10" s="2">
+        <v>394050030.02175975</v>
+      </c>
+      <c r="X10" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>416741660.57462549</v>
-      </c>
-      <c r="Y10" s="2">
+        <v>384684609.76119268</v>
+      </c>
+      <c r="Y10" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>462804943.30981487</v>
+        <v>445975672.64400339</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11" s="3">
         <v>2500</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="3">
         <v>2322.0300000000002</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="3">
         <v>440.35</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>63.24</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="3">
         <v>36.344827586206897</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H11" s="3">
         <v>105.63000000000001</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I11" s="3">
         <v>411.88</v>
       </c>
-      <c r="J11" s="2">
+      <c r="J11" s="3">
         <v>5.68</v>
       </c>
-      <c r="K11" s="2">
+      <c r="K11" s="3">
         <v>-52.84</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="3">
         <v>48.53</v>
       </c>
       <c r="M11" s="3">
         <v>0.15353986598038263</v>
       </c>
-      <c r="O11" s="4">
+      <c r="O11" s="3">
         <f t="shared" si="0"/>
+        <v>377.11</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="1"/>
         <v>0.14361303508572726</v>
       </c>
-      <c r="P11" s="2">
-        <f>E11-F11</f>
-        <v>377.11</v>
-      </c>
-      <c r="Q11" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q11" s="3">
+        <f>O11*10000000</f>
         <v>3771100000</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R11" s="3">
         <f>Q11/B11</f>
         <v>1508440</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S11" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>399041180.28679752</v>
-      </c>
-      <c r="T11" s="2">
+        <v>464102242.29007971</v>
+      </c>
+      <c r="T11" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>418051110.61434603</v>
-      </c>
-      <c r="U11" s="2">
+        <v>389639870.08715743</v>
+      </c>
+      <c r="U11" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>437876270.72614217</v>
-      </c>
-      <c r="V11" s="2">
+        <v>392436280.36776894</v>
+      </c>
+      <c r="V11" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>453352829.0008114</v>
-      </c>
-      <c r="W11" s="2">
+        <v>391531988.6825189</v>
+      </c>
+      <c r="W11" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>411486741.12232661</v>
-      </c>
-      <c r="X11" s="2">
+        <v>395027271.47743356</v>
+      </c>
+      <c r="X11" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>430579584.59519321</v>
-      </c>
-      <c r="Y11" s="2">
+        <v>438781100.49224448</v>
+      </c>
+      <c r="Y11" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>452090269.59452933</v>
+        <v>396117188.5971114</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12" s="3">
         <v>350000</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="3">
         <v>41346.76</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="3">
         <v>12188</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>812.1</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="3">
         <v>24.285287081339714</v>
       </c>
-      <c r="H12" s="2">
+      <c r="H12" s="3">
         <v>1906.7</v>
       </c>
-      <c r="I12" s="2">
+      <c r="I12" s="3">
         <v>6379.2</v>
       </c>
-      <c r="J12" s="2">
+      <c r="J12" s="3">
         <v>1237.0999999999999</v>
       </c>
-      <c r="K12" s="2">
+      <c r="K12" s="3">
         <v>-2438.1</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <v>1675.3</v>
       </c>
       <c r="M12" s="3">
         <v>0.1273043641835967</v>
       </c>
-      <c r="O12" s="4">
+      <c r="O12" s="3">
         <f t="shared" si="0"/>
+        <v>11375.9</v>
+      </c>
+      <c r="P12" s="4">
+        <f t="shared" si="1"/>
         <v>6.6631112569740733E-2</v>
       </c>
-      <c r="P12" s="2">
-        <f>E12-F12</f>
-        <v>11375.9</v>
-      </c>
-      <c r="Q12" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q12" s="3">
+        <f>O12*10000000</f>
         <v>113759000000</v>
       </c>
-      <c r="R12" s="2">
+      <c r="R12" s="3">
         <f>Q12/B12</f>
         <v>325025.71428571426</v>
       </c>
-      <c r="S12" s="2">
+      <c r="S12" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>11775791709.206406</v>
-      </c>
-      <c r="T12" s="2">
+        <v>14130950051.047688</v>
+      </c>
+      <c r="T12" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>12488493305.686075</v>
-      </c>
-      <c r="U12" s="2">
+        <v>13223110558.961727</v>
+      </c>
+      <c r="U12" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>11589006614.31246</v>
-      </c>
-      <c r="V12" s="2">
+        <v>13582814203.871595</v>
+      </c>
+      <c r="V12" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>12308257014.365297</v>
-      </c>
-      <c r="W12" s="2">
+        <v>12556908671.221163</v>
+      </c>
+      <c r="W12" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>12537037836.484873</v>
-      </c>
-      <c r="X12" s="2">
+        <v>13405941448.914516</v>
+      </c>
+      <c r="X12" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>11751828837.554369</v>
-      </c>
-      <c r="Y12" s="2">
+        <v>11133311530.314667</v>
+      </c>
+      <c r="Y12" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>13507871382.217953</v>
+        <v>12079154216.791052</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="3">
         <v>12022</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="3">
         <v>9994.08</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="3">
         <v>7457</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>615.70000000000005</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="3">
         <v>55.468468468468473</v>
       </c>
-      <c r="H13" s="2">
+      <c r="H13" s="3">
         <v>1213.4000000000001</v>
       </c>
-      <c r="I13" s="2">
+      <c r="I13" s="3">
         <v>5309.5</v>
       </c>
-      <c r="J13" s="2">
+      <c r="J13" s="3">
         <v>789.9</v>
       </c>
-      <c r="K13" s="2">
+      <c r="K13" s="3">
         <v>-134.1</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <v>-58.2</v>
       </c>
       <c r="M13" s="3">
         <v>0.11596195498634523</v>
       </c>
-      <c r="O13" s="4">
+      <c r="O13" s="3">
         <f t="shared" si="0"/>
+        <v>6841.3</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="1"/>
         <v>8.2566715837468163E-2</v>
       </c>
-      <c r="P13" s="2">
-        <f>E13-F13</f>
-        <v>6841.3</v>
-      </c>
-      <c r="Q13" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q13" s="3">
+        <f>O13*10000000</f>
         <v>68413000000</v>
       </c>
-      <c r="R13" s="2">
+      <c r="R13" s="3">
         <f>Q13/B13</f>
         <v>5690650.4741307599</v>
       </c>
-      <c r="S13" s="2">
+      <c r="S13" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>7553908298.086894</v>
-      </c>
-      <c r="T13" s="2">
+        <v>8183400656.2608023</v>
+      </c>
+      <c r="T13" s="3">
         <f t="shared" ca="1" si="3"/>
         <v>7731291393.1739473</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>7344161310.9742298</v>
-      </c>
-      <c r="V13" s="2">
+        <v>6819578360.1903563</v>
+      </c>
+      <c r="V13" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>8074915507.5724497</v>
-      </c>
-      <c r="W13" s="2">
+        <v>7177702673.3977318</v>
+      </c>
+      <c r="W13" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>7539591324.7078438</v>
-      </c>
-      <c r="X13" s="2">
+        <v>7614240743.7643566</v>
+      </c>
+      <c r="X13" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>8108886461.5207481</v>
-      </c>
-      <c r="Y13" s="2">
+        <v>6695410839.7877731</v>
+      </c>
+      <c r="Y13" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>7342336773.5179701</v>
+        <v>7029896910.8150787</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="3">
         <v>5800</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="3">
         <v>14615.45</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="3">
         <v>2843.2000000000003</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>220.6</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G14" s="3">
         <v>65.850746268656707</v>
       </c>
-      <c r="H14" s="2">
+      <c r="H14" s="3">
         <v>389.1</v>
       </c>
-      <c r="I14" s="2">
+      <c r="I14" s="3">
         <v>1752.6999999999998</v>
       </c>
-      <c r="J14" s="2">
+      <c r="J14" s="3">
         <v>397</v>
       </c>
-      <c r="K14" s="2">
+      <c r="K14" s="3">
         <v>-190.9</v>
       </c>
-      <c r="L14">
+      <c r="L14" s="3">
         <v>-22.4</v>
       </c>
       <c r="M14" s="3">
         <v>0.12586295429908143</v>
       </c>
-      <c r="O14" s="4">
+      <c r="O14" s="3">
         <f t="shared" si="0"/>
+        <v>2622.6000000000004</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="1"/>
         <v>7.7588632526730442E-2</v>
       </c>
-      <c r="P14" s="2">
-        <f>E14-F14</f>
-        <v>2622.6000000000004</v>
-      </c>
-      <c r="Q14" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q14" s="3">
+        <f>O14*10000000</f>
         <v>26226000000.000004</v>
       </c>
-      <c r="R14" s="2">
+      <c r="R14" s="3">
         <f>Q14/B14</f>
         <v>4521724.1379310349</v>
       </c>
-      <c r="S14" s="2">
+      <c r="S14" s="3">
         <f t="shared" ca="1" si="2"/>
         <v>3137091862.8198709</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T14" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>3076682368.2820539</v>
-      </c>
-      <c r="U14" s="2">
+        <v>2709738599.5878639</v>
+      </c>
+      <c r="U14" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>2700457874.3852773</v>
-      </c>
-      <c r="V14" s="2">
+        <v>2872827525.9417844</v>
+      </c>
+      <c r="V14" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2722897280.684082</v>
-      </c>
-      <c r="W14" s="2">
+        <v>2980855970.4331007</v>
+      </c>
+      <c r="W14" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2861671998.2695074</v>
-      </c>
-      <c r="X14" s="2">
+        <v>2775821838.3214221</v>
+      </c>
+      <c r="X14" s="3">
         <f t="shared" ca="1" si="7"/>
         <v>3137045576.9891295</v>
       </c>
-      <c r="Y14" s="2">
+      <c r="Y14" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>2784728228.0044847</v>
+        <v>2964388113.6821933</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="3">
         <v>5098</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="3">
         <v>5686.81</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="3">
         <v>2150.06</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>184.66</v>
       </c>
-      <c r="G15" s="2">
+      <c r="G15" s="3">
         <v>12.124753775443203</v>
       </c>
-      <c r="H15" s="2">
+      <c r="H15" s="3">
         <v>444.11</v>
       </c>
-      <c r="I15" s="2">
+      <c r="I15" s="3">
         <v>1574.58</v>
       </c>
-      <c r="J15" s="2">
+      <c r="J15" s="3">
         <v>236.42</v>
       </c>
-      <c r="K15" s="2">
+      <c r="K15" s="3">
         <v>-731.46</v>
       </c>
-      <c r="L15">
+      <c r="L15" s="3">
         <v>499.46</v>
       </c>
       <c r="M15" s="3">
         <v>0.11727571796923625</v>
       </c>
-      <c r="O15" s="4">
+      <c r="O15" s="3">
         <f t="shared" si="0"/>
+        <v>1965.3999999999999</v>
+      </c>
+      <c r="P15" s="4">
+        <f t="shared" si="1"/>
         <v>8.5885975275108606E-2</v>
       </c>
-      <c r="P15" s="2">
-        <f>E15-F15</f>
-        <v>1965.3999999999999</v>
-      </c>
-      <c r="Q15" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q15" s="3">
+        <f>O15*10000000</f>
         <v>19654000000</v>
       </c>
-      <c r="R15" s="2">
+      <c r="R15" s="3">
         <f>Q15/B15</f>
         <v>3855237.3479796001</v>
       </c>
-      <c r="S15" s="2">
+      <c r="S15" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2350964823.9099269</v>
-      </c>
-      <c r="T15" s="2">
+        <v>2215332237.9151235</v>
+      </c>
+      <c r="T15" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1967242997.7947645</v>
-      </c>
-      <c r="U15" s="2">
+        <v>2009549298.8226089</v>
+      </c>
+      <c r="U15" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>2368215031.4323878</v>
-      </c>
-      <c r="V15" s="2">
+        <v>1980688935.3798151</v>
+      </c>
+      <c r="V15" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2105002536.3128452</v>
-      </c>
-      <c r="W15" s="2">
+        <v>2019084065.4429331</v>
+      </c>
+      <c r="W15" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2273236465.3865714</v>
-      </c>
-      <c r="X15" s="2">
+        <v>1951552059.9073396</v>
+      </c>
+      <c r="X15" s="3">
         <f t="shared" ca="1" si="7"/>
         <v>1944860385.974756</v>
       </c>
-      <c r="Y15" s="2">
+      <c r="Y15" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>2243978871.5458488</v>
+        <v>2086900350.5376394</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="3">
         <v>22640</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="3">
         <v>388107.2</v>
       </c>
-      <c r="E16" s="2">
+      <c r="E16" s="3">
         <v>119540</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>17390</v>
       </c>
-      <c r="G16" s="2">
+      <c r="G16" s="3">
         <v>64.082249327486451</v>
       </c>
-      <c r="H16" s="2">
+      <c r="H16" s="3">
         <v>28199</v>
       </c>
-      <c r="I16" s="2">
+      <c r="I16" s="3">
         <v>69655</v>
       </c>
-      <c r="J16" s="2">
+      <c r="J16" s="3">
         <v>22261</v>
       </c>
-      <c r="K16" s="2">
+      <c r="K16" s="3">
         <v>-4896</v>
       </c>
-      <c r="L16">
+      <c r="L16" s="3">
         <v>-18561</v>
       </c>
       <c r="M16" s="3">
         <v>0.24965903380948962</v>
       </c>
-      <c r="O16" s="4">
+      <c r="O16" s="3">
         <f t="shared" si="0"/>
+        <v>102150</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" si="1"/>
         <v>0.14547431821984272</v>
       </c>
-      <c r="P16" s="2">
-        <f>E16-F16</f>
-        <v>102150</v>
-      </c>
-      <c r="Q16" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q16" s="3">
+        <f>O16*10000000</f>
         <v>1021500000000</v>
       </c>
-      <c r="R16" s="2">
+      <c r="R16" s="3">
         <f>Q16/B16</f>
         <v>45119257.950530037</v>
       </c>
-      <c r="S16" s="2">
+      <c r="S16" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>119839608837.52719</v>
-      </c>
-      <c r="T16" s="2">
+        <v>112790220082.37852</v>
+      </c>
+      <c r="T16" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>115438793184.44136</v>
-      </c>
-      <c r="U16" s="2">
+        <v>104444622404.97075</v>
+      </c>
+      <c r="U16" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>111896336374.19096</v>
-      </c>
-      <c r="V16" s="2">
+        <v>118610116556.64241</v>
+      </c>
+      <c r="V16" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>116104033165.4622</v>
-      </c>
-      <c r="W16" s="2">
+        <v>101591029019.77943</v>
+      </c>
+      <c r="W16" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>111461829719.83151</v>
-      </c>
-      <c r="X16" s="2">
+        <v>100315646747.84836</v>
+      </c>
+      <c r="X16" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>118855213108.33118</v>
-      </c>
-      <c r="Y16" s="2">
+        <v>117744416724.14117</v>
+      </c>
+      <c r="Y16" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>117795189857.37894</v>
+        <v>118961478865.86783</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="3">
         <v>33800</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="3">
         <v>28946.75</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17" s="3">
         <v>13707.6</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>1369.2</v>
       </c>
-      <c r="G17" s="2">
+      <c r="G17" s="3">
         <v>22.409165302782323</v>
       </c>
-      <c r="H17" s="2">
+      <c r="H17" s="3">
         <v>2189.5</v>
       </c>
-      <c r="I17" s="2">
+      <c r="I17" s="3">
         <v>6315.7999999999993</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J17" s="3">
         <v>1739.1</v>
       </c>
-      <c r="K17" s="2">
+      <c r="K17" s="3">
         <v>-996.2</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="3">
         <v>-830.8</v>
       </c>
       <c r="M17" s="3">
         <v>0.21678963868393555</v>
       </c>
-      <c r="O17" s="4">
+      <c r="O17" s="3">
         <f t="shared" si="0"/>
+        <v>12338.4</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" si="1"/>
         <v>9.9886194519828414E-2</v>
       </c>
-      <c r="P17" s="2">
-        <f>E17-F17</f>
-        <v>12338.4</v>
-      </c>
-      <c r="Q17" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q17" s="3">
+        <f>O17*10000000</f>
         <v>123384000000</v>
       </c>
-      <c r="R17" s="2">
+      <c r="R17" s="3">
         <f>Q17/B17</f>
         <v>3650414.2011834318</v>
       </c>
-      <c r="S17" s="2">
+      <c r="S17" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>12914038534.351257</v>
-      </c>
-      <c r="T17" s="2">
+        <v>13765513602.55024</v>
+      </c>
+      <c r="T17" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>14474696001.224468</v>
-      </c>
-      <c r="U17" s="2">
+        <v>13279537615.802263</v>
+      </c>
+      <c r="U17" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>13245318860.351751</v>
-      </c>
-      <c r="V17" s="2">
+        <v>12975006230.548655</v>
+      </c>
+      <c r="V17" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>14158711763.895252</v>
-      </c>
-      <c r="W17" s="2">
+        <v>13079952772.360374</v>
+      </c>
+      <c r="W17" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>12116833830.970654</v>
-      </c>
-      <c r="X17" s="2">
+        <v>13193885727.056932</v>
+      </c>
+      <c r="X17" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>14758683423.748444</v>
-      </c>
-      <c r="Y17" s="2">
+        <v>13014475382.759991</v>
+      </c>
+      <c r="Y17" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>13382900917.496304</v>
+        <v>14087264123.680321</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>33</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="3">
         <v>1195</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="2">
+      <c r="D18" s="3">
         <v>1682.97</v>
       </c>
-      <c r="E18" s="2">
+      <c r="E18" s="3">
         <v>408.2</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>37.97</v>
       </c>
-      <c r="G18" s="2">
+      <c r="G18" s="3">
         <v>3.8943589743589744</v>
       </c>
-      <c r="H18" s="2">
+      <c r="H18" s="3">
         <v>80.290000000000006</v>
       </c>
-      <c r="I18" s="2">
+      <c r="I18" s="3">
         <v>332.23</v>
       </c>
-      <c r="J18" s="2">
+      <c r="J18" s="3">
         <v>50.03</v>
       </c>
-      <c r="K18" s="2">
+      <c r="K18" s="3">
         <v>-27.33</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="3">
         <v>-13</v>
       </c>
       <c r="M18" s="3">
         <v>0.11428829425398067</v>
       </c>
-      <c r="O18" s="4">
+      <c r="O18" s="3">
         <f t="shared" si="0"/>
+        <v>370.23</v>
+      </c>
+      <c r="P18" s="4">
+        <f t="shared" si="1"/>
         <v>9.3018128368446834E-2</v>
       </c>
-      <c r="P18" s="2">
-        <f>E18-F18</f>
-        <v>370.23</v>
-      </c>
-      <c r="Q18" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q18" s="3">
+        <f>O18*10000000</f>
         <v>3702300000</v>
       </c>
-      <c r="R18" s="2">
+      <c r="R18" s="3">
         <f>Q18/B18</f>
         <v>3098158.9958158997</v>
       </c>
-      <c r="S18" s="2">
+      <c r="S18" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>404535884.95313317</v>
-      </c>
-      <c r="T18" s="2">
+        <v>442860337.21185106</v>
+      </c>
+      <c r="T18" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>394485377.3085236</v>
-      </c>
-      <c r="U18" s="2">
+        <v>426362983.555677</v>
+      </c>
+      <c r="U18" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>397443299.10426223</v>
-      </c>
-      <c r="V18" s="2">
+        <v>401498842.97267306</v>
+      </c>
+      <c r="V18" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>392481271.06520951</v>
-      </c>
-      <c r="W18" s="2">
+        <v>396527469.73598486</v>
+      </c>
+      <c r="W18" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>432258141.3839975</v>
       </c>
-      <c r="X18" s="2">
+      <c r="X18" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>386490591.78259522</v>
-      </c>
-      <c r="Y18" s="2">
+        <v>378438704.45379114</v>
+      </c>
+      <c r="Y18" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>452296468.1211403</v>
+        <v>418479909.75694287</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="3">
         <v>337000</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="2">
+      <c r="D19" s="3">
         <v>518105.18</v>
       </c>
-      <c r="E19" s="2">
+      <c r="E19" s="3">
         <v>166590</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>26713</v>
       </c>
-      <c r="G19" s="2">
+      <c r="G19" s="3">
         <v>64.317530638287636</v>
       </c>
-      <c r="H19" s="2">
+      <c r="H19" s="3">
         <v>42763</v>
       </c>
-      <c r="I19" s="2">
+      <c r="I19" s="3">
         <v>95818</v>
       </c>
-      <c r="J19" s="2">
+      <c r="J19" s="3">
         <v>35694</v>
       </c>
-      <c r="K19" s="2">
+      <c r="K19" s="3">
         <v>-1864</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="3">
         <v>-24161</v>
       </c>
       <c r="M19" s="3">
         <v>0.27878895405873633</v>
       </c>
-      <c r="O19" s="4">
+      <c r="O19" s="3">
         <f t="shared" si="0"/>
+        <v>139877</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="1"/>
         <v>0.16035176181043279</v>
       </c>
-      <c r="P19" s="2">
-        <f>E19-F19</f>
-        <v>139877</v>
-      </c>
-      <c r="Q19" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q19" s="3">
+        <f>O19*10000000</f>
         <v>1398770000000</v>
       </c>
-      <c r="R19" s="2">
+      <c r="R19" s="3">
         <f>Q19/B19</f>
         <v>4150652.8189910981</v>
       </c>
-      <c r="S19" s="2">
+      <c r="S19" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>164099901765.70526</v>
-      </c>
-      <c r="T19" s="2">
+        <v>167317546898.36615</v>
+      </c>
+      <c r="T19" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>165601056165.63983</v>
-      </c>
-      <c r="U19" s="2">
+        <v>158073735430.83801</v>
+      </c>
+      <c r="U19" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>137900650599.23093</v>
-      </c>
-      <c r="V19" s="2">
+        <v>159351862914.66684</v>
+      </c>
+      <c r="V19" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>139111584593.24216</v>
-      </c>
-      <c r="W19" s="2">
+        <v>165099463033.73798</v>
+      </c>
+      <c r="W19" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>160259360484.64923</v>
-      </c>
-      <c r="X19" s="2">
+        <v>143470284624.35263</v>
+      </c>
+      <c r="X19" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>152104616574.98401</v>
-      </c>
-      <c r="Y19" s="2">
+        <v>162751939735.23291</v>
+      </c>
+      <c r="Y19" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>151718215622.49811</v>
+        <v>167688554109.07684</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="3">
         <v>5900</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="2">
+      <c r="D20" s="3">
         <v>9137.58</v>
       </c>
-      <c r="E20" s="2">
+      <c r="E20" s="3">
         <v>2577.0300000000002</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>332.77</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G20" s="3">
         <v>23.957523398128146</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H20" s="3">
         <v>641.39</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I20" s="3">
         <v>2785.8399999999997</v>
       </c>
-      <c r="J20" s="2">
+      <c r="J20" s="3">
         <v>431.36</v>
       </c>
-      <c r="K20" s="2">
+      <c r="K20" s="3">
         <v>-243.96</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="3">
         <v>-63.31</v>
       </c>
       <c r="M20" s="3">
         <v>0.11945050684892169</v>
       </c>
-      <c r="O20" s="4">
+      <c r="O20" s="3">
         <f t="shared" si="0"/>
+        <v>2244.2600000000002</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="1"/>
         <v>0.12912926896466084</v>
       </c>
-      <c r="P20" s="2">
-        <f>E20-F20</f>
-        <v>2244.2600000000002</v>
-      </c>
-      <c r="Q20" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q20" s="3">
+        <f>O20*10000000</f>
         <v>22442600000.000004</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R20" s="3">
         <f>Q20/B20</f>
         <v>3803830.5084745768</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S20" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2581279361.6625767</v>
-      </c>
-      <c r="T20" s="2">
+        <v>2400589806.3461962</v>
+      </c>
+      <c r="T20" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>2439600145.9295206</v>
-      </c>
-      <c r="U20" s="2">
+        <v>2294673404.5871725</v>
+      </c>
+      <c r="U20" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>2261718199.9163046</v>
-      </c>
-      <c r="V20" s="2">
+        <v>2286302093.3936558</v>
+      </c>
+      <c r="V20" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2550833455.4275112</v>
-      </c>
-      <c r="W20" s="2">
+        <v>2624415189.7186894</v>
+      </c>
+      <c r="W20" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2546796857.6183095</v>
-      </c>
-      <c r="X20" s="2">
+        <v>2693727445.5578275</v>
+      </c>
+      <c r="X20" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>2489255223.7356048</v>
-      </c>
-      <c r="Y20" s="2">
+        <v>2294019519.9132042</v>
+      </c>
+      <c r="Y20" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>2459870327.345715</v>
+        <v>2818601416.750299</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="3">
         <v>7530</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="2">
+      <c r="D21" s="3">
         <v>25972.09</v>
       </c>
-      <c r="E21" s="2">
+      <c r="E21" s="3">
         <v>2702.99</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>486.06</v>
       </c>
-      <c r="G21" s="2">
+      <c r="G21" s="3">
         <v>28.325174825174827</v>
       </c>
-      <c r="H21" s="2">
+      <c r="H21" s="3">
         <v>816.14</v>
       </c>
-      <c r="I21" s="2">
+      <c r="I21" s="3">
         <v>1789.69</v>
       </c>
-      <c r="J21" s="2">
+      <c r="J21" s="3">
         <v>317.89</v>
       </c>
-      <c r="K21" s="2">
+      <c r="K21" s="3">
         <v>241.24</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="3">
         <v>-389.49</v>
       </c>
       <c r="M21" s="3">
         <v>0.2715889343964597</v>
       </c>
-      <c r="O21" s="4">
+      <c r="O21" s="3">
         <f t="shared" si="0"/>
+        <v>2216.9299999999998</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="1"/>
         <v>0.17982308480608514</v>
       </c>
-      <c r="P21" s="2">
-        <f>E21-F21</f>
-        <v>2216.9299999999998</v>
-      </c>
-      <c r="Q21" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q21" s="3">
+        <f>O21*10000000</f>
         <v>22169300000</v>
       </c>
-      <c r="R21" s="2">
+      <c r="R21" s="3">
         <f>Q21/B21</f>
         <v>2944130.1460823375</v>
       </c>
-      <c r="S21" s="2">
+      <c r="S21" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>2779331300.3944154</v>
-      </c>
-      <c r="T21" s="2">
+        <v>2422352968.2336645</v>
+      </c>
+      <c r="T21" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>2147427931.8177769</v>
-      </c>
-      <c r="U21" s="2">
+        <v>2386031035.3530855</v>
+      </c>
+      <c r="U21" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>2647012394.0074239</v>
-      </c>
-      <c r="V21" s="2">
+        <v>2598443359.2549939</v>
+      </c>
+      <c r="V21" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>2325941617.4901896</v>
-      </c>
-      <c r="W21" s="2">
+        <v>2253255941.9436212</v>
+      </c>
+      <c r="W21" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>2612543515.356329</v>
-      </c>
-      <c r="X21" s="2">
+        <v>2394831555.7433014</v>
+      </c>
+      <c r="X21" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>2290190833.6781626</v>
-      </c>
-      <c r="Y21" s="2">
+        <v>2314298105.6116166</v>
+      </c>
+      <c r="Y21" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>2303356625.8896337</v>
+        <v>2455226293.5307083</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="3">
         <v>503</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D22" s="2">
+      <c r="D22" s="3">
         <v>478.52</v>
       </c>
-      <c r="E22" s="2">
+      <c r="E22" s="3">
         <v>128.51</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>13.03</v>
       </c>
-      <c r="G22" s="2">
+      <c r="G22" s="3">
         <v>6.3560975609756101</v>
       </c>
-      <c r="H22" s="2">
+      <c r="H22" s="3">
         <v>21.35</v>
       </c>
-      <c r="I22" s="2">
+      <c r="I22" s="3">
         <v>75.69</v>
       </c>
-      <c r="J22" s="2">
+      <c r="J22" s="3">
         <v>27.78</v>
       </c>
-      <c r="K22" s="2">
+      <c r="K22" s="3">
         <v>-26.85</v>
       </c>
-      <c r="L22">
+      <c r="L22" s="3">
         <v>17.47</v>
       </c>
       <c r="M22" s="3">
         <v>0.17214955740520543</v>
       </c>
-      <c r="O22" s="4">
+      <c r="O22" s="3">
         <f t="shared" si="0"/>
+        <v>115.47999999999999</v>
+      </c>
+      <c r="P22" s="4">
+        <f t="shared" si="1"/>
         <v>0.10139288771301845</v>
       </c>
-      <c r="P22" s="2">
-        <f>E22-F22</f>
-        <v>115.47999999999999</v>
-      </c>
-      <c r="Q22" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q22" s="3">
+        <f>O22*10000000</f>
         <v>1154800000</v>
       </c>
-      <c r="R22" s="2">
+      <c r="R22" s="3">
         <f>Q22/B22</f>
         <v>2295825.0497017894</v>
       </c>
-      <c r="S22" s="2">
+      <c r="S22" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>119539414.60272646</v>
-      </c>
-      <c r="T22" s="2">
+        <v>120867630.32053453</v>
+      </c>
+      <c r="T22" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>134231560.34677696</v>
-      </c>
-      <c r="U22" s="2">
+        <v>131745790.71072555</v>
+      </c>
+      <c r="U22" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>127763160.19321084</v>
-      </c>
-      <c r="V22" s="2">
+        <v>134088069.11366683</v>
+      </c>
+      <c r="V22" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>113586019.56919329</v>
-      </c>
-      <c r="W22" s="2">
+        <v>138827357.25123626</v>
+      </c>
+      <c r="W22" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>129787180.21466008</v>
-      </c>
-      <c r="X22" s="2">
+        <v>138607668.19041368</v>
+      </c>
+      <c r="X22" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>125574905.96795151</v>
-      </c>
-      <c r="Y22" s="2">
+        <v>114273164.43083587</v>
+      </c>
+      <c r="Y22" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>127892866.43102229</v>
+        <v>145033147.49909747</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="3">
         <v>14000</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D23" s="2">
+      <c r="D23" s="3">
         <v>19454.650000000001</v>
       </c>
-      <c r="E23" s="2">
+      <c r="E23" s="3">
         <v>6012.47</v>
       </c>
-      <c r="F23" s="2">
+      <c r="F23" s="3">
         <v>839.6</v>
       </c>
-      <c r="G23" s="2">
+      <c r="G23" s="3">
         <v>30.631156512221818</v>
       </c>
-      <c r="H23" s="2">
+      <c r="H23" s="3">
         <v>1451.45</v>
       </c>
-      <c r="I23" s="2">
+      <c r="I23" s="3">
         <v>2912.16</v>
       </c>
-      <c r="J23" s="2">
+      <c r="J23" s="3">
         <v>1389.53</v>
       </c>
-      <c r="K23" s="2">
+      <c r="K23" s="3">
         <v>-627.79999999999995</v>
       </c>
-      <c r="L23">
+      <c r="L23" s="3">
         <v>-342.44</v>
       </c>
       <c r="M23" s="3">
         <v>0.28830833470688427</v>
       </c>
-      <c r="O23" s="4">
+      <c r="O23" s="3">
         <f t="shared" si="0"/>
+        <v>5172.87</v>
+      </c>
+      <c r="P23" s="4">
+        <f t="shared" si="1"/>
         <v>0.1396431084063621</v>
       </c>
-      <c r="P23" s="2">
-        <f>E23-F23</f>
-        <v>5172.87</v>
-      </c>
-      <c r="Q23" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q23" s="3">
+        <f>O23*10000000</f>
         <v>51728700000</v>
       </c>
-      <c r="R23" s="2">
+      <c r="R23" s="3">
         <f>Q23/B23</f>
         <v>3694907.1428571427</v>
       </c>
-      <c r="S23" s="2">
+      <c r="S23" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>5949677208.3285761</v>
-      </c>
-      <c r="T23" s="2">
+        <v>5652193347.9121466</v>
+      </c>
+      <c r="T23" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>5734464873.8130312</v>
-      </c>
-      <c r="U23" s="2">
+        <v>5289069543.808135</v>
+      </c>
+      <c r="U23" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>5156445750.3804665</v>
-      </c>
-      <c r="V23" s="2">
+        <v>5609759662.5018263</v>
+      </c>
+      <c r="V23" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>5709900417.3823442</v>
-      </c>
-      <c r="W23" s="2">
+        <v>5483765747.3870029</v>
+      </c>
+      <c r="W23" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>6095974150.8668709</v>
-      </c>
-      <c r="X23" s="2">
+        <v>5983085740.6656322</v>
+      </c>
+      <c r="X23" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>6187573001.5403633</v>
-      </c>
-      <c r="Y23" s="2">
+        <v>5175061055.8337584</v>
+      </c>
+      <c r="Y23" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>6260445529.8507071</v>
+        <v>6142323916.0799389</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="3">
         <v>646</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D24" s="2">
+      <c r="D24" s="3">
         <v>726.55</v>
       </c>
-      <c r="E24" s="2">
+      <c r="E24" s="3">
         <v>137.88</v>
       </c>
-      <c r="F24" s="2">
+      <c r="F24" s="3">
         <v>34.32</v>
       </c>
-      <c r="G24" s="2">
+      <c r="G24" s="3">
         <v>14.481012658227847</v>
       </c>
-      <c r="H24" s="2">
+      <c r="H24" s="3">
         <v>49.360000000000007</v>
       </c>
-      <c r="I24" s="2">
+      <c r="I24" s="3">
         <v>20.759999999999998</v>
       </c>
-      <c r="J24" s="2">
+      <c r="J24" s="3">
         <v>34.11</v>
       </c>
-      <c r="K24" s="2">
+      <c r="K24" s="3">
         <v>-7.59</v>
       </c>
-      <c r="L24">
+      <c r="L24" s="3">
         <v>-23.41</v>
       </c>
       <c r="M24" s="3">
         <v>1.6531791907514453</v>
       </c>
-      <c r="O24" s="4">
+      <c r="O24" s="3">
         <f t="shared" si="0"/>
+        <v>103.56</v>
+      </c>
+      <c r="P24" s="4">
+        <f t="shared" si="1"/>
         <v>0.24891209747606616</v>
       </c>
-      <c r="P24" s="2">
-        <f>E24-F24</f>
-        <v>103.56</v>
-      </c>
-      <c r="Q24" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q24" s="3">
+        <f>O24*10000000</f>
         <v>1035600000</v>
       </c>
-      <c r="R24" s="2">
+      <c r="R24" s="3">
         <f>Q24/B24</f>
         <v>1603095.9752321981</v>
       </c>
-      <c r="S24" s="2">
+      <c r="S24" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>119111551.55542423</v>
-      </c>
-      <c r="T24" s="2">
+        <v>109582627.43099029</v>
+      </c>
+      <c r="T24" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>101427925.26568753</v>
-      </c>
-      <c r="U24" s="2">
+        <v>110344665.94838533</v>
+      </c>
+      <c r="U24" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>121381728.01326482</v>
-      </c>
-      <c r="V24" s="2">
+        <v>114575275.97513781</v>
+      </c>
+      <c r="V24" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>114311259.94353533</v>
-      </c>
-      <c r="W24" s="2">
+        <v>117706643.90225419</v>
+      </c>
+      <c r="W24" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>117520377.57432385</v>
-      </c>
-      <c r="X24" s="2">
+        <v>105090337.63857806</v>
+      </c>
+      <c r="X24" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>115991283.16507006</v>
-      </c>
-      <c r="Y24" s="2">
+        <v>105856122.50016102</v>
+      </c>
+      <c r="Y24" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>126515469.4071936</v>
+        <v>128880244.53630003</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="3">
         <v>18491</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="2">
+      <c r="D25" s="3">
         <v>35652.870000000003</v>
       </c>
-      <c r="E25" s="2">
+      <c r="E25" s="3">
         <v>10880.1</v>
       </c>
-      <c r="F25" s="2">
+      <c r="F25" s="3">
         <v>1266.7</v>
       </c>
-      <c r="G25" s="2">
+      <c r="G25" s="3">
         <v>119.61284230406044</v>
       </c>
-      <c r="H25" s="2">
+      <c r="H25" s="3">
         <v>2142.4</v>
       </c>
-      <c r="I25" s="2">
+      <c r="I25" s="3">
         <v>6080</v>
       </c>
-      <c r="J25" s="2">
+      <c r="J25" s="3">
         <v>1481.1</v>
       </c>
-      <c r="K25" s="2">
+      <c r="K25" s="3">
         <v>-509.4</v>
       </c>
-      <c r="L25">
+      <c r="L25" s="3">
         <v>-718.2</v>
       </c>
       <c r="M25" s="3">
         <v>0.20833881578947369</v>
       </c>
-      <c r="O25" s="4">
+      <c r="O25" s="3">
         <f t="shared" si="0"/>
+        <v>9613.4</v>
+      </c>
+      <c r="P25" s="4">
+        <f t="shared" si="1"/>
         <v>0.11642356228343489</v>
       </c>
-      <c r="P25" s="2">
-        <f>E25-F25</f>
-        <v>9613.4</v>
-      </c>
-      <c r="Q25" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q25" s="3">
+        <f>O25*10000000</f>
         <v>96134000000</v>
       </c>
-      <c r="R25" s="2">
+      <c r="R25" s="3">
         <f>Q25/B25</f>
         <v>5198961.6570223356</v>
       </c>
-      <c r="S25" s="2">
+      <c r="S25" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>10283046547.337883</v>
-      </c>
-      <c r="T25" s="2">
+        <v>10061905761.373629</v>
+      </c>
+      <c r="T25" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>9518947867.0243473</v>
-      </c>
-      <c r="U25" s="2">
+        <v>10864016587.364744</v>
+      </c>
+      <c r="U25" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>10635940112.585842</v>
-      </c>
-      <c r="V25" s="2">
+        <v>11583697152.321217</v>
+      </c>
+      <c r="V25" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>10296240654.619877</v>
-      </c>
-      <c r="W25" s="2">
+        <v>11031686415.664154</v>
+      </c>
+      <c r="W25" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>10909331766.83087</v>
-      </c>
-      <c r="X25" s="2">
+        <v>10175049820.986485</v>
+      </c>
+      <c r="X25" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>10871924775.490105</v>
-      </c>
-      <c r="Y25" s="2">
+        <v>10767387037.264238</v>
+      </c>
+      <c r="Y25" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>11634579461.047113</v>
+        <v>9988176707.1253529</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="3">
         <v>1172</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="2">
+      <c r="D26" s="3">
         <v>5995.71</v>
       </c>
-      <c r="E26" s="2">
+      <c r="E26" s="3">
         <v>916.78</v>
       </c>
-      <c r="F26" s="2">
+      <c r="F26" s="3">
         <v>174.18</v>
       </c>
-      <c r="G26" s="2">
+      <c r="G26" s="3">
         <v>8.4348668280871681</v>
       </c>
-      <c r="H26" s="2">
+      <c r="H26" s="3">
         <v>276.08000000000004</v>
       </c>
-      <c r="I26" s="2">
+      <c r="I26" s="3">
         <v>1500.02</v>
       </c>
-      <c r="J26" s="2">
+      <c r="J26" s="3">
         <v>130.47</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26" s="3">
         <v>-221.32</v>
       </c>
-      <c r="L26">
+      <c r="L26" s="3">
         <v>-4.58</v>
       </c>
       <c r="M26" s="3">
         <v>0.11611845175397661</v>
       </c>
-      <c r="O26" s="4">
+      <c r="O26" s="3">
         <f t="shared" si="0"/>
+        <v>742.59999999999991</v>
+      </c>
+      <c r="P26" s="4">
+        <f t="shared" si="1"/>
         <v>0.18999105565130131</v>
       </c>
-      <c r="P26" s="2">
-        <f>E26-F26</f>
-        <v>742.59999999999991</v>
-      </c>
-      <c r="Q26" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q26" s="3">
+        <f>O26*10000000</f>
         <v>7425999999.999999</v>
       </c>
-      <c r="R26" s="2">
+      <c r="R26" s="3">
         <f>Q26/B26</f>
         <v>6336177.4744027294</v>
       </c>
-      <c r="S26" s="2">
+      <c r="S26" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>879739333.0495342</v>
-      </c>
-      <c r="T26" s="2">
+        <v>777245430.16997683</v>
+      </c>
+      <c r="T26" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>743296351.97028184</v>
-      </c>
-      <c r="U26" s="2">
+        <v>823220690.89181757</v>
+      </c>
+      <c r="U26" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>894798250.91161656</v>
-      </c>
-      <c r="V26" s="2">
+        <v>821587484.9279387</v>
+      </c>
+      <c r="V26" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>844041654.71044767</v>
-      </c>
-      <c r="W26" s="2">
+        <v>884620580.41768074</v>
+      </c>
+      <c r="W26" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>891323643.90544856</v>
-      </c>
-      <c r="X26" s="2">
+        <v>834603048.38419271</v>
+      </c>
+      <c r="X26" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>726764224.5810591</v>
-      </c>
-      <c r="Y26" s="2">
+        <v>750989698.73376095</v>
+      </c>
+      <c r="Y26" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>788507276.02994347</v>
+        <v>763071557.44833243</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="3">
         <v>90000</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D27" s="2">
+      <c r="D27" s="3">
         <v>132726.75</v>
       </c>
-      <c r="E27" s="2">
+      <c r="E27" s="3">
         <v>38997.799999999996</v>
       </c>
-      <c r="F27" s="2">
+      <c r="F27" s="3">
         <v>4598.7</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G27" s="3">
         <v>155.20418494768816</v>
       </c>
-      <c r="H27" s="2">
+      <c r="H27" s="3">
         <v>7531.0999999999995</v>
       </c>
-      <c r="I27" s="2">
+      <c r="I27" s="3">
         <v>22698.3</v>
       </c>
-      <c r="J27" s="2">
+      <c r="J27" s="3">
         <v>4545.8</v>
       </c>
-      <c r="K27" s="2">
+      <c r="K27" s="3">
         <v>-1729.1</v>
       </c>
-      <c r="L27">
+      <c r="L27" s="3">
         <v>-2574.4</v>
       </c>
       <c r="M27" s="3">
         <v>0.20260107585149548</v>
       </c>
-      <c r="O27" s="4">
+      <c r="O27" s="3">
         <f t="shared" si="0"/>
+        <v>34399.1</v>
+      </c>
+      <c r="P27" s="4">
+        <f t="shared" si="1"/>
         <v>0.11792203662770721</v>
       </c>
-      <c r="P27" s="2">
-        <f>E27-F27</f>
-        <v>34399.1</v>
-      </c>
-      <c r="Q27" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q27" s="3">
+        <f>O27*10000000</f>
         <v>343991000000</v>
       </c>
-      <c r="R27" s="2">
+      <c r="R27" s="3">
         <f>Q27/B27</f>
         <v>3822122.222222222</v>
       </c>
-      <c r="S27" s="2">
+      <c r="S27" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>43125626580.630661</v>
-      </c>
-      <c r="T27" s="2">
+        <v>42729978630.349648</v>
+      </c>
+      <c r="T27" s="3">
         <f t="shared" ca="1" si="3"/>
         <v>39244342130.562164</v>
       </c>
-      <c r="U27" s="2">
+      <c r="U27" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>35797127766.431335</v>
-      </c>
-      <c r="V27" s="2">
+        <v>38057998993.784889</v>
+      </c>
+      <c r="V27" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>36090583958.089241</v>
-      </c>
-      <c r="W27" s="2">
+        <v>34962753209.398949</v>
+      </c>
+      <c r="W27" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>34907425970.096664</v>
-      </c>
-      <c r="X27" s="2">
+        <v>34156728637.406414</v>
+      </c>
+      <c r="X27" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>39276471555.908112</v>
-      </c>
-      <c r="Y27" s="2">
+        <v>36283978484.981781</v>
+      </c>
+      <c r="Y27" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>38882133440.618134</v>
+        <v>43202370489.575706</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="3">
         <v>314</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="2">
+      <c r="D28" s="3">
         <v>1539.23</v>
       </c>
-      <c r="E28" s="2">
+      <c r="E28" s="3">
         <v>604.16000000000008</v>
       </c>
-      <c r="F28" s="2">
+      <c r="F28" s="3">
         <v>102.69</v>
       </c>
-      <c r="G28" s="2">
+      <c r="G28" s="3">
         <v>1.7571868583162218</v>
       </c>
-      <c r="H28" s="2">
+      <c r="H28" s="3">
         <v>212.98</v>
       </c>
-      <c r="I28" s="2">
+      <c r="I28" s="3">
         <v>517.47</v>
       </c>
-      <c r="J28" s="2">
+      <c r="J28" s="3">
         <v>143.04</v>
       </c>
-      <c r="K28" s="2">
+      <c r="K28" s="3">
         <v>-63.89</v>
       </c>
-      <c r="L28">
+      <c r="L28" s="3">
         <v>-48.34</v>
       </c>
       <c r="M28" s="3">
         <v>0.19844628674126036</v>
       </c>
-      <c r="O28" s="4">
+      <c r="O28" s="3">
         <f t="shared" si="0"/>
+        <v>501.47000000000008</v>
+      </c>
+      <c r="P28" s="4">
+        <f t="shared" si="1"/>
         <v>0.16997153072033896</v>
       </c>
-      <c r="P28" s="2">
-        <f>E28-F28</f>
-        <v>501.47000000000008</v>
-      </c>
-      <c r="Q28" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q28" s="3">
+        <f>O28*10000000</f>
         <v>5014700000.000001</v>
       </c>
-      <c r="R28" s="2">
+      <c r="R28" s="3">
         <f>Q28/B28</f>
         <v>15970382.165605098</v>
       </c>
-      <c r="S28" s="2">
+      <c r="S28" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>524865696.02388686</v>
-      </c>
-      <c r="T28" s="2">
+        <v>611382019.54430783</v>
+      </c>
+      <c r="T28" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>485748618.57102424</v>
-      </c>
-      <c r="U28" s="2">
+        <v>593692756.03125191</v>
+      </c>
+      <c r="U28" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>598754721.72008288</v>
       </c>
-      <c r="V28" s="2">
+      <c r="V28" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>575452991.33117366</v>
-      </c>
-      <c r="W28" s="2">
+        <v>548050467.9344511</v>
+      </c>
+      <c r="W28" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>547183198.72348428</v>
-      </c>
-      <c r="X28" s="2">
+        <v>530767702.76177973</v>
+      </c>
+      <c r="X28" s="3">
         <f t="shared" ca="1" si="7"/>
         <v>518041614.91999668</v>
       </c>
-      <c r="Y28" s="2">
+      <c r="Y28" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>624078565.34973335</v>
+        <v>629804056.77496028</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29" s="3">
         <v>686</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D29" s="2">
+      <c r="D29" s="3">
         <v>584.97</v>
       </c>
-      <c r="E29" s="2">
+      <c r="E29" s="3">
         <v>430.23</v>
       </c>
-      <c r="F29" s="2">
+      <c r="F29" s="3">
         <v>28.68</v>
       </c>
-      <c r="G29" s="2">
+      <c r="G29" s="3">
         <v>8.9905956112852667</v>
       </c>
-      <c r="H29" s="2">
+      <c r="H29" s="3">
         <v>41.02</v>
       </c>
-      <c r="I29" s="2">
+      <c r="I29" s="3">
         <v>259.89</v>
       </c>
-      <c r="J29" s="2">
+      <c r="J29" s="3">
         <v>24.13</v>
       </c>
-      <c r="K29" s="2">
+      <c r="K29" s="3">
         <v>-5.45</v>
       </c>
-      <c r="L29">
+      <c r="L29" s="3">
         <v>1.47</v>
       </c>
       <c r="M29" s="3">
         <v>0.11035438069952673</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="3">
         <f t="shared" si="0"/>
+        <v>401.55</v>
+      </c>
+      <c r="P29" s="4">
+        <f t="shared" si="1"/>
         <v>6.6662017990377243E-2</v>
       </c>
-      <c r="P29" s="2">
-        <f>E29-F29</f>
-        <v>401.55</v>
-      </c>
-      <c r="Q29" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q29" s="3">
+        <f>O29*10000000</f>
         <v>4015500000</v>
       </c>
-      <c r="R29" s="2">
+      <c r="R29" s="3">
         <f>Q29/B29</f>
         <v>5853498.5422740523</v>
       </c>
-      <c r="S29" s="2">
+      <c r="S29" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>447995038.83032227</v>
-      </c>
-      <c r="T29" s="2">
+        <v>475706072.16003299</v>
+      </c>
+      <c r="T29" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>414891914.38439202</v>
-      </c>
-      <c r="U29" s="2">
+        <v>401926542.05987978</v>
+      </c>
+      <c r="U29" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>431065437.03999269</v>
-      </c>
-      <c r="V29" s="2">
+        <v>422268183.22284997</v>
+      </c>
+      <c r="V29" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>473957043.55396158</v>
-      </c>
-      <c r="W29" s="2">
+        <v>482734025.84199792</v>
+      </c>
+      <c r="W29" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>398720733.51775324</v>
-      </c>
-      <c r="X29" s="2">
+        <v>473207024.39469618</v>
+      </c>
+      <c r="X29" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>454118354.96266168</v>
-      </c>
-      <c r="Y29" s="2">
+        <v>462851400.25040519</v>
+      </c>
+      <c r="Y29" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>435543009.09523451</v>
+        <v>444712335.60250258</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
-      <c r="B30" s="2">
+      <c r="B30" s="3">
         <v>30000</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D30" s="2">
+      <c r="D30" s="3">
         <v>44140.09</v>
       </c>
-      <c r="E30" s="2">
+      <c r="E30" s="3">
         <v>14484.99</v>
       </c>
-      <c r="F30" s="2">
+      <c r="F30" s="3">
         <v>1702.14</v>
       </c>
-      <c r="G30" s="2">
+      <c r="G30" s="3">
         <v>89.539189900052605</v>
       </c>
-      <c r="H30" s="2">
+      <c r="H30" s="3">
         <v>2963.4700000000003</v>
       </c>
-      <c r="I30" s="2">
+      <c r="I30" s="3">
         <v>9628.39</v>
       </c>
-      <c r="J30" s="2">
+      <c r="J30" s="3">
         <v>1905.2</v>
       </c>
-      <c r="K30" s="2">
+      <c r="K30" s="3">
         <v>31.94</v>
       </c>
-      <c r="L30">
+      <c r="L30" s="3">
         <v>-1755.71</v>
       </c>
       <c r="M30" s="3">
         <v>0.17678344977716942</v>
       </c>
-      <c r="O30" s="4">
+      <c r="O30" s="3">
         <f t="shared" si="0"/>
+        <v>12782.85</v>
+      </c>
+      <c r="P30" s="4">
+        <f t="shared" si="1"/>
         <v>0.11751060925827357</v>
       </c>
-      <c r="P30" s="2">
-        <f>E30-F30</f>
-        <v>12782.85</v>
-      </c>
-      <c r="Q30" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q30" s="3">
+        <f>O30*10000000</f>
         <v>127828500000</v>
       </c>
-      <c r="R30" s="2">
+      <c r="R30" s="3">
         <f>Q30/B30</f>
         <v>4260950</v>
       </c>
-      <c r="S30" s="2">
+      <c r="S30" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>14702443962.922504</v>
-      </c>
-      <c r="T30" s="2">
+        <v>13232199566.630255</v>
+      </c>
+      <c r="T30" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>13620310091.911139</v>
-      </c>
-      <c r="U30" s="2">
+        <v>12519678973.372864</v>
+      </c>
+      <c r="U30" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>12742263494.008345</v>
-      </c>
-      <c r="V30" s="2">
+        <v>15262711218.097908</v>
+      </c>
+      <c r="V30" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>14529030253.050695</v>
-      </c>
-      <c r="W30" s="2">
+        <v>14808434680.993979</v>
+      </c>
+      <c r="W30" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>13808632907.819939</v>
-      </c>
-      <c r="X30" s="2">
+        <v>12692783783.955702</v>
+      </c>
+      <c r="X30" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>13622281633.33374</v>
-      </c>
-      <c r="Y30" s="2">
+        <v>12649261516.667046</v>
+      </c>
+      <c r="Y30" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>14448764050.55381</v>
+        <v>15470393831.906101</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
-      <c r="B31">
+      <c r="B31" s="3">
         <v>489</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D31" s="2">
+      <c r="D31" s="3">
         <v>18880.09</v>
       </c>
-      <c r="E31" s="2">
+      <c r="E31" s="3">
         <v>1158.4100000000001</v>
       </c>
-      <c r="F31" s="2">
+      <c r="F31" s="3">
         <v>114.48</v>
       </c>
-      <c r="G31" s="2">
+      <c r="G31" s="3">
         <v>20.19047619047619</v>
       </c>
-      <c r="H31" s="2">
+      <c r="H31" s="3">
         <v>171.62</v>
       </c>
-      <c r="I31" s="2">
+      <c r="I31" s="3">
         <v>530.33000000000004</v>
       </c>
-      <c r="J31" s="2">
+      <c r="J31" s="3">
         <v>-13.21</v>
       </c>
-      <c r="K31" s="2">
+      <c r="K31" s="3">
         <v>111.59</v>
       </c>
-      <c r="L31">
+      <c r="L31" s="3">
         <v>-17.97</v>
       </c>
       <c r="M31" s="3">
         <v>0.2158655931212641</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="3">
         <f t="shared" si="0"/>
+        <v>1043.93</v>
+      </c>
+      <c r="P31" s="4">
+        <f t="shared" si="1"/>
         <v>9.8825113733479505E-2</v>
       </c>
-      <c r="P31" s="2">
-        <f>E31-F31</f>
-        <v>1043.93</v>
-      </c>
-      <c r="Q31" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q31" s="3">
+        <f>O31*10000000</f>
         <v>10439300000</v>
       </c>
-      <c r="R31" s="2">
+      <c r="R31" s="3">
         <f>Q31/B31</f>
         <v>21348261.758691207</v>
       </c>
-      <c r="S31" s="2">
+      <c r="S31" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>1104640713.1521215</v>
-      </c>
-      <c r="T31" s="2">
+        <v>1176682498.7924771</v>
+      </c>
+      <c r="T31" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1044908915.5835394</v>
-      </c>
-      <c r="U31" s="2">
+        <v>1011202176.3711673</v>
+      </c>
+      <c r="U31" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>1154968789.5782697</v>
-      </c>
-      <c r="V31" s="2">
+        <v>1074921447.7263105</v>
+      </c>
+      <c r="V31" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>1049626535.9673491</v>
-      </c>
-      <c r="W31" s="2">
+        <v>1083853488.2271538</v>
+      </c>
+      <c r="W31" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1184656699.1228652</v>
-      </c>
-      <c r="X31" s="2">
+        <v>1150483909.72509</v>
+      </c>
+      <c r="X31" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>1112483402.8003216</v>
-      </c>
-      <c r="Y31" s="2">
+        <v>1021668431.1431526</v>
+      </c>
+      <c r="Y31" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>1227655219.9420187</v>
+        <v>1275331150.8135536</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
-      <c r="B32" s="2">
+      <c r="B32" s="3">
         <v>4457</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D32" s="2">
+      <c r="D32" s="3">
         <v>6304.1</v>
       </c>
-      <c r="E32" s="2">
+      <c r="E32" s="3">
         <v>1550.46</v>
       </c>
-      <c r="F32" s="2">
+      <c r="F32" s="3">
         <v>315.24</v>
       </c>
-      <c r="G32" s="2">
+      <c r="G32" s="3">
         <v>22.262711864406779</v>
       </c>
-      <c r="H32" s="2">
+      <c r="H32" s="3">
         <v>442.61</v>
       </c>
-      <c r="I32" s="2">
+      <c r="I32" s="3">
         <v>1516.43</v>
       </c>
-      <c r="J32" s="2">
+      <c r="J32" s="3">
         <v>214.98</v>
       </c>
-      <c r="K32" s="2">
+      <c r="K32" s="3">
         <v>-167.69</v>
       </c>
-      <c r="L32">
+      <c r="L32" s="3">
         <v>-68.09</v>
       </c>
       <c r="M32" s="3">
         <v>0.20788298833444338</v>
       </c>
-      <c r="O32" s="4">
+      <c r="O32" s="3">
         <f t="shared" si="0"/>
+        <v>1235.22</v>
+      </c>
+      <c r="P32" s="4">
+        <f t="shared" si="1"/>
         <v>0.20332030494175923</v>
       </c>
-      <c r="P32" s="2">
-        <f>E32-F32</f>
-        <v>1235.22</v>
-      </c>
-      <c r="Q32" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q32" s="3">
+        <f>O32*10000000</f>
         <v>12352200000</v>
       </c>
-      <c r="R32" s="2">
+      <c r="R32" s="3">
         <f>Q32/B32</f>
         <v>2771415.7505048239</v>
       </c>
-      <c r="S32" s="2">
+      <c r="S32" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>1278641112.795114</v>
-      </c>
-      <c r="T32" s="2">
+        <v>1520162211.8786354</v>
+      </c>
+      <c r="T32" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>1329439024.0056467</v>
-      </c>
-      <c r="U32" s="2">
+        <v>1435794145.9260986</v>
+      </c>
+      <c r="U32" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>1420728558.462404</v>
-      </c>
-      <c r="V32" s="2">
+        <v>1326013321.2315769</v>
+      </c>
+      <c r="V32" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>1403955201.6313484</v>
-      </c>
-      <c r="W32" s="2">
+        <v>1484952617.11008</v>
+      </c>
+      <c r="W32" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>1226516808.5065351</v>
-      </c>
-      <c r="X32" s="2">
+        <v>1361298875.375385</v>
+      </c>
+      <c r="X32" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>1208879215.576375</v>
-      </c>
-      <c r="Y32" s="2">
+        <v>1396927093.5549221</v>
+      </c>
+      <c r="Y32" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>1297477854.4693165</v>
+        <v>1325683894.7838666</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33" s="3">
         <v>450</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="2">
+      <c r="D33" s="3">
         <v>761.41</v>
       </c>
-      <c r="E33" s="2">
+      <c r="E33" s="3">
         <v>144.26000000000002</v>
       </c>
-      <c r="F33" s="2">
+      <c r="F33" s="3">
         <v>26.32</v>
       </c>
-      <c r="G33" s="2">
+      <c r="G33" s="3">
         <v>14.150537634408602</v>
       </c>
-      <c r="H33" s="2">
+      <c r="H33" s="3">
         <v>37.81</v>
       </c>
-      <c r="I33" s="2">
+      <c r="I33" s="3">
         <v>61.35</v>
       </c>
-      <c r="J33" s="2">
+      <c r="J33" s="3">
         <v>23.73</v>
       </c>
-      <c r="K33" s="2">
+      <c r="K33" s="3">
         <v>-6.14</v>
       </c>
-      <c r="L33">
+      <c r="L33" s="3">
         <v>-0.49</v>
       </c>
       <c r="M33" s="3">
         <v>0.42901385493072536</v>
       </c>
-      <c r="O33" s="4">
+      <c r="O33" s="3">
         <f t="shared" si="0"/>
+        <v>117.94000000000003</v>
+      </c>
+      <c r="P33" s="4">
+        <f t="shared" si="1"/>
         <v>0.18244835713295438</v>
       </c>
-      <c r="P33" s="2">
-        <f>E33-F33</f>
-        <v>117.94000000000003</v>
-      </c>
-      <c r="Q33" s="2">
-        <f t="shared" si="1"/>
+      <c r="Q33" s="3">
+        <f>O33*10000000</f>
         <v>1179400000.0000002</v>
       </c>
-      <c r="R33" s="2">
+      <c r="R33" s="3">
         <f>Q33/B33</f>
         <v>2620888.8888888895</v>
       </c>
-      <c r="S33" s="2">
+      <c r="S33" s="3">
         <f t="shared" ca="1" si="2"/>
-        <v>143790048.02890635</v>
-      </c>
-      <c r="T33" s="2">
+        <v>135650988.7065154</v>
+      </c>
+      <c r="T33" s="3">
         <f t="shared" ca="1" si="3"/>
-        <v>130744207.22297467</v>
-      </c>
-      <c r="U33" s="2">
+        <v>135821652.16367272</v>
+      </c>
+      <c r="U33" s="3">
         <f t="shared" ca="1" si="4"/>
-        <v>129192891.94294748</v>
-      </c>
-      <c r="V33" s="2">
+        <v>142112181.13724226</v>
+      </c>
+      <c r="V33" s="3">
         <f t="shared" ca="1" si="5"/>
-        <v>140495759.83633354</v>
-      </c>
-      <c r="W33" s="2">
+        <v>130184144.43550172</v>
+      </c>
+      <c r="W33" s="3">
         <f t="shared" ca="1" si="6"/>
-        <v>117109010.86062466</v>
-      </c>
-      <c r="X33" s="2">
+        <v>138986518.38403806</v>
+      </c>
+      <c r="X33" s="3">
         <f t="shared" ca="1" si="7"/>
-        <v>124402453.04437476</v>
-      </c>
-      <c r="Y33" s="2">
+        <v>141074946.75135285</v>
+      </c>
+      <c r="Y33" s="3">
         <f t="shared" ca="1" si="8"/>
-        <v>138696710.16252214</v>
+        <v>140043280.16410002</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>31</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="3">
         <v>1868</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D34" s="2">
+      <c r="D34" s="3">
         <v>2091.7399999999998</v>
       </c>
-      <c r="E34" s="2">
+      <c r="E34" s="3">
         <v>898.51</v>
       </c>
-      <c r="F34" s="2">
+      <c r="F34" s="3">
         <v>163</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G34" s="3">
         <v>61.977186311787072</v>
       </c>
-      <c r="H34" s="2">
+      <c r="H34" s="3">
         <v>234.77</v>
       </c>
-      <c r="I34" s="2">
+      <c r="I34" s="3">
         <v>814.22</v>
       </c>
-      <c r="J34" s="2">
+      <c r="J34" s="3">
         <v>150.94</v>
       </c>
-      <c r="K34" s="2">
+      <c r="K34" s="3">
         <v>-20.48</v>
       </c>
-      <c r="L34">
+      <c r="L34" s="3">
         <v>-125.8</v>
       </c>
       <c r="M34" s="3">
         <v>0.20019159440937337</v>
       </c>
-      <c r="O34" s="4">
-        <f t="shared" ref="O34:O52" si="9">F34/E34</f>
+      <c r="O34" s="3">
+        <f t="shared" si="0"/>
+        <v>735.51</v>
+      </c>
+      <c r="P34" s="4">
+        <f t="shared" si="1"/>
         <v>0.18141144784142638</v>
       </c>
-      <c r="P34" s="2">
-        <f>E34-F34</f>
-        <v>735.51</v>
-      </c>
-      <c r="Q34" s="2">
-        <f t="shared" ref="Q34:Q52" si="10">P34*10000000</f>
+      <c r="Q34" s="3">
+        <f>O34*10000000</f>
         <v>7355100000</v>
       </c>
-      <c r="R34" s="2">
+      <c r="R34" s="3">
         <f>Q34/B34</f>
         <v>3937419.7002141327</v>
       </c>
-      <c r="S34" s="2">
-        <f t="shared" ref="S34:S52" ca="1" si="11">Q34*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>837501544.14527583</v>
-      </c>
-      <c r="T34" s="2">
-        <f t="shared" ref="T34:T52" ca="1" si="12">Q34*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>783696458.59112489</v>
-      </c>
-      <c r="U34" s="2">
-        <f t="shared" ref="U34:U52" ca="1" si="13">Q34*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>733174700.67145264</v>
-      </c>
-      <c r="V34" s="2">
-        <f t="shared" ref="V34:V52" ca="1" si="14">Q34*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>819906538.10572398</v>
-      </c>
-      <c r="W34" s="2">
-        <f t="shared" ref="W34:W52" ca="1" si="15">Q34*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>738353276.03577697</v>
-      </c>
-      <c r="X34" s="2">
-        <f t="shared" ref="X34:X52" ca="1" si="16">Q34*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>839796320.08064091</v>
-      </c>
-      <c r="Y34" s="2">
-        <f t="shared" ref="Y34:Y52" ca="1" si="17">Q34*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>764183727.9066478</v>
+      <c r="S34" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>845961155.70229888</v>
+      </c>
+      <c r="T34" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>759948081.05806041</v>
+      </c>
+      <c r="U34" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>749288430.35653949</v>
+      </c>
+      <c r="V34" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>779715041.13975716</v>
+      </c>
+      <c r="W34" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>810583487.82188547</v>
+      </c>
+      <c r="X34" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>791807958.93317568</v>
+      </c>
+      <c r="Y34" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>797774221.44100583</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35" s="3">
         <v>8887</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D35" s="2">
+      <c r="D35" s="3">
         <v>62212.53</v>
       </c>
-      <c r="E35" s="2">
+      <c r="E35" s="3">
         <v>7151</v>
       </c>
-      <c r="F35" s="2">
+      <c r="F35" s="3">
         <v>2379.6</v>
       </c>
-      <c r="G35" s="2">
+      <c r="G35" s="3">
         <v>273.83199079401612</v>
       </c>
-      <c r="H35" s="2">
+      <c r="H35" s="3">
         <v>3378.2999999999997</v>
       </c>
-      <c r="I35" s="2">
+      <c r="I35" s="3">
         <v>8362.4</v>
       </c>
-      <c r="J35" s="2">
+      <c r="J35" s="3">
         <v>2198.9</v>
       </c>
-      <c r="K35" s="2">
+      <c r="K35" s="3">
         <v>-2371.9</v>
       </c>
-      <c r="L35">
+      <c r="L35" s="3">
         <v>-2096.1</v>
       </c>
       <c r="M35" s="3">
         <v>0.28455945661532572</v>
       </c>
-      <c r="O35" s="4">
-        <f t="shared" si="9"/>
+      <c r="O35" s="3">
+        <f t="shared" si="0"/>
+        <v>4771.3999999999996</v>
+      </c>
+      <c r="P35" s="4">
+        <f t="shared" si="1"/>
         <v>0.33276464830093694</v>
       </c>
-      <c r="P35" s="2">
-        <f>E35-F35</f>
-        <v>4771.3999999999996</v>
-      </c>
-      <c r="Q35" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q35" s="3">
+        <f>O35*10000000</f>
         <v>47714000000</v>
       </c>
-      <c r="R35" s="2">
+      <c r="R35" s="3">
         <f>Q35/B35</f>
         <v>5368965.9052548669</v>
       </c>
-      <c r="S35" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>5158643546.4084406</v>
-      </c>
-      <c r="T35" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>5238055622.7419834</v>
-      </c>
-      <c r="U35" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>5435714797.3651228</v>
-      </c>
-      <c r="V35" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>5318897167.8395281</v>
-      </c>
-      <c r="W35" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>5622861402.5572243</v>
-      </c>
-      <c r="X35" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>4669650984.6028357</v>
-      </c>
-      <c r="Y35" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>5229797474.400177</v>
+      <c r="S35" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>5378160293.0641193</v>
+      </c>
+      <c r="T35" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>5135348649.7470427</v>
+      </c>
+      <c r="U35" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>5331181820.4927168</v>
+      </c>
+      <c r="V35" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>5631773471.8300886</v>
+      </c>
+      <c r="W35" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>5362543745.0314264</v>
+      </c>
+      <c r="X35" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>5032846061.1830559</v>
+      </c>
+      <c r="Y35" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>4902935132.2501669</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>10</v>
       </c>
-      <c r="B36" s="2">
+      <c r="B36" s="3">
         <v>24000</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D36" s="2">
+      <c r="D36" s="3">
         <v>84738.29</v>
       </c>
-      <c r="E36" s="2">
+      <c r="E36" s="3">
         <v>12076.869999999999</v>
       </c>
-      <c r="F36" s="2">
+      <c r="F36" s="3">
         <v>1400.16</v>
       </c>
-      <c r="G36" s="2">
+      <c r="G36" s="3">
         <v>90.566623544631312</v>
       </c>
-      <c r="H36" s="2">
+      <c r="H36" s="3">
         <v>2262.9499999999998</v>
       </c>
-      <c r="I36" s="2">
+      <c r="I36" s="3">
         <v>6319.0700000000006</v>
       </c>
-      <c r="J36" s="2">
+      <c r="J36" s="3">
         <v>1156.92</v>
       </c>
-      <c r="K36" s="2">
+      <c r="K36" s="3">
         <v>-516.83000000000004</v>
       </c>
-      <c r="L36">
+      <c r="L36" s="3">
         <v>-628.20000000000005</v>
       </c>
       <c r="M36" s="3">
         <v>0.22157690926038165</v>
       </c>
-      <c r="O36" s="4">
-        <f t="shared" si="9"/>
+      <c r="O36" s="3">
+        <f t="shared" si="0"/>
+        <v>10676.71</v>
+      </c>
+      <c r="P36" s="4">
+        <f t="shared" si="1"/>
         <v>0.11593732482008999</v>
       </c>
-      <c r="P36" s="2">
-        <f>E36-F36</f>
-        <v>10676.71</v>
-      </c>
-      <c r="Q36" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q36" s="3">
+        <f>O36*10000000</f>
         <v>106767099999.99998</v>
       </c>
-      <c r="R36" s="2">
+      <c r="R36" s="3">
         <f>Q36/B36</f>
         <v>4448629.166666666</v>
       </c>
-      <c r="S36" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>12034425489.910843</v>
-      </c>
-      <c r="T36" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>12410386583.564573</v>
-      </c>
-      <c r="U36" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>12397120093.406456</v>
-      </c>
-      <c r="V36" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>12601922317.228279</v>
-      </c>
-      <c r="W36" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>11300482261.658165</v>
-      </c>
-      <c r="X36" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>10797332650.643326</v>
-      </c>
-      <c r="Y36" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>10971039224.51412</v>
+      <c r="S36" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>12157225750.011974</v>
+      </c>
+      <c r="T36" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>10571810793.406858</v>
+      </c>
+      <c r="U36" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>11929304240.825081</v>
+      </c>
+      <c r="V36" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>12835291249.028803</v>
+      </c>
+      <c r="W36" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>12465480432.963131</v>
+      </c>
+      <c r="X36" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>11958336161.465189</v>
+      </c>
+      <c r="Y36" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>13043346633.58901</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="3">
         <v>973</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="2">
+      <c r="D37" s="3">
         <v>885.29</v>
       </c>
-      <c r="E37" s="2">
+      <c r="E37" s="3">
         <v>300.29999999999995</v>
       </c>
-      <c r="F37" s="2">
+      <c r="F37" s="3">
         <v>5.04</v>
       </c>
-      <c r="G37" s="2">
+      <c r="G37" s="3">
         <v>0.93333333333333324</v>
       </c>
-      <c r="H37" s="2">
+      <c r="H37" s="3">
         <v>14.68</v>
       </c>
-      <c r="I37" s="2">
+      <c r="I37" s="3">
         <v>441.48</v>
       </c>
-      <c r="J37" s="2">
+      <c r="J37" s="3">
         <v>-22.3</v>
       </c>
-      <c r="K37" s="2">
+      <c r="K37" s="3">
         <v>15.95</v>
       </c>
-      <c r="L37">
+      <c r="L37" s="3">
         <v>-10.32</v>
       </c>
       <c r="M37" s="3">
         <v>1.1416145691764065E-2</v>
       </c>
-      <c r="O37" s="4">
-        <f t="shared" si="9"/>
+      <c r="O37" s="3">
+        <f t="shared" si="0"/>
+        <v>295.25999999999993</v>
+      </c>
+      <c r="P37" s="4">
+        <f t="shared" si="1"/>
         <v>1.6783216783216787E-2</v>
       </c>
-      <c r="P37" s="2">
-        <f>E37-F37</f>
-        <v>295.25999999999993</v>
-      </c>
-      <c r="Q37" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q37" s="3">
+        <f>O37*10000000</f>
         <v>2952599999.9999995</v>
       </c>
-      <c r="R37" s="2">
+      <c r="R37" s="3">
         <f>Q37/B37</f>
         <v>3034532.3741007191</v>
       </c>
-      <c r="S37" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>342995031.66644549</v>
-      </c>
-      <c r="T37" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>346381924.82992411</v>
-      </c>
-      <c r="U37" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>349305856.68204707</v>
-      </c>
-      <c r="V37" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>348500950.51610672</v>
-      </c>
-      <c r="W37" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>318953672.48797524</v>
-      </c>
-      <c r="X37" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>308227891.12100333</v>
-      </c>
-      <c r="Y37" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>367450569.73530263</v>
+      <c r="S37" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>370162954.96675801</v>
+      </c>
+      <c r="T37" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>314603766.58864665</v>
+      </c>
+      <c r="U37" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>313728408.31628299</v>
+      </c>
+      <c r="V37" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>338820368.55732602</v>
+      </c>
+      <c r="W37" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>351171215.16352832</v>
+      </c>
+      <c r="X37" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>301806476.7226491</v>
+      </c>
+      <c r="Y37" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>306770659.13681227</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="3">
         <v>1668</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D38" s="2">
+      <c r="D38" s="3">
         <v>1590.57</v>
       </c>
-      <c r="E38" s="2">
+      <c r="E38" s="3">
         <v>596.57000000000005</v>
       </c>
-      <c r="F38" s="2">
+      <c r="F38" s="3">
         <v>-34.25</v>
       </c>
-      <c r="G38" s="2">
+      <c r="G38" s="3">
         <v>-9.1823056300268089</v>
       </c>
-      <c r="H38" s="2">
+      <c r="H38" s="3">
         <v>83.2</v>
       </c>
-      <c r="I38" s="2">
+      <c r="I38" s="3">
         <v>315.77999999999997</v>
       </c>
-      <c r="J38" s="2">
+      <c r="J38" s="3">
         <v>113.35</v>
       </c>
-      <c r="K38" s="2">
+      <c r="K38" s="3">
         <v>-109.39</v>
       </c>
-      <c r="L38">
+      <c r="L38" s="3">
         <v>13.41</v>
       </c>
       <c r="M38" s="3">
@@ -4030,511 +4029,511 @@
       <c r="N38" t="s">
         <v>116</v>
       </c>
-      <c r="O38" s="4">
-        <f t="shared" si="9"/>
+      <c r="O38" s="3">
+        <f t="shared" si="0"/>
+        <v>630.82000000000005</v>
+      </c>
+      <c r="P38" s="4">
+        <f t="shared" si="1"/>
         <v>-5.7411535947164617E-2</v>
       </c>
-      <c r="P38" s="2">
-        <f>E38-F38</f>
-        <v>630.82000000000005</v>
-      </c>
-      <c r="Q38" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q38" s="3">
+        <f>O38*10000000</f>
         <v>6308200000.000001</v>
       </c>
-      <c r="R38" s="2">
+      <c r="R38" s="3">
         <f>Q38/B38</f>
         <v>3781894.4844124704</v>
       </c>
-      <c r="S38" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>747316410.01118672</v>
-      </c>
-      <c r="T38" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>692515875.41143036</v>
-      </c>
-      <c r="U38" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>621907021.24728763</v>
-      </c>
-      <c r="V38" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>620473959.68685937</v>
-      </c>
-      <c r="W38" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>619492083.02963984</v>
-      </c>
-      <c r="X38" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>624227550.97211552</v>
-      </c>
-      <c r="Y38" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>756245084.63212597</v>
+      <c r="S38" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>682016917.87428689</v>
+      </c>
+      <c r="T38" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>712883989.3941195</v>
+      </c>
+      <c r="U38" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>677187645.35815775</v>
+      </c>
+      <c r="V38" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>716992131.19370413</v>
+      </c>
+      <c r="W38" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>743390499.6355679</v>
+      </c>
+      <c r="X38" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>679104698.31032348</v>
+      </c>
+      <c r="Y38" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>691424077.37794375</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="3">
         <v>690</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="2">
+      <c r="D39" s="3">
         <v>6597.21</v>
       </c>
-      <c r="E39" s="2">
+      <c r="E39" s="3">
         <v>1153.04</v>
       </c>
-      <c r="F39" s="2">
+      <c r="F39" s="3">
         <v>208.93</v>
       </c>
-      <c r="G39" s="2">
+      <c r="G39" s="3">
         <v>17.690939881456394</v>
       </c>
-      <c r="H39" s="2">
+      <c r="H39" s="3">
         <v>329.34000000000003</v>
       </c>
-      <c r="I39" s="2">
+      <c r="I39" s="3">
         <v>1682.6699999999998</v>
       </c>
-      <c r="J39" s="2">
+      <c r="J39" s="3">
         <v>119.97</v>
       </c>
-      <c r="K39" s="2">
+      <c r="K39" s="3">
         <v>-38.380000000000003</v>
       </c>
-      <c r="L39">
+      <c r="L39" s="3">
         <v>-1.74</v>
       </c>
       <c r="M39" s="3">
         <v>0.12416576036893748</v>
       </c>
-      <c r="O39" s="4">
-        <f t="shared" si="9"/>
+      <c r="O39" s="3">
+        <f t="shared" si="0"/>
+        <v>944.1099999999999</v>
+      </c>
+      <c r="P39" s="4">
+        <f t="shared" si="1"/>
         <v>0.18119926455283425</v>
       </c>
-      <c r="P39" s="2">
-        <f>E39-F39</f>
-        <v>944.1099999999999</v>
-      </c>
-      <c r="Q39" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q39" s="3">
+        <f>O39*10000000</f>
         <v>9441099999.9999981</v>
       </c>
-      <c r="R39" s="2">
+      <c r="R39" s="3">
         <f>Q39/B39</f>
         <v>13682753.623188403</v>
       </c>
-      <c r="S39" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>1020733319.06771</v>
-      </c>
-      <c r="T39" s="2">
-        <f t="shared" ca="1" si="12"/>
+      <c r="S39" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>1161898565.3217552</v>
+      </c>
+      <c r="T39" s="3">
+        <f t="shared" ca="1" si="3"/>
         <v>1066930191.2223486</v>
       </c>
-      <c r="U39" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>1003163745.7680889</v>
-      </c>
-      <c r="V39" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>980216026.71648276</v>
-      </c>
-      <c r="W39" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>1019871813.7662476</v>
-      </c>
-      <c r="X39" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>1016374776.8329464</v>
-      </c>
-      <c r="Y39" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>1185722591.6641226</v>
+      <c r="U39" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>992821851.48181999</v>
+      </c>
+      <c r="V39" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>1000852153.5947245</v>
+      </c>
+      <c r="W39" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>1091983962.2143662</v>
+      </c>
+      <c r="X39" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>1108772483.8177598</v>
+      </c>
+      <c r="Y39" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>1121046813.9369886</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>56</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="3">
         <v>17187</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D40" s="2">
+      <c r="D40" s="3">
         <v>19652.2</v>
       </c>
-      <c r="E40" s="2">
+      <c r="E40" s="3">
         <v>5617.12</v>
       </c>
-      <c r="F40" s="2">
+      <c r="F40" s="3">
         <v>539.12</v>
       </c>
-      <c r="G40" s="2">
+      <c r="G40" s="3">
         <v>1.1516459103240553</v>
       </c>
-      <c r="H40" s="2">
+      <c r="H40" s="3">
         <v>1364.89</v>
       </c>
-      <c r="I40" s="2">
+      <c r="I40" s="3">
         <v>8336.0500000000011</v>
       </c>
-      <c r="J40" s="2">
+      <c r="J40" s="3">
         <v>1214.07</v>
       </c>
-      <c r="K40" s="2">
+      <c r="K40" s="3">
         <v>-958.37</v>
       </c>
-      <c r="L40">
+      <c r="L40" s="3">
         <v>-256.07</v>
       </c>
       <c r="M40" s="3">
         <v>6.4673316498821382E-2</v>
       </c>
-      <c r="O40" s="4">
-        <f t="shared" si="9"/>
+      <c r="O40" s="3">
+        <f t="shared" si="0"/>
+        <v>5078</v>
+      </c>
+      <c r="P40" s="4">
+        <f t="shared" si="1"/>
         <v>9.5978010083459145E-2</v>
       </c>
-      <c r="P40" s="2">
-        <f>E40-F40</f>
-        <v>5078</v>
-      </c>
-      <c r="Q40" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q40" s="3">
+        <f>O40*10000000</f>
         <v>50780000000</v>
       </c>
-      <c r="R40" s="2">
+      <c r="R40" s="3">
         <f>Q40/B40</f>
         <v>2954558.6780706346</v>
       </c>
-      <c r="S40" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>5314910172.9102373</v>
-      </c>
-      <c r="T40" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>4918801693.2292271</v>
-      </c>
-      <c r="U40" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>5896252294.4163504</v>
-      </c>
-      <c r="V40" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>5383193945.5720329</v>
-      </c>
-      <c r="W40" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>5873356452.240262</v>
-      </c>
-      <c r="X40" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>5963655371.5420713</v>
-      </c>
-      <c r="Y40" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>5971696576.2700291</v>
+      <c r="S40" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>5723749416.9802561</v>
+      </c>
+      <c r="T40" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>5902562031.8750734</v>
+      </c>
+      <c r="U40" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>5729377229.4800386</v>
+      </c>
+      <c r="V40" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>5938162393.5691509</v>
+      </c>
+      <c r="W40" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>5485493290.2998667</v>
+      </c>
+      <c r="X40" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>5301026996.9262848</v>
+      </c>
+      <c r="Y40" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>6203607122.9212933</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>32</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="3">
         <v>2278</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D41" s="2">
+      <c r="D41" s="3">
         <v>1787.98</v>
       </c>
-      <c r="E41" s="2">
+      <c r="E41" s="3">
         <v>899.84</v>
       </c>
-      <c r="F41" s="2">
+      <c r="F41" s="3">
         <v>108.8</v>
       </c>
-      <c r="G41" s="2">
+      <c r="G41" s="3">
         <v>8.2051282051282044</v>
       </c>
-      <c r="H41" s="2">
+      <c r="H41" s="3">
         <v>163.86999999999998</v>
       </c>
-      <c r="I41" s="2">
+      <c r="I41" s="3">
         <v>619.1</v>
       </c>
-      <c r="J41" s="2">
+      <c r="J41" s="3">
         <v>111</v>
       </c>
-      <c r="K41" s="2">
+      <c r="K41" s="3">
         <v>-105.76</v>
       </c>
-      <c r="L41">
+      <c r="L41" s="3">
         <v>21.24</v>
       </c>
       <c r="M41" s="3">
         <v>0.17573897593280569</v>
       </c>
-      <c r="O41" s="4">
-        <f t="shared" si="9"/>
+      <c r="O41" s="3">
+        <f t="shared" si="0"/>
+        <v>791.04000000000008</v>
+      </c>
+      <c r="P41" s="4">
+        <f t="shared" si="1"/>
         <v>0.1209103840682788</v>
       </c>
-      <c r="P41" s="2">
-        <f>E41-F41</f>
-        <v>791.04000000000008</v>
-      </c>
-      <c r="Q41" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q41" s="3">
+        <f>O41*10000000</f>
         <v>7910400000.000001</v>
       </c>
-      <c r="R41" s="2">
+      <c r="R41" s="3">
         <f>Q41/B41</f>
         <v>3472519.7541703251</v>
       </c>
-      <c r="S41" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>982616472.40049267</v>
-      </c>
-      <c r="T41" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>876919600.48890853</v>
-      </c>
-      <c r="U41" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>918505595.70206988</v>
-      </c>
-      <c r="V41" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>804001741.28866601</v>
-      </c>
-      <c r="W41" s="2">
-        <f t="shared" ca="1" si="15"/>
+      <c r="S41" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>827945361.0041188</v>
+      </c>
+      <c r="T41" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>868405817.95989001</v>
+      </c>
+      <c r="U41" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>901175301.44354022</v>
+      </c>
+      <c r="V41" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>838582461.34409249</v>
+      </c>
+      <c r="W41" s="3">
+        <f t="shared" ca="1" si="6"/>
         <v>776834940.80683291</v>
       </c>
-      <c r="X41" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>808578863.87145019</v>
-      </c>
-      <c r="Y41" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>975416307.25116467</v>
+      <c r="X41" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>834384572.29287946</v>
+      </c>
+      <c r="Y41" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>930258144.87842548</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="3">
         <v>406</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D42" s="2">
+      <c r="D42" s="3">
         <v>418.1</v>
       </c>
-      <c r="E42" s="2">
+      <c r="E42" s="3">
         <v>97.49</v>
       </c>
-      <c r="F42" s="2">
+      <c r="F42" s="3">
         <v>1.31</v>
       </c>
-      <c r="G42" s="2">
+      <c r="G42" s="3">
         <v>0.94927536231884069</v>
       </c>
-      <c r="H42" s="2">
+      <c r="H42" s="3">
         <v>29.669999999999998</v>
       </c>
-      <c r="I42" s="2">
+      <c r="I42" s="3">
         <v>168.77</v>
       </c>
-      <c r="J42" s="2">
+      <c r="J42" s="3">
         <v>27.96</v>
       </c>
-      <c r="K42" s="2">
+      <c r="K42" s="3">
         <v>-64.03</v>
       </c>
-      <c r="L42">
+      <c r="L42" s="3">
         <v>37.25</v>
       </c>
       <c r="M42" s="3">
         <v>7.7620430171238966E-3</v>
       </c>
-      <c r="O42" s="4">
-        <f t="shared" si="9"/>
+      <c r="O42" s="3">
+        <f t="shared" si="0"/>
+        <v>96.179999999999993</v>
+      </c>
+      <c r="P42" s="4">
+        <f t="shared" si="1"/>
         <v>1.3437275618012105E-2</v>
       </c>
-      <c r="P42" s="2">
-        <f>E42-F42</f>
-        <v>96.179999999999993</v>
-      </c>
-      <c r="Q42" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q42" s="3">
+        <f>O42*10000000</f>
         <v>961799999.99999988</v>
       </c>
-      <c r="R42" s="2">
+      <c r="R42" s="3">
         <f>Q42/B42</f>
         <v>2368965.5172413792</v>
       </c>
-      <c r="S42" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>121685630.8561295</v>
-      </c>
-      <c r="T42" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>95235026.717956349</v>
-      </c>
-      <c r="U42" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>109570995.76865856</v>
-      </c>
-      <c r="V42" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>97755976.280774519</v>
-      </c>
-      <c r="W42" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>105997090.26214319</v>
-      </c>
-      <c r="X42" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>101450126.6220787</v>
-      </c>
-      <c r="Y42" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>104322068.52142859</v>
+      <c r="S42" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>103985902.73160157</v>
+      </c>
+      <c r="T42" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>107656986.7246463</v>
+      </c>
+      <c r="U42" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>113785264.8366839</v>
+      </c>
+      <c r="V42" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>110369650.63958414</v>
+      </c>
+      <c r="W42" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>95502328.850049824</v>
+      </c>
+      <c r="X42" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>106679514.59228894</v>
+      </c>
+      <c r="Y42" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>112008957.78090227</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>12</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="3">
         <v>6873</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D43" s="2">
+      <c r="D43" s="3">
         <v>6806.48</v>
       </c>
-      <c r="E43" s="2">
+      <c r="E43" s="3">
         <v>10228.01</v>
       </c>
-      <c r="F43" s="2">
+      <c r="F43" s="3">
         <v>424.67</v>
       </c>
-      <c r="G43" s="2">
+      <c r="G43" s="3">
         <v>15.145149786019973</v>
       </c>
-      <c r="H43" s="2">
+      <c r="H43" s="3">
         <v>740.82</v>
       </c>
-      <c r="I43" s="2">
+      <c r="I43" s="3">
         <v>1705.94</v>
       </c>
-      <c r="J43" s="2">
+      <c r="J43" s="3">
         <v>644.33000000000004</v>
       </c>
-      <c r="K43" s="2">
+      <c r="K43" s="3">
         <v>-437.07</v>
       </c>
-      <c r="L43">
+      <c r="L43" s="3">
         <v>-433.3</v>
       </c>
       <c r="M43" s="3">
         <v>0.24893607043624044</v>
       </c>
-      <c r="O43" s="4">
-        <f t="shared" si="9"/>
+      <c r="O43" s="3">
+        <f t="shared" si="0"/>
+        <v>9803.34</v>
+      </c>
+      <c r="P43" s="4">
+        <f t="shared" si="1"/>
         <v>4.1520295736902878E-2</v>
       </c>
-      <c r="P43" s="2">
-        <f>E43-F43</f>
-        <v>9803.34</v>
-      </c>
-      <c r="Q43" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q43" s="3">
+        <f>O43*10000000</f>
         <v>98033400000</v>
       </c>
-      <c r="R43" s="2">
+      <c r="R43" s="3">
         <f>Q43/B43</f>
         <v>14263553.033609778</v>
       </c>
-      <c r="S43" s="2">
-        <f t="shared" ca="1" si="11"/>
+      <c r="S43" s="3">
+        <f t="shared" ca="1" si="2"/>
         <v>12290297713.689014</v>
       </c>
-      <c r="T43" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>10445599434.90193</v>
-      </c>
-      <c r="U43" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>9986987588.0021725</v>
-      </c>
-      <c r="V43" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>11785346245.543249</v>
-      </c>
-      <c r="W43" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>9841236971.7509937</v>
-      </c>
-      <c r="X43" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>10020698724.900816</v>
-      </c>
-      <c r="Y43" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>10297450292.120619</v>
+      <c r="T43" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>10762132751.111078</v>
+      </c>
+      <c r="U43" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>10094374551.314024</v>
+      </c>
+      <c r="V43" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>10606811620.988924</v>
+      </c>
+      <c r="W43" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>9734267004.6667442</v>
+      </c>
+      <c r="X43" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>11086730504.145586</v>
+      </c>
+      <c r="Y43" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>12312168827.535522</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>41</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="3">
         <v>632</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D44" s="2">
+      <c r="D44" s="3">
         <v>497.72</v>
       </c>
-      <c r="E44" s="2">
+      <c r="E44" s="3">
         <v>296.68</v>
       </c>
-      <c r="F44" s="2">
+      <c r="F44" s="3">
         <v>-31.44</v>
       </c>
-      <c r="G44" s="2">
+      <c r="G44" s="3">
         <v>-0.55774348057477385</v>
       </c>
-      <c r="H44" s="2">
+      <c r="H44" s="3">
         <v>-5.0500000000000007</v>
       </c>
-      <c r="I44" s="2">
+      <c r="I44" s="3">
         <v>304.48</v>
       </c>
-      <c r="J44" s="2">
+      <c r="J44" s="3">
         <v>9.75</v>
       </c>
-      <c r="K44" s="2">
+      <c r="K44" s="3">
         <v>-14.57</v>
       </c>
-      <c r="L44">
+      <c r="L44" s="3">
         <v>-12.05</v>
       </c>
       <c r="M44" s="3">
@@ -4543,558 +4542,558 @@
       <c r="N44" t="s">
         <v>115</v>
       </c>
-      <c r="O44" s="4">
-        <f t="shared" si="9"/>
+      <c r="O44" s="3">
+        <f t="shared" si="0"/>
+        <v>328.12</v>
+      </c>
+      <c r="P44" s="4">
+        <f t="shared" si="1"/>
         <v>-0.10597276526897667</v>
       </c>
-      <c r="P44" s="2">
-        <f>E44-F44</f>
-        <v>328.12</v>
-      </c>
-      <c r="Q44" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q44" s="3">
+        <f>O44*10000000</f>
         <v>3281200000</v>
       </c>
-      <c r="R44" s="2">
+      <c r="R44" s="3">
         <f>Q44/B44</f>
         <v>5191772.1518987343</v>
       </c>
-      <c r="S44" s="2">
-        <f t="shared" ca="1" si="11"/>
+      <c r="S44" s="3">
+        <f t="shared" ca="1" si="2"/>
         <v>347202121.59768766</v>
       </c>
-      <c r="T44" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>339022126.62883008</v>
-      </c>
-      <c r="U44" s="2">
-        <f t="shared" ca="1" si="13"/>
+      <c r="T44" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>328427685.17167914</v>
+      </c>
+      <c r="U44" s="3">
+        <f t="shared" ca="1" si="4"/>
         <v>363020853.15722501</v>
       </c>
-      <c r="V44" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>326324507.50827241</v>
-      </c>
-      <c r="W44" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>379512744.99981779</v>
-      </c>
-      <c r="X44" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>321122915.92989117</v>
-      </c>
-      <c r="Y44" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>359643112.56658137</v>
+      <c r="V44" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>333496474.70625639</v>
+      </c>
+      <c r="W44" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>325808111.27342844</v>
+      </c>
+      <c r="X44" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>342531110.32521719</v>
+      </c>
+      <c r="Y44" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>408344784.05997264</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="3">
         <v>1032</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D45" s="2">
+      <c r="D45" s="3">
         <v>6113.01</v>
       </c>
-      <c r="E45" s="2">
+      <c r="E45" s="3">
         <v>4067.9399999999996</v>
       </c>
-      <c r="F45" s="2">
+      <c r="F45" s="3">
         <v>507.28</v>
       </c>
-      <c r="G45" s="2">
+      <c r="G45" s="3">
         <v>37.687964338781569</v>
       </c>
-      <c r="H45" s="2">
+      <c r="H45" s="3">
         <v>751.2399999999999</v>
       </c>
-      <c r="I45" s="2">
+      <c r="I45" s="3">
         <v>2268.29</v>
       </c>
-      <c r="J45" s="2">
+      <c r="J45" s="3">
         <v>642.1</v>
       </c>
-      <c r="K45" s="2">
+      <c r="K45" s="3">
         <v>-220.3</v>
       </c>
-      <c r="L45">
+      <c r="L45" s="3">
         <v>-208.23</v>
       </c>
       <c r="M45" s="3">
         <v>0.22363983441270735</v>
       </c>
-      <c r="O45" s="4">
-        <f t="shared" si="9"/>
+      <c r="O45" s="3">
+        <f t="shared" si="0"/>
+        <v>3560.66</v>
+      </c>
+      <c r="P45" s="4">
+        <f t="shared" si="1"/>
         <v>0.12470193759003328</v>
       </c>
-      <c r="P45" s="2">
-        <f>E45-F45</f>
-        <v>3560.66</v>
-      </c>
-      <c r="Q45" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q45" s="3">
+        <f>O45*10000000</f>
         <v>35606600000</v>
       </c>
-      <c r="R45" s="2">
+      <c r="R45" s="3">
         <f>Q45/B45</f>
         <v>34502519.379844964</v>
       </c>
-      <c r="S45" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>3685826220.9849668</v>
-      </c>
-      <c r="T45" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>4177160009.7030334</v>
-      </c>
-      <c r="U45" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>3744374123.4572854</v>
-      </c>
-      <c r="V45" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>3696831934.5079622</v>
-      </c>
-      <c r="W45" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>4157211122.0061707</v>
-      </c>
-      <c r="X45" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>4220394905.6580572</v>
-      </c>
-      <c r="Y45" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>3984046449.874465</v>
+      <c r="S45" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>4341084215.8267384</v>
+      </c>
+      <c r="T45" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>3908902027.4285269</v>
+      </c>
+      <c r="U45" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>3627362432.0992451</v>
+      </c>
+      <c r="V45" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>4124886158.5036216</v>
+      </c>
+      <c r="W45" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>3613276956.510036</v>
+      </c>
+      <c r="X45" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>3794483493.1604548</v>
+      </c>
+      <c r="Y45" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>3780778773.8604617</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="3">
         <v>13000</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D46" s="2">
+      <c r="D46" s="3">
         <v>27484.94</v>
       </c>
-      <c r="E46" s="2">
+      <c r="E46" s="3">
         <v>3908.36</v>
       </c>
-      <c r="F46" s="2">
+      <c r="F46" s="3">
         <v>784.94</v>
       </c>
-      <c r="G46" s="2">
+      <c r="G46" s="3">
         <v>125.99357945425361</v>
       </c>
-      <c r="H46" s="2">
+      <c r="H46" s="3">
         <v>1143.8200000000002</v>
       </c>
-      <c r="I46" s="2">
+      <c r="I46" s="3">
         <v>2859.96</v>
       </c>
-      <c r="J46" s="2">
+      <c r="J46" s="3">
         <v>811.98</v>
       </c>
-      <c r="K46" s="2">
+      <c r="K46" s="3">
         <v>-311.35000000000002</v>
       </c>
-      <c r="L46">
+      <c r="L46" s="3">
         <v>-498.59</v>
       </c>
       <c r="M46" s="3">
         <v>0.27445838403334316</v>
       </c>
-      <c r="O46" s="4">
-        <f t="shared" si="9"/>
+      <c r="O46" s="3">
+        <f t="shared" si="0"/>
+        <v>3123.42</v>
+      </c>
+      <c r="P46" s="4">
+        <f t="shared" si="1"/>
         <v>0.20083615634179042</v>
       </c>
-      <c r="P46" s="2">
-        <f>E46-F46</f>
-        <v>3123.42</v>
-      </c>
-      <c r="Q46" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q46" s="3">
+        <f>O46*10000000</f>
         <v>31234200000</v>
       </c>
-      <c r="R46" s="2">
+      <c r="R46" s="3">
         <f>Q46/B46</f>
         <v>2402630.769230769</v>
       </c>
-      <c r="S46" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>3233216127.1081386</v>
-      </c>
-      <c r="T46" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>3428898791.3787918</v>
-      </c>
-      <c r="U46" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>3558289037.2607985</v>
-      </c>
-      <c r="V46" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>3754902530.1840692</v>
-      </c>
-      <c r="W46" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>3476308862.9191041</v>
-      </c>
-      <c r="X46" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>3328530562.3696809</v>
-      </c>
-      <c r="Y46" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>3245185979.005291</v>
+      <c r="S46" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>3664311610.7225571</v>
+      </c>
+      <c r="T46" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>3630598720.2834268</v>
+      </c>
+      <c r="U46" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>3729360625.5906448</v>
+      </c>
+      <c r="V46" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>3174599411.8828945</v>
+      </c>
+      <c r="W46" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>3578553241.2402544</v>
+      </c>
+      <c r="X46" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>3362495159.9448814</v>
+      </c>
+      <c r="Y46" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>3423492900.9286585</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="3">
         <v>12638</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D47" s="2">
+      <c r="D47" s="3">
         <v>22732.83</v>
       </c>
-      <c r="E47" s="2">
+      <c r="E47" s="3">
         <v>5296.6399999999994</v>
       </c>
-      <c r="F47" s="2">
+      <c r="F47" s="3">
         <v>676.95</v>
       </c>
-      <c r="G47" s="2">
+      <c r="G47" s="3">
         <v>16.68597485826966</v>
       </c>
-      <c r="H47" s="2">
+      <c r="H47" s="3">
         <v>1070.4000000000001</v>
       </c>
-      <c r="I47" s="2">
+      <c r="I47" s="3">
         <v>3579.42</v>
       </c>
-      <c r="J47" s="2">
+      <c r="J47" s="3">
         <v>699.25</v>
       </c>
-      <c r="K47" s="2">
+      <c r="K47" s="3">
         <v>-65.22</v>
       </c>
-      <c r="L47">
+      <c r="L47" s="3">
         <v>-486.39</v>
       </c>
       <c r="M47" s="3">
         <v>0.18912281878069631</v>
       </c>
-      <c r="O47" s="4">
-        <f t="shared" si="9"/>
+      <c r="O47" s="3">
+        <f t="shared" si="0"/>
+        <v>4619.6899999999996</v>
+      </c>
+      <c r="P47" s="4">
+        <f t="shared" si="1"/>
         <v>0.12780744018849688</v>
       </c>
-      <c r="P47" s="2">
-        <f>E47-F47</f>
-        <v>4619.6899999999996</v>
-      </c>
-      <c r="Q47" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q47" s="3">
+        <f>O47*10000000</f>
         <v>46196899999.999992</v>
       </c>
-      <c r="R47" s="2">
+      <c r="R47" s="3">
         <f>Q47/B47</f>
         <v>3655396.4234847282</v>
       </c>
-      <c r="S47" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>5632232041.5351715</v>
-      </c>
-      <c r="T47" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>5121228647.3283339</v>
-      </c>
-      <c r="U47" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>4807440693.8351622</v>
-      </c>
-      <c r="V47" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>4695386837.8512297</v>
-      </c>
-      <c r="W47" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>4587140294.9187632</v>
-      </c>
-      <c r="X47" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>4671882037.8984222</v>
-      </c>
-      <c r="Y47" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>5432726852.3885164</v>
+      <c r="S47" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>5100889396.1073246</v>
+      </c>
+      <c r="T47" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>5419552646.2018299</v>
+      </c>
+      <c r="U47" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>5566510277.0722933</v>
+      </c>
+      <c r="V47" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>4745874868.3657589</v>
+      </c>
+      <c r="W47" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>5544894861.9897137</v>
+      </c>
+      <c r="X47" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>5525881980.3099623</v>
+      </c>
+      <c r="Y47" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>5801941298.6673479</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>2</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="3">
         <v>636833</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="2">
+      <c r="D48" s="3">
         <v>894608.69</v>
       </c>
-      <c r="E48" s="2">
+      <c r="E48" s="3">
         <v>266897</v>
       </c>
-      <c r="F48" s="2">
+      <c r="F48" s="3">
         <v>49210</v>
       </c>
-      <c r="G48" s="2">
+      <c r="G48" s="3">
         <v>136.01061330532599</v>
       </c>
-      <c r="H48" s="2">
+      <c r="H48" s="3">
         <v>72030</v>
       </c>
-      <c r="I48" s="2">
+      <c r="I48" s="3">
         <v>107240</v>
       </c>
-      <c r="J48" s="2">
+      <c r="J48" s="3">
         <v>52094</v>
       </c>
-      <c r="K48" s="2">
+      <c r="K48" s="3">
         <v>-12845</v>
       </c>
-      <c r="L48">
+      <c r="L48" s="3">
         <v>-42133</v>
       </c>
       <c r="M48" s="3">
         <v>0.45887728459530025</v>
       </c>
-      <c r="O48" s="4">
-        <f t="shared" si="9"/>
+      <c r="O48" s="3">
+        <f t="shared" si="0"/>
+        <v>217687</v>
+      </c>
+      <c r="P48" s="4">
+        <f t="shared" si="1"/>
         <v>0.18437824329235622</v>
       </c>
-      <c r="P48" s="2">
-        <f>E48-F48</f>
-        <v>217687</v>
-      </c>
-      <c r="Q48" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q48" s="3">
+        <f>O48*10000000</f>
         <v>2176870000000</v>
       </c>
-      <c r="R48" s="2">
+      <c r="R48" s="3">
         <f>Q48/B48</f>
         <v>3418274.4926848956</v>
       </c>
-      <c r="S48" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>252880713467.36279</v>
-      </c>
-      <c r="T48" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>217891129775.59219</v>
-      </c>
-      <c r="U48" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>259918079061.7178</v>
-      </c>
-      <c r="V48" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>252181925032.48776</v>
-      </c>
-      <c r="W48" s="2">
-        <f t="shared" ca="1" si="15"/>
+      <c r="S48" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>262895791228.44647</v>
+      </c>
+      <c r="T48" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>257720691132.4209</v>
+      </c>
+      <c r="U48" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>214611257940.86792</v>
+      </c>
+      <c r="V48" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>254560999796.94519</v>
+      </c>
+      <c r="W48" s="3">
+        <f t="shared" ca="1" si="6"/>
         <v>232780376893.74979</v>
       </c>
-      <c r="X48" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>234349361879.90134</v>
-      </c>
-      <c r="Y48" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>253513141946.88373</v>
+      <c r="X48" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>224880700793.84473</v>
+      </c>
+      <c r="Y48" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>268425679708.46515</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>5</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="3">
         <v>148000</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D49" s="2">
+      <c r="D49" s="3">
         <v>140573.01</v>
       </c>
-      <c r="E49" s="2">
+      <c r="E49" s="3">
         <v>53852.3</v>
       </c>
-      <c r="F49" s="2">
+      <c r="F49" s="3">
         <v>4251.5</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G49" s="3">
         <v>43.426966292134829</v>
       </c>
-      <c r="H49" s="2">
+      <c r="H49" s="3">
         <v>7836</v>
       </c>
-      <c r="I49" s="2">
+      <c r="I49" s="3">
         <v>27361.5</v>
       </c>
-      <c r="J49" s="2">
+      <c r="J49" s="3">
         <v>5785.7</v>
       </c>
-      <c r="K49" s="2">
+      <c r="K49" s="3">
         <v>20</v>
       </c>
-      <c r="L49">
+      <c r="L49" s="3">
         <v>-5834.3</v>
       </c>
       <c r="M49" s="3">
         <v>0.15538256309047385</v>
       </c>
-      <c r="O49" s="4">
-        <f t="shared" si="9"/>
+      <c r="O49" s="3">
+        <f t="shared" si="0"/>
+        <v>49600.800000000003</v>
+      </c>
+      <c r="P49" s="4">
+        <f t="shared" si="1"/>
         <v>7.8947417287655308E-2</v>
       </c>
-      <c r="P49" s="2">
-        <f>E49-F49</f>
-        <v>49600.800000000003</v>
-      </c>
-      <c r="Q49" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q49" s="3">
+        <f>O49*10000000</f>
         <v>496008000000</v>
       </c>
-      <c r="R49" s="2">
+      <c r="R49" s="3">
         <f>Q49/B49</f>
         <v>3351405.4054054054</v>
       </c>
-      <c r="S49" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>61042779293.526512</v>
-      </c>
-      <c r="T49" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>48045785550.516792</v>
-      </c>
-      <c r="U49" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>56506644280.745277</v>
-      </c>
-      <c r="V49" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>59628922597.394516</v>
-      </c>
-      <c r="W49" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>51957435992.4104</v>
-      </c>
-      <c r="X49" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>57172954136.571526</v>
-      </c>
-      <c r="Y49" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>52100791408.786835</v>
+      <c r="S49" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>51344393798.293327</v>
+      </c>
+      <c r="T49" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>55519574413.930519</v>
+      </c>
+      <c r="U49" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>57049977398.829361</v>
+      </c>
+      <c r="V49" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>53666030337.65506</v>
+      </c>
+      <c r="W49" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>50874989409.235184</v>
+      </c>
+      <c r="X49" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>50161176742.463692</v>
+      </c>
+      <c r="Y49" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>54932356159.264374</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>3</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="3">
         <v>234000</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D50" s="2">
+      <c r="D50" s="3">
         <v>212948.04</v>
       </c>
-      <c r="E50" s="2">
+      <c r="E50" s="3">
         <v>92997.799999999988</v>
       </c>
-      <c r="F50" s="2">
+      <c r="F50" s="3">
         <v>13135.4</v>
       </c>
-      <c r="G50" s="2">
+      <c r="G50" s="3">
         <v>12.543233926337601</v>
       </c>
-      <c r="H50" s="2">
+      <c r="H50" s="3">
         <v>21794</v>
       </c>
-      <c r="I50" s="2">
+      <c r="I50" s="3">
         <v>82830.899999999994</v>
       </c>
-      <c r="J50" s="2">
+      <c r="J50" s="3">
         <v>16942.599999999999</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50" s="3">
         <v>-8044</v>
       </c>
-      <c r="L50">
+      <c r="L50" s="3">
         <v>-6396.3</v>
       </c>
       <c r="M50" s="3">
         <v>0.15858091605910354</v>
       </c>
-      <c r="O50" s="4">
-        <f t="shared" si="9"/>
+      <c r="O50" s="3">
+        <f t="shared" si="0"/>
+        <v>79862.399999999994</v>
+      </c>
+      <c r="P50" s="4">
+        <f t="shared" si="1"/>
         <v>0.14124420147573385</v>
       </c>
-      <c r="P50" s="2">
-        <f>E50-F50</f>
-        <v>79862.399999999994</v>
-      </c>
-      <c r="Q50" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q50" s="3">
+        <f>O50*10000000</f>
         <v>798624000000</v>
       </c>
-      <c r="R50" s="2">
+      <c r="R50" s="3">
         <f>Q50/B50</f>
         <v>3412923.076923077</v>
       </c>
-      <c r="S50" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>86343977524.560791</v>
-      </c>
-      <c r="T50" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>94549481243.684067</v>
-      </c>
-      <c r="U50" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>82233297852.248428</v>
-      </c>
-      <c r="V50" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>87280646280.671417</v>
-      </c>
-      <c r="W50" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>95856780742.034073</v>
-      </c>
-      <c r="X50" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>84238413311.947388</v>
-      </c>
-      <c r="Y50" s="2">
-        <f t="shared" ca="1" si="17"/>
+      <c r="S50" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>87262530476.949738</v>
+      </c>
+      <c r="T50" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>90251777550.789322</v>
+      </c>
+      <c r="U50" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>91856343345.596649</v>
+      </c>
+      <c r="V50" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>81171001041.024414</v>
+      </c>
+      <c r="W50" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>90628229065.195847</v>
+      </c>
+      <c r="X50" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>89449036815.779175</v>
+      </c>
+      <c r="Y50" s="3">
+        <f t="shared" ca="1" si="8"/>
         <v>82975821608.913361</v>
       </c>
     </row>
@@ -5102,170 +5101,170 @@
       <c r="A51" t="s">
         <v>45</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="3">
         <v>548</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="2">
+      <c r="D51" s="3">
         <v>392.95</v>
       </c>
-      <c r="E51" s="2">
+      <c r="E51" s="3">
         <v>236.07999999999998</v>
       </c>
-      <c r="F51" s="2">
+      <c r="F51" s="3">
         <v>9.15</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G51" s="3">
         <v>0.68488023952095811</v>
       </c>
-      <c r="H51" s="2">
+      <c r="H51" s="3">
         <v>22.580000000000002</v>
       </c>
-      <c r="I51" s="2">
+      <c r="I51" s="3">
         <v>182.55</v>
       </c>
-      <c r="J51" s="2">
+      <c r="J51" s="3">
         <v>16.7</v>
       </c>
-      <c r="K51" s="2">
+      <c r="K51" s="3">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="L51">
+      <c r="L51" s="3">
         <v>-9.06</v>
       </c>
       <c r="M51" s="3">
         <v>5.012325390304026E-2</v>
       </c>
-      <c r="O51" s="4">
-        <f t="shared" si="9"/>
+      <c r="O51" s="3">
+        <f t="shared" si="0"/>
+        <v>226.92999999999998</v>
+      </c>
+      <c r="P51" s="4">
+        <f t="shared" si="1"/>
         <v>3.8758048119281602E-2</v>
       </c>
-      <c r="P51" s="2">
-        <f>E51-F51</f>
-        <v>226.92999999999998</v>
-      </c>
-      <c r="Q51" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q51" s="3">
+        <f>O51*10000000</f>
         <v>2269300000</v>
       </c>
-      <c r="R51" s="2">
+      <c r="R51" s="3">
         <f>Q51/B51</f>
         <v>4141058.3941605841</v>
       </c>
-      <c r="S51" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>240127323.70523974</v>
-      </c>
-      <c r="T51" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>236912379.80770499</v>
-      </c>
-      <c r="U51" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>270954212.61478919</v>
-      </c>
-      <c r="V51" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>270329852.29488868</v>
-      </c>
-      <c r="W51" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>252568905.32244536</v>
-      </c>
-      <c r="X51" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>222090769.57201689</v>
-      </c>
-      <c r="Y51" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>272050183.97572738</v>
+      <c r="S51" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>247957562.52171493</v>
+      </c>
+      <c r="T51" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>239354775.47582567</v>
+      </c>
+      <c r="U51" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>236152754.11380711</v>
+      </c>
+      <c r="V51" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>240568767.63857061</v>
+      </c>
+      <c r="W51" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>240188076.63016862</v>
+      </c>
+      <c r="X51" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>224558444.78948376</v>
+      </c>
+      <c r="Y51" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>251322550.91091001</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>18</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="3">
         <v>9900</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D52" s="2">
+      <c r="D52" s="3">
         <v>12575.77</v>
       </c>
-      <c r="E52" s="2">
+      <c r="E52" s="3">
         <v>5440.8</v>
       </c>
-      <c r="F52" s="2">
+      <c r="F52" s="3">
         <v>649.79999999999995</v>
       </c>
-      <c r="G52" s="2">
+      <c r="G52" s="3">
         <v>28.612945838837515</v>
       </c>
-      <c r="H52" s="2">
+      <c r="H52" s="3">
         <v>967.39999999999986</v>
       </c>
-      <c r="I52" s="2">
+      <c r="I52" s="3">
         <v>4069.7000000000003</v>
       </c>
-      <c r="J52" s="2">
+      <c r="J52" s="3">
         <v>565</v>
       </c>
-      <c r="K52" s="2">
+      <c r="K52" s="3">
         <v>-472.9</v>
       </c>
-      <c r="L52">
+      <c r="L52" s="3">
         <v>-264.5</v>
       </c>
       <c r="M52" s="3">
         <v>0.15966778878049978</v>
       </c>
-      <c r="O52" s="4">
-        <f t="shared" si="9"/>
+      <c r="O52" s="3">
+        <f t="shared" si="0"/>
+        <v>4791</v>
+      </c>
+      <c r="P52" s="4">
+        <f>F52/E52</f>
         <v>0.1194309660344067</v>
       </c>
-      <c r="P52" s="2">
-        <f>E52-F52</f>
-        <v>4791</v>
-      </c>
-      <c r="Q52" s="2">
-        <f t="shared" si="10"/>
+      <c r="Q52" s="3">
+        <f>O52*10000000</f>
         <v>47910000000</v>
       </c>
-      <c r="R52" s="2">
+      <c r="R52" s="3">
         <f>Q52/B52</f>
         <v>4839393.9393939395</v>
       </c>
-      <c r="S52" s="2">
-        <f t="shared" ca="1" si="11"/>
-        <v>5455357368.3566732</v>
-      </c>
-      <c r="T52" s="2">
-        <f t="shared" ca="1" si="12"/>
-        <v>4847057060.4187031</v>
-      </c>
-      <c r="U52" s="2">
-        <f t="shared" ca="1" si="13"/>
-        <v>5090675351.3625689</v>
-      </c>
-      <c r="V52" s="2">
-        <f t="shared" ca="1" si="14"/>
-        <v>5759628235.1114721</v>
-      </c>
-      <c r="W52" s="2">
-        <f t="shared" ca="1" si="15"/>
-        <v>4704965869.4952669</v>
-      </c>
-      <c r="X52" s="2">
-        <f t="shared" ca="1" si="16"/>
-        <v>5053520031.673727</v>
-      </c>
-      <c r="Y52" s="2">
-        <f t="shared" ca="1" si="17"/>
-        <v>5852989705.7731218</v>
+      <c r="S52" s="3">
+        <f t="shared" ca="1" si="2"/>
+        <v>5841089707.5334082</v>
+      </c>
+      <c r="T52" s="3">
+        <f t="shared" ca="1" si="3"/>
+        <v>5362701428.5483522</v>
+      </c>
+      <c r="U52" s="3">
+        <f t="shared" ca="1" si="4"/>
+        <v>4880750594.6053495</v>
+      </c>
+      <c r="V52" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>4764783358.1376724</v>
+      </c>
+      <c r="W52" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>5123185057.894846</v>
+      </c>
+      <c r="X52" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>4688833019.0787163</v>
+      </c>
+      <c r="Y52" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>5634186352.2862759</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">

--- a/Excel Files/Dataset.xlsx
+++ b/Excel Files/Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\Code\Code\Python\Data_Project\Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA625E34-3705-4A43-88AA-95F467CDEBC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B18FB-D990-4AB8-8D1C-4FDD50DAC32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{369E4836-92E2-44AD-8257-2B7A8DF32B0E}"/>
   </bookViews>
@@ -413,16 +413,16 @@
     <t>Support</t>
   </si>
   <si>
-    <t>Legal / Compliance</t>
-  </si>
-  <si>
-    <t>R/D</t>
-  </si>
-  <si>
     <t>Maintanience</t>
   </si>
   <si>
     <t>Customer Service</t>
+  </si>
+  <si>
+    <t>Research and Development</t>
+  </si>
+  <si>
+    <t>Compliance</t>
   </si>
 </sst>
 </file>
@@ -884,7 +884,7 @@
         <v>120</v>
       </c>
       <c r="T1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="U1" t="s">
         <v>121</v>
@@ -893,13 +893,13 @@
         <v>122</v>
       </c>
       <c r="W1" t="s">
+        <v>126</v>
+      </c>
+      <c r="X1" t="s">
         <v>123</v>
       </c>
-      <c r="X1" t="s">
-        <v>125</v>
-      </c>
       <c r="Y1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="AC1">
         <v>0.11501694819952127</v>
@@ -975,40 +975,40 @@
         <v>-0.12407421261315178</v>
       </c>
       <c r="Q2" s="3">
-        <f>O2*10000000</f>
+        <f t="shared" ref="Q2:Q33" si="0">O2*10000000</f>
         <v>3005100000.0000005</v>
       </c>
       <c r="R2" s="3">
-        <f>Q2/B2</f>
+        <f t="shared" ref="R2:R33" si="1">Q2/B2</f>
         <v>7121090.0473933658</v>
       </c>
       <c r="S2" s="3">
         <f ca="1">Q2*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>345637431.03438139</v>
+        <v>324899185.17231846</v>
       </c>
       <c r="T2" s="3">
         <f ca="1">Q2*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>297557474.30872399</v>
+        <v>323432037.29209125</v>
       </c>
       <c r="U2" s="3">
         <f ca="1">Q2*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>312723148.71872467</v>
+        <v>358808665.37201047</v>
       </c>
       <c r="V2" s="3">
         <f ca="1">Q2*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>315286777.42282212</v>
+        <v>357981861.86549598</v>
       </c>
       <c r="W2" s="3">
         <f ca="1">Q2*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>350857288.89421475</v>
+        <v>357415369.06046176</v>
       </c>
       <c r="X2" s="3">
         <f ca="1">Q2*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>297369489.46233547</v>
+        <v>320244065.57482278</v>
       </c>
       <c r="Y2" s="3">
         <f ca="1">Q2*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>308794281.88634318</v>
+        <v>360259995.53406703</v>
       </c>
     </row>
     <row r="3" spans="1:35" x14ac:dyDescent="0.35">
@@ -1052,48 +1052,48 @@
         <v>6.1343678062920966E-2</v>
       </c>
       <c r="O3" s="3">
-        <f t="shared" ref="O3:O52" si="0">E3-F3</f>
+        <f t="shared" ref="O3:O52" si="2">E3-F3</f>
         <v>90.45</v>
       </c>
       <c r="P3" s="4">
-        <f t="shared" ref="P3:P51" si="1">F3/E3</f>
+        <f t="shared" ref="P3:P51" si="3">F3/E3</f>
         <v>0.13725677222434185</v>
       </c>
       <c r="Q3" s="3">
-        <f>O3*10000000</f>
+        <f t="shared" si="0"/>
         <v>904500000</v>
       </c>
       <c r="R3" s="3">
-        <f>Q3/B3</f>
+        <f t="shared" si="1"/>
         <v>1612299.4652406417</v>
       </c>
       <c r="S3" s="3">
-        <f t="shared" ref="S3:S52" ca="1" si="2">Q3*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>106113486.23939633</v>
+        <f t="shared" ref="S3:S52" ca="1" si="4">Q3*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>94669874.978284955</v>
       </c>
       <c r="T3" s="3">
-        <f t="shared" ref="T3:T52" ca="1" si="3">Q3*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>104163714.07668471</v>
+        <f ca="1">Q3*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>94428787.527461842</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U52" ca="1" si="4">Q3*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>97098415.590256095</v>
+        <f t="shared" ref="U3:U52" ca="1" si="5">Q3*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
+        <v>95116815.272087604</v>
       </c>
       <c r="V3" s="3">
-        <f t="shared" ref="V3:V52" ca="1" si="5">Q3*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>105771325.02921025</v>
+        <f t="shared" ref="V3:V52" ca="1" si="6">Q3*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>90943569.183993861</v>
       </c>
       <c r="W3" s="3">
-        <f t="shared" ref="W3:W52" ca="1" si="6">Q3*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>105603945.89358662</v>
+        <f t="shared" ref="W3:W52" ca="1" si="7">Q3*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>104616993.128226</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" ref="X3:X52" ca="1" si="7">Q3*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>90488311.614280552</v>
+        <f t="shared" ref="X3:X52" ca="1" si="8">Q3*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>106225409.28632934</v>
       </c>
       <c r="Y3" s="3">
-        <f t="shared" ref="Y3:Y52" ca="1" si="8">Q3*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>97074293.067794189</v>
+        <f t="shared" ref="Y3:Y52" ca="1" si="9">Q3*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>102237819.29480453</v>
       </c>
     </row>
     <row r="4" spans="1:35" x14ac:dyDescent="0.35">
@@ -1137,48 +1137,48 @@
         <v>0.4646355517142034</v>
       </c>
       <c r="O4" s="3">
+        <f t="shared" si="2"/>
+        <v>411.37</v>
+      </c>
+      <c r="P4" s="4">
+        <f t="shared" si="3"/>
+        <v>0.23875349284775813</v>
+      </c>
+      <c r="Q4" s="3">
         <f t="shared" si="0"/>
-        <v>411.37</v>
-      </c>
-      <c r="P4" s="4">
+        <v>4113700000</v>
+      </c>
+      <c r="R4" s="3">
         <f t="shared" si="1"/>
-        <v>0.23875349284775813</v>
-      </c>
-      <c r="Q4" s="3">
-        <f>O4*10000000</f>
-        <v>4113700000</v>
-      </c>
-      <c r="R4" s="3">
-        <f>Q4/B4</f>
         <v>3201322.9571984434</v>
       </c>
       <c r="S4" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>477876672.00645435</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>506265385.1949566</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>425038194.04882914</v>
+        <f t="shared" ref="T3:T52" ca="1" si="10">Q4*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>469313005.9289155</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>428088654.91471744</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>446113440.38481081</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>409118958.47152877</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>476556149.42837417</v>
       </c>
       <c r="W4" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>462335922.4532795</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>480290715.55826122</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>469697233.47279209</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>407070935.67641979</v>
       </c>
       <c r="Y4" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>432103969.3277657</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>502555703.45729274</v>
       </c>
     </row>
     <row r="5" spans="1:35" x14ac:dyDescent="0.35">
@@ -1222,48 +1222,48 @@
         <v>0.12960298120456412</v>
       </c>
       <c r="O5" s="3">
+        <f t="shared" si="2"/>
+        <v>1978.21</v>
+      </c>
+      <c r="P5" s="4">
+        <f t="shared" si="3"/>
+        <v>0.16180383715806246</v>
+      </c>
+      <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>1978.21</v>
-      </c>
-      <c r="P5" s="4">
+        <v>19782100000</v>
+      </c>
+      <c r="R5" s="3">
         <f t="shared" si="1"/>
-        <v>0.16180383715806246</v>
-      </c>
-      <c r="Q5" s="3">
-        <f>O5*10000000</f>
-        <v>19782100000</v>
-      </c>
-      <c r="R5" s="3">
-        <f>Q5/B5</f>
         <v>32009870.550161812</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>2047749093.8799748</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2366287841.8168597</v>
       </c>
       <c r="T5" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2192975226.1366854</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2150393182.9107304</v>
       </c>
       <c r="U5" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1971929035.1120641</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2253633182.9852161</v>
       </c>
       <c r="V5" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2075483198.4479744</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2378157831.5549712</v>
       </c>
       <c r="W5" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2180125846.6154532</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2374394486.4128704</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2258695977.4125772</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2366252928.7179384</v>
       </c>
       <c r="Y5" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2484465039.090661</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>2168260397.7518497</v>
       </c>
     </row>
     <row r="6" spans="1:35" x14ac:dyDescent="0.35">
@@ -1307,48 +1307,48 @@
         <v>0.15884454672076548</v>
       </c>
       <c r="O6" s="3">
+        <f t="shared" si="2"/>
+        <v>271</v>
+      </c>
+      <c r="P6" s="4">
+        <f t="shared" si="3"/>
+        <v>8.8248157992127305E-2</v>
+      </c>
+      <c r="Q6" s="3">
         <f t="shared" si="0"/>
-        <v>271</v>
-      </c>
-      <c r="P6" s="4">
+        <v>2710000000</v>
+      </c>
+      <c r="R6" s="3">
         <f t="shared" si="1"/>
-        <v>8.8248157992127305E-2</v>
-      </c>
-      <c r="Q6" s="3">
-        <f>O6*10000000</f>
-        <v>2710000000</v>
-      </c>
-      <c r="R6" s="3">
-        <f>Q6/B6</f>
         <v>1477644.4929116685</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>324163766.80553073</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>342865522.58277291</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>282920966.50018972</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>280004255.50534242</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>296856653.52330643</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>314668052.73470479</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>308019510.40470147</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>287287427.97361577</v>
       </c>
       <c r="W6" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>272047610.23738027</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>289789845.68764418</v>
       </c>
       <c r="X6" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>271114786.59447241</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>324158983.97165179</v>
       </c>
       <c r="Y6" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>318694322.99511188</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>340353160.48021656</v>
       </c>
     </row>
     <row r="7" spans="1:35" x14ac:dyDescent="0.35">
@@ -1392,48 +1392,48 @@
         <v>0.12384417865173024</v>
       </c>
       <c r="O7" s="3">
+        <f t="shared" si="2"/>
+        <v>1006.9700000000001</v>
+      </c>
+      <c r="P7" s="4">
+        <f t="shared" si="3"/>
+        <v>0.15603365908443265</v>
+      </c>
+      <c r="Q7" s="3">
         <f t="shared" si="0"/>
-        <v>1006.9700000000001</v>
-      </c>
-      <c r="P7" s="4">
+        <v>10069700000.000002</v>
+      </c>
+      <c r="R7" s="3">
         <f t="shared" si="1"/>
-        <v>0.15603365908443265</v>
-      </c>
-      <c r="Q7" s="3">
-        <f>O7*10000000</f>
-        <v>10069700000.000002</v>
-      </c>
-      <c r="R7" s="3">
-        <f>Q7/B7</f>
         <v>3356566.6666666674</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>1146604301.6518722</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1181349886.5504138</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>1127129922.2511659</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1192156648.5348868</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>1213351730.0302596</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1210555801.2753499</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1001459799.2368803</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1098763765.7658224</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1087776128.1081641</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1105946178.4999449</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1040246405.5197501</v>
       </c>
       <c r="Y7" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1264669453.9068773</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>1115208518.4451554</v>
       </c>
     </row>
     <row r="8" spans="1:35" x14ac:dyDescent="0.35">
@@ -1477,48 +1477,48 @@
         <v>0.14856981855713969</v>
       </c>
       <c r="O8" s="3">
+        <f t="shared" si="2"/>
+        <v>4966.9599999999991</v>
+      </c>
+      <c r="P8" s="4">
+        <f t="shared" si="3"/>
+        <v>9.4235300124732857E-2</v>
+      </c>
+      <c r="Q8" s="3">
         <f t="shared" si="0"/>
-        <v>4966.9599999999991</v>
-      </c>
-      <c r="P8" s="4">
+        <v>49669599999.999992</v>
+      </c>
+      <c r="R8" s="3">
         <f t="shared" si="1"/>
-        <v>9.4235300124732857E-2</v>
-      </c>
-      <c r="Q8" s="3">
-        <f>O8*10000000</f>
-        <v>49669599999.999992</v>
-      </c>
-      <c r="R8" s="3">
-        <f>Q8/B8</f>
         <v>4139133.3333333326</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>6055616558.9083967</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>6284130391.320035</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="10"/>
         <v>5880407943.6396713</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5876137024.6747293</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5604093643.902751</v>
       </c>
       <c r="V8" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5102630400.7797031</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5211197005.0516119</v>
       </c>
       <c r="W8" s="3">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>4986160878.7625761</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5941271981.6525297</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5563191037.36555</v>
       </c>
       <c r="Y8" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5274015755.1167355</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5500855142.4335852</v>
       </c>
     </row>
     <row r="9" spans="1:35" x14ac:dyDescent="0.35">
@@ -1562,48 +1562,48 @@
         <v>0.26989482563196882</v>
       </c>
       <c r="O9" s="3">
+        <f t="shared" si="2"/>
+        <v>5693.92</v>
+      </c>
+      <c r="P9" s="4">
+        <f t="shared" si="3"/>
+        <v>3.4716123891704954E-2</v>
+      </c>
+      <c r="Q9" s="3">
         <f t="shared" si="0"/>
-        <v>5693.92</v>
-      </c>
-      <c r="P9" s="4">
+        <v>56939200000</v>
+      </c>
+      <c r="R9" s="3">
         <f t="shared" si="1"/>
-        <v>3.4716123891704954E-2</v>
-      </c>
-      <c r="Q9" s="3">
-        <f>O9*10000000</f>
-        <v>56939200000</v>
-      </c>
-      <c r="R9" s="3">
-        <f>Q9/B9</f>
         <v>16571362.048894063</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>6221524366.0760717</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>7138380588.445178</v>
       </c>
       <c r="T9" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>6373365251.1041603</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>6741059400.2063236</v>
       </c>
       <c r="U9" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>6112444560.5049314</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>6658413079.1633043</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>6845097558.0183506</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>6772135763.2050314</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5778060788.7896128</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>6067831652.3835964</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5572498456.2706499</v>
       </c>
       <c r="Y9" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5915896469.1196852</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>7021063941.3728142</v>
       </c>
     </row>
     <row r="10" spans="1:35" x14ac:dyDescent="0.35">
@@ -1647,48 +1647,48 @@
         <v>0.18614209474669297</v>
       </c>
       <c r="O10" s="3">
+        <f t="shared" si="2"/>
+        <v>368.50000000000006</v>
+      </c>
+      <c r="P10" s="4">
+        <f t="shared" si="3"/>
+        <v>0.28542341329093057</v>
+      </c>
+      <c r="Q10" s="3">
         <f t="shared" si="0"/>
-        <v>368.50000000000006</v>
-      </c>
-      <c r="P10" s="4">
+        <v>3685000000.0000005</v>
+      </c>
+      <c r="R10" s="3">
         <f t="shared" si="1"/>
-        <v>0.28542341329093057</v>
-      </c>
-      <c r="Q10" s="3">
-        <f>O10*10000000</f>
-        <v>3685000000.0000005</v>
-      </c>
-      <c r="R10" s="3">
-        <f>Q10/B10</f>
         <v>3941176.4705882357</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>466221199.52675956</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>381453708.70371234</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>380743793.92516118</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>432302849.35252678</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>367329984.90493715</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>439988663.23778188</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>382592712.54941058</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>362456253.99417847</v>
       </c>
       <c r="W10" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>394050030.02175975</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>410133704.71652544</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>384684609.76119268</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>360641821.65111816</v>
       </c>
       <c r="Y10" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>445975672.64400339</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>441768354.97755051</v>
       </c>
     </row>
     <row r="11" spans="1:35" x14ac:dyDescent="0.35">
@@ -1732,48 +1732,48 @@
         <v>0.15353986598038263</v>
       </c>
       <c r="O11" s="3">
+        <f t="shared" si="2"/>
+        <v>377.11</v>
+      </c>
+      <c r="P11" s="4">
+        <f t="shared" si="3"/>
+        <v>0.14361303508572726</v>
+      </c>
+      <c r="Q11" s="3">
         <f t="shared" si="0"/>
-        <v>377.11</v>
-      </c>
-      <c r="P11" s="4">
+        <v>3771100000</v>
+      </c>
+      <c r="R11" s="3">
         <f t="shared" si="1"/>
-        <v>0.14361303508572726</v>
-      </c>
-      <c r="Q11" s="3">
-        <f>O11*10000000</f>
-        <v>3771100000</v>
-      </c>
-      <c r="R11" s="3">
-        <f>Q11/B11</f>
         <v>1508440</v>
       </c>
       <c r="S11" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>464102242.29007971</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>477114454.69073617</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>389639870.08715743</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>369346126.85345131</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>392436280.36776894</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>391531988.6825189</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>436867271.58260006</v>
       </c>
       <c r="W11" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>395027271.47743356</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>423831343.35599643</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>438781100.49224448</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>426478826.64666754</v>
       </c>
       <c r="Y11" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>396117188.5971114</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>456395891.20971531</v>
       </c>
     </row>
     <row r="12" spans="1:35" x14ac:dyDescent="0.35">
@@ -1817,48 +1817,48 @@
         <v>0.1273043641835967</v>
       </c>
       <c r="O12" s="3">
+        <f t="shared" si="2"/>
+        <v>11375.9</v>
+      </c>
+      <c r="P12" s="4">
+        <f t="shared" si="3"/>
+        <v>6.6631112569740733E-2</v>
+      </c>
+      <c r="Q12" s="3">
         <f t="shared" si="0"/>
-        <v>11375.9</v>
-      </c>
-      <c r="P12" s="4">
+        <v>113759000000</v>
+      </c>
+      <c r="R12" s="3">
         <f t="shared" si="1"/>
-        <v>6.6631112569740733E-2</v>
-      </c>
-      <c r="Q12" s="3">
-        <f>O12*10000000</f>
-        <v>113759000000</v>
-      </c>
-      <c r="R12" s="3">
-        <f>Q12/B12</f>
         <v>325025.71428571426</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>14130950051.047688</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>14000107920.945395</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>13223110558.961727</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>12855801932.323902</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>13582814203.871595</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>13208975280.829256</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>12556908671.221163</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>12432582842.79323</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>13405941448.914516</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>11916392399.035126</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11133311530.314667</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>11504421914.658487</v>
       </c>
       <c r="Y12" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>12079154216.791052</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>12468804352.81657</v>
       </c>
     </row>
     <row r="13" spans="1:35" x14ac:dyDescent="0.35">
@@ -1902,48 +1902,48 @@
         <v>0.11596195498634523</v>
       </c>
       <c r="O13" s="3">
+        <f t="shared" si="2"/>
+        <v>6841.3</v>
+      </c>
+      <c r="P13" s="4">
+        <f t="shared" si="3"/>
+        <v>8.2566715837468163E-2</v>
+      </c>
+      <c r="Q13" s="3">
         <f t="shared" si="0"/>
-        <v>6841.3</v>
-      </c>
-      <c r="P13" s="4">
+        <v>68413000000</v>
+      </c>
+      <c r="R13" s="3">
         <f t="shared" si="1"/>
-        <v>8.2566715837468163E-2</v>
-      </c>
-      <c r="Q13" s="3">
-        <f>O13*10000000</f>
-        <v>68413000000</v>
-      </c>
-      <c r="R13" s="3">
-        <f>Q13/B13</f>
         <v>5690650.4741307599</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>8183400656.2608023</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>8655519924.8912334</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>7731291393.1739473</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>6626821194.1490974</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>6819578360.1903563</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>8168505947.9203167</v>
       </c>
       <c r="V13" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>7177702673.3977318</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>7327238145.7601852</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>7614240743.7643566</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>7763539581.8773832</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>6695410839.7877731</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>6918591201.1140318</v>
       </c>
       <c r="Y13" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>7029896910.8150787</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>7186116842.1665249</v>
       </c>
     </row>
     <row r="14" spans="1:35" x14ac:dyDescent="0.35">
@@ -1987,48 +1987,48 @@
         <v>0.12586295429908143</v>
       </c>
       <c r="O14" s="3">
+        <f t="shared" si="2"/>
+        <v>2622.6000000000004</v>
+      </c>
+      <c r="P14" s="4">
+        <f t="shared" si="3"/>
+        <v>7.7588632526730442E-2</v>
+      </c>
+      <c r="Q14" s="3">
         <f t="shared" si="0"/>
-        <v>2622.6000000000004</v>
-      </c>
-      <c r="P14" s="4">
+        <v>26226000000.000004</v>
+      </c>
+      <c r="R14" s="3">
         <f t="shared" si="1"/>
-        <v>7.7588632526730442E-2</v>
-      </c>
-      <c r="Q14" s="3">
-        <f>O14*10000000</f>
-        <v>26226000000.000004</v>
-      </c>
-      <c r="R14" s="3">
-        <f>Q14/B14</f>
         <v>4521724.1379310349</v>
       </c>
       <c r="S14" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>3137091862.8198709</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2775119724.8021936</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2709738599.5878639</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2907323705.8078122</v>
       </c>
       <c r="U14" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2872827525.9417844</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3016468902.2388735</v>
       </c>
       <c r="V14" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2980855970.4331007</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2636911050.7677426</v>
       </c>
       <c r="W14" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2775821838.3214221</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2575504798.4425569</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>3137045576.9891295</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2680748038.517983</v>
       </c>
       <c r="Y14" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2964388113.6821933</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>2754784913.7248669</v>
       </c>
     </row>
     <row r="15" spans="1:35" x14ac:dyDescent="0.35">
@@ -2072,48 +2072,48 @@
         <v>0.11727571796923625</v>
       </c>
       <c r="O15" s="3">
+        <f t="shared" si="2"/>
+        <v>1965.3999999999999</v>
+      </c>
+      <c r="P15" s="4">
+        <f t="shared" si="3"/>
+        <v>8.5885975275108606E-2</v>
+      </c>
+      <c r="Q15" s="3">
         <f t="shared" si="0"/>
-        <v>1965.3999999999999</v>
-      </c>
-      <c r="P15" s="4">
+        <v>19654000000</v>
+      </c>
+      <c r="R15" s="3">
         <f t="shared" si="1"/>
-        <v>8.5885975275108606E-2</v>
-      </c>
-      <c r="Q15" s="3">
-        <f>O15*10000000</f>
-        <v>19654000000</v>
-      </c>
-      <c r="R15" s="3">
-        <f>Q15/B15</f>
         <v>3855237.3479796001</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>2215332237.9151235</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2260543099.9133911</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2009549298.8226089</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1903783546.2529981</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1980688935.3798151</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2002218162.9382913</v>
       </c>
       <c r="V15" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2019084065.4429331</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2212400624.9002352</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1951552059.9073396</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2144562703.1948786</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1944860385.974756</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2073092938.8961685</v>
       </c>
       <c r="Y15" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2086900350.5376394</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>2042020773.1067226</v>
       </c>
     </row>
     <row r="16" spans="1:35" x14ac:dyDescent="0.35">
@@ -2157,48 +2157,48 @@
         <v>0.24965903380948962</v>
       </c>
       <c r="O16" s="3">
+        <f t="shared" si="2"/>
+        <v>102150</v>
+      </c>
+      <c r="P16" s="4">
+        <f t="shared" si="3"/>
+        <v>0.14547431821984272</v>
+      </c>
+      <c r="Q16" s="3">
         <f t="shared" si="0"/>
-        <v>102150</v>
-      </c>
-      <c r="P16" s="4">
+        <v>1021500000000</v>
+      </c>
+      <c r="R16" s="3">
         <f t="shared" si="1"/>
-        <v>0.14547431821984272</v>
-      </c>
-      <c r="Q16" s="3">
-        <f>O16*10000000</f>
-        <v>1021500000000</v>
-      </c>
-      <c r="R16" s="3">
-        <f>Q16/B16</f>
         <v>45119257.950530037</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>112790220082.37852</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>118664710711.66908</v>
       </c>
       <c r="T16" s="3">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="10"/>
         <v>104444622404.97075</v>
       </c>
       <c r="U16" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>118610116556.64241</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>119729079920.38434</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>101591029019.77943</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>111638493428.32904</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>100315646747.84836</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>117034921205.82309</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>117744416724.14117</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>109968842034.81108</v>
       </c>
       <c r="Y16" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>118961478865.86783</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>104966010764.00102</v>
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
@@ -2242,48 +2242,48 @@
         <v>0.21678963868393555</v>
       </c>
       <c r="O17" s="3">
+        <f t="shared" si="2"/>
+        <v>12338.4</v>
+      </c>
+      <c r="P17" s="4">
+        <f t="shared" si="3"/>
+        <v>9.9886194519828414E-2</v>
+      </c>
+      <c r="Q17" s="3">
         <f t="shared" si="0"/>
-        <v>12338.4</v>
-      </c>
-      <c r="P17" s="4">
+        <v>123384000000</v>
+      </c>
+      <c r="R17" s="3">
         <f t="shared" si="1"/>
-        <v>9.9886194519828414E-2</v>
-      </c>
-      <c r="Q17" s="3">
-        <f>O17*10000000</f>
-        <v>123384000000</v>
-      </c>
-      <c r="R17" s="3">
-        <f>Q17/B17</f>
         <v>3650414.2011834318</v>
       </c>
       <c r="S17" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>13765513602.55024</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>12772126022.98476</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>13279537615.802263</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>12084379230.38006</v>
       </c>
       <c r="U17" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>12975006230.548655</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>12569537285.844007</v>
       </c>
       <c r="V17" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>13079952772.360374</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>14023866889.953392</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>13193885727.056932</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>12924622753.035362</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>13014475382.759991</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>13953664327.907619</v>
       </c>
       <c r="Y17" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>14087264123.680321</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>14791627329.864338</v>
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
@@ -2327,48 +2327,48 @@
         <v>0.11428829425398067</v>
       </c>
       <c r="O18" s="3">
+        <f t="shared" si="2"/>
+        <v>370.23</v>
+      </c>
+      <c r="P18" s="4">
+        <f t="shared" si="3"/>
+        <v>9.3018128368446834E-2</v>
+      </c>
+      <c r="Q18" s="3">
         <f t="shared" si="0"/>
-        <v>370.23</v>
-      </c>
-      <c r="P18" s="4">
+        <v>3702300000</v>
+      </c>
+      <c r="R18" s="3">
         <f t="shared" si="1"/>
-        <v>9.3018128368446834E-2</v>
-      </c>
-      <c r="Q18" s="3">
-        <f>O18*10000000</f>
-        <v>3702300000</v>
-      </c>
-      <c r="R18" s="3">
-        <f>Q18/B18</f>
         <v>3098158.9958158997</v>
       </c>
       <c r="S18" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>442860337.21185106</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>421568974.84589666</v>
       </c>
       <c r="T18" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>426362983.555677</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>390500676.52762938</v>
       </c>
       <c r="U18" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>401498842.97267306</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>409609930.70949471</v>
       </c>
       <c r="V18" s="3">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>396527469.73598486</v>
       </c>
       <c r="W18" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>432258141.3839975</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>375701001.38982958</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>378438704.45379114</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>374412760.78938913</v>
       </c>
       <c r="Y18" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>418479909.75694287</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>426934049.34799218</v>
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
@@ -2412,48 +2412,48 @@
         <v>0.27878895405873633</v>
       </c>
       <c r="O19" s="3">
+        <f t="shared" si="2"/>
+        <v>139877</v>
+      </c>
+      <c r="P19" s="4">
+        <f t="shared" si="3"/>
+        <v>0.16035176181043279</v>
+      </c>
+      <c r="Q19" s="3">
         <f t="shared" si="0"/>
-        <v>139877</v>
-      </c>
-      <c r="P19" s="4">
+        <v>1398770000000</v>
+      </c>
+      <c r="R19" s="3">
         <f t="shared" si="1"/>
-        <v>0.16035176181043279</v>
-      </c>
-      <c r="Q19" s="3">
-        <f>O19*10000000</f>
-        <v>1398770000000</v>
-      </c>
-      <c r="R19" s="3">
-        <f>Q19/B19</f>
         <v>4150652.8189910981</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>167317546898.36615</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>175361659730.01837</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>158073735430.83801</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>138502701520.3533</v>
       </c>
       <c r="U19" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>159351862914.66684</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>167013010170.17966</v>
       </c>
       <c r="V19" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>165099463033.73798</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>155927270642.97473</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>143470284624.35263</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>160259360484.64923</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>162751939735.23291</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>136894154917.48561</v>
       </c>
       <c r="Y19" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>167688554109.07684</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>158106351017.12961</v>
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
@@ -2497,48 +2497,48 @@
         <v>0.11945050684892169</v>
       </c>
       <c r="O20" s="3">
+        <f t="shared" si="2"/>
+        <v>2244.2600000000002</v>
+      </c>
+      <c r="P20" s="4">
+        <f t="shared" si="3"/>
+        <v>0.12912926896466084</v>
+      </c>
+      <c r="Q20" s="3">
         <f t="shared" si="0"/>
-        <v>2244.2600000000002</v>
-      </c>
-      <c r="P20" s="4">
+        <v>22442600000.000004</v>
+      </c>
+      <c r="R20" s="3">
         <f t="shared" si="1"/>
-        <v>0.12912926896466084</v>
-      </c>
-      <c r="Q20" s="3">
-        <f>O20*10000000</f>
-        <v>22442600000.000004</v>
-      </c>
-      <c r="R20" s="3">
-        <f>Q20/B20</f>
         <v>3803830.5084745768</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>2400589806.3461962</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2736156123.3623314</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2294673404.5871725</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2367136775.2583466</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2286302093.3936558</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2605892708.5992203</v>
       </c>
       <c r="V20" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2624415189.7186894</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2256506518.2627983</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2693727445.5578275</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2620262151.5880685</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2294019519.9132042</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2416041834.8022046</v>
       </c>
       <c r="Y20" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2818601416.750299</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>2382999379.6161613</v>
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
@@ -2582,48 +2582,48 @@
         <v>0.2715889343964597</v>
       </c>
       <c r="O21" s="3">
+        <f t="shared" si="2"/>
+        <v>2216.9299999999998</v>
+      </c>
+      <c r="P21" s="4">
+        <f t="shared" si="3"/>
+        <v>0.17982308480608514</v>
+      </c>
+      <c r="Q21" s="3">
         <f t="shared" si="0"/>
-        <v>2216.9299999999998</v>
-      </c>
-      <c r="P21" s="4">
+        <v>22169300000</v>
+      </c>
+      <c r="R21" s="3">
         <f t="shared" si="1"/>
-        <v>0.17982308480608514</v>
-      </c>
-      <c r="Q21" s="3">
-        <f>O21*10000000</f>
-        <v>22169300000</v>
-      </c>
-      <c r="R21" s="3">
-        <f>Q21/B21</f>
         <v>2944130.1460823375</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>2422352968.2336645</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2626340586.6112366</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>2386031035.3530855</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2266729483.5854311</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2598443359.2549939</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2428451737.6214895</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2253255941.9436212</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2374398734.5212355</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2394831555.7433014</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2612543515.356329</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2314298105.6116166</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2193761745.944345</v>
       </c>
       <c r="Y21" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2455226293.5307083</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>2505849516.0777335</v>
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
@@ -2667,48 +2667,48 @@
         <v>0.17214955740520543</v>
       </c>
       <c r="O22" s="3">
+        <f t="shared" si="2"/>
+        <v>115.47999999999999</v>
+      </c>
+      <c r="P22" s="4">
+        <f t="shared" si="3"/>
+        <v>0.10139288771301845</v>
+      </c>
+      <c r="Q22" s="3">
         <f t="shared" si="0"/>
-        <v>115.47999999999999</v>
-      </c>
-      <c r="P22" s="4">
+        <v>1154800000</v>
+      </c>
+      <c r="R22" s="3">
         <f t="shared" si="1"/>
-        <v>0.10139288771301845</v>
-      </c>
-      <c r="Q22" s="3">
-        <f>O22*10000000</f>
-        <v>1154800000</v>
-      </c>
-      <c r="R22" s="3">
-        <f>Q22/B22</f>
         <v>2295825.0497017894</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>120867630.32053453</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>140790866.0876556</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>131745790.71072555</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>136717329.98282841</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>134088069.11366683</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>121438251.27275486</v>
       </c>
       <c r="V22" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>138827357.25123626</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>131254955.94662336</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>138607668.19041368</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>114666343.68479678</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>114273164.43083587</v>
       </c>
       <c r="Y22" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>145033147.49909747</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>126574383.27193958</v>
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
@@ -2752,48 +2752,48 @@
         <v>0.28830833470688427</v>
       </c>
       <c r="O23" s="3">
+        <f t="shared" si="2"/>
+        <v>5172.87</v>
+      </c>
+      <c r="P23" s="4">
+        <f t="shared" si="3"/>
+        <v>0.1396431084063621</v>
+      </c>
+      <c r="Q23" s="3">
         <f t="shared" si="0"/>
-        <v>5172.87</v>
-      </c>
-      <c r="P23" s="4">
+        <v>51728700000</v>
+      </c>
+      <c r="R23" s="3">
         <f t="shared" si="1"/>
-        <v>0.1396431084063621</v>
-      </c>
-      <c r="Q23" s="3">
-        <f>O23*10000000</f>
-        <v>51728700000</v>
-      </c>
-      <c r="R23" s="3">
-        <f>Q23/B23</f>
         <v>3694907.1428571427</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>5652193347.9121466</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5473703031.6622906</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>5289069543.808135</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5122046295.0563002</v>
       </c>
       <c r="U23" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5609759662.5018263</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5836416618.5625067</v>
       </c>
       <c r="V23" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5483765747.3870029</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5936035087.3776846</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5983085740.6656322</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>6208862561.0681095</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5175061055.8337584</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5118810392.1833916</v>
       </c>
       <c r="Y23" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>6142323916.0799389</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5492655040.3407145</v>
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
@@ -2837,48 +2837,48 @@
         <v>1.6531791907514453</v>
       </c>
       <c r="O24" s="3">
+        <f t="shared" si="2"/>
+        <v>103.56</v>
+      </c>
+      <c r="P24" s="4">
+        <f t="shared" si="3"/>
+        <v>0.24891209747606616</v>
+      </c>
+      <c r="Q24" s="3">
         <f t="shared" si="0"/>
-        <v>103.56</v>
-      </c>
-      <c r="P24" s="4">
+        <v>1035600000</v>
+      </c>
+      <c r="R24" s="3">
         <f t="shared" si="1"/>
-        <v>0.24891209747606616</v>
-      </c>
-      <c r="Q24" s="3">
-        <f>O24*10000000</f>
-        <v>1035600000</v>
-      </c>
-      <c r="R24" s="3">
-        <f>Q24/B24</f>
         <v>1603095.9752321981</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>109582627.43099029</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>110773742.94654453</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>110344665.94838533</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>117032221.46040869</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>114575275.97513781</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>112306458.62909548</v>
       </c>
       <c r="V24" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>117706643.90225419</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>115443054.59644161</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>105090337.63857806</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>105856122.50016102</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>114865154.20230238</v>
       </c>
       <c r="Y24" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>128880244.53630003</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>124150694.27808718</v>
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
@@ -2922,48 +2922,48 @@
         <v>0.20833881578947369</v>
       </c>
       <c r="O25" s="3">
+        <f t="shared" si="2"/>
+        <v>9613.4</v>
+      </c>
+      <c r="P25" s="4">
+        <f t="shared" si="3"/>
+        <v>0.11642356228343489</v>
+      </c>
+      <c r="Q25" s="3">
         <f t="shared" si="0"/>
-        <v>9613.4</v>
-      </c>
-      <c r="P25" s="4">
+        <v>96134000000</v>
+      </c>
+      <c r="R25" s="3">
         <f t="shared" si="1"/>
-        <v>0.11642356228343489</v>
-      </c>
-      <c r="Q25" s="3">
-        <f>O25*10000000</f>
-        <v>96134000000</v>
-      </c>
-      <c r="R25" s="3">
-        <f>Q25/B25</f>
         <v>5198961.6570223356</v>
       </c>
       <c r="S25" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>10061905761.373629</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>10725328119.266394</v>
       </c>
       <c r="T25" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>10864016587.364744</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>9725881516.3074837</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>11583697152.321217</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>11057165463.579342</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>11031686415.664154</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>10611431695.067425</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>10175049820.986485</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>11433818871.00543</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>10767387037.264238</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>10453773822.586639</v>
       </c>
       <c r="Y25" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>9988176707.1253529</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>10317457257.909704</v>
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
@@ -3007,48 +3007,48 @@
         <v>0.11611845175397661</v>
       </c>
       <c r="O26" s="3">
+        <f t="shared" si="2"/>
+        <v>742.59999999999991</v>
+      </c>
+      <c r="P26" s="4">
+        <f t="shared" si="3"/>
+        <v>0.18999105565130131</v>
+      </c>
+      <c r="Q26" s="3">
         <f t="shared" si="0"/>
-        <v>742.59999999999991</v>
-      </c>
-      <c r="P26" s="4">
+        <v>7425999999.999999</v>
+      </c>
+      <c r="R26" s="3">
         <f t="shared" si="1"/>
-        <v>0.18999105565130131</v>
-      </c>
-      <c r="Q26" s="3">
-        <f>O26*10000000</f>
-        <v>7425999999.999999</v>
-      </c>
-      <c r="R26" s="3">
-        <f>Q26/B26</f>
         <v>6336177.4744027294</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>777245430.16997683</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>854115857.3296448</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>823220690.89181757</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>783258521.4310497</v>
       </c>
       <c r="U26" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>821587484.9279387</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>780914837.1592288</v>
       </c>
       <c r="V26" s="3">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>884620580.41768074</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>834603048.38419271</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>785985395.08025908</v>
       </c>
       <c r="X26" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>750989698.73376095</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>726764224.5810591</v>
       </c>
       <c r="Y26" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>763071557.44833243</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>924164441.79853606</v>
       </c>
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.35">
@@ -3092,48 +3092,48 @@
         <v>0.20260107585149548</v>
       </c>
       <c r="O27" s="3">
+        <f t="shared" si="2"/>
+        <v>34399.1</v>
+      </c>
+      <c r="P27" s="4">
+        <f t="shared" si="3"/>
+        <v>0.11792203662770721</v>
+      </c>
+      <c r="Q27" s="3">
         <f t="shared" si="0"/>
-        <v>34399.1</v>
-      </c>
-      <c r="P27" s="4">
+        <v>343991000000</v>
+      </c>
+      <c r="R27" s="3">
         <f t="shared" si="1"/>
-        <v>0.11792203662770721</v>
-      </c>
-      <c r="Q27" s="3">
-        <f>O27*10000000</f>
-        <v>343991000000</v>
-      </c>
-      <c r="R27" s="3">
-        <f>Q27/B27</f>
         <v>3822122.222222222</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>42729978630.349648</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>37190907326.415428</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>39244342130.562164</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>38133653202.338707</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>38057998993.784889</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>40318870221.138451</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>34962753209.398949</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>34586809626.50219</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>34156728637.406414</v>
       </c>
       <c r="X27" s="3">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>36283978484.981781</v>
       </c>
       <c r="Y27" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>43202370489.575706</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>37311138150.088104</v>
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
@@ -3177,48 +3177,48 @@
         <v>0.19844628674126036</v>
       </c>
       <c r="O28" s="3">
+        <f t="shared" si="2"/>
+        <v>501.47000000000008</v>
+      </c>
+      <c r="P28" s="4">
+        <f t="shared" si="3"/>
+        <v>0.16997153072033896</v>
+      </c>
+      <c r="Q28" s="3">
         <f t="shared" si="0"/>
-        <v>501.47000000000008</v>
-      </c>
-      <c r="P28" s="4">
+        <v>5014700000.000001</v>
+      </c>
+      <c r="R28" s="3">
         <f t="shared" si="1"/>
-        <v>0.16997153072033896</v>
-      </c>
-      <c r="Q28" s="3">
-        <f>O28*10000000</f>
-        <v>5014700000.000001</v>
-      </c>
-      <c r="R28" s="3">
-        <f>Q28/B28</f>
         <v>15970382.165605098</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>611382019.54430783</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>628685284.24839199</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>593692756.03125191</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>566706721.66619492</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>598754721.72008288</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>494384632.61291236</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>548050467.9344511</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>515167439.85838401</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>530767702.76177973</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>552655030.71071911</v>
       </c>
       <c r="X28" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>518041614.91999668</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>539853893.44294393</v>
       </c>
       <c r="Y28" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>629804056.77496028</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>612627582.4992795</v>
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
@@ -3262,48 +3262,48 @@
         <v>0.11035438069952673</v>
       </c>
       <c r="O29" s="3">
+        <f t="shared" si="2"/>
+        <v>401.55</v>
+      </c>
+      <c r="P29" s="4">
+        <f t="shared" si="3"/>
+        <v>6.6662017990377243E-2</v>
+      </c>
+      <c r="Q29" s="3">
         <f t="shared" si="0"/>
-        <v>401.55</v>
-      </c>
-      <c r="P29" s="4">
+        <v>4015500000</v>
+      </c>
+      <c r="R29" s="3">
         <f t="shared" si="1"/>
-        <v>6.6662017990377243E-2</v>
-      </c>
-      <c r="Q29" s="3">
-        <f>O29*10000000</f>
-        <v>4015500000</v>
-      </c>
-      <c r="R29" s="3">
-        <f>Q29/B29</f>
         <v>5853498.5422740523</v>
       </c>
       <c r="S29" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>475706072.16003299</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>498798599.93479186</v>
       </c>
       <c r="T29" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>401926542.05987978</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>471075194.45727849</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>422268183.22284997</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>435464063.94856405</v>
       </c>
       <c r="V29" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>482734025.84199792</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>394964202.96163464</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>473207024.39469618</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>407483826.56209946</v>
       </c>
       <c r="X29" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>462851400.25040519</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>392987037.94845718</v>
       </c>
       <c r="Y29" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>444712335.60250258</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>435543009.09523451</v>
       </c>
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.35">
@@ -3347,48 +3347,48 @@
         <v>0.17678344977716942</v>
       </c>
       <c r="O30" s="3">
+        <f t="shared" si="2"/>
+        <v>12782.85</v>
+      </c>
+      <c r="P30" s="4">
+        <f t="shared" si="3"/>
+        <v>0.11751060925827357</v>
+      </c>
+      <c r="Q30" s="3">
         <f t="shared" si="0"/>
-        <v>12782.85</v>
-      </c>
-      <c r="P30" s="4">
+        <v>127828500000</v>
+      </c>
+      <c r="R30" s="3">
         <f t="shared" si="1"/>
-        <v>0.11751060925827357</v>
-      </c>
-      <c r="Q30" s="3">
-        <f>O30*10000000</f>
-        <v>127828500000</v>
-      </c>
-      <c r="R30" s="3">
-        <f>Q30/B30</f>
         <v>4260950</v>
       </c>
       <c r="S30" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>13232199566.630255</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>15290541721.439405</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>12519678973.372864</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>13895467871.545706</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>15262711218.097908</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>14808434680.993979</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>12852603685.390999</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>12692783783.955702</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>13948114048.302969</v>
       </c>
       <c r="X30" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>12649261516.667046</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>14456298876.190908</v>
       </c>
       <c r="Y30" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>15470393831.906101</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>14740658273.797321</v>
       </c>
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.35">
@@ -3432,48 +3432,48 @@
         <v>0.2158655931212641</v>
       </c>
       <c r="O31" s="3">
+        <f t="shared" si="2"/>
+        <v>1043.93</v>
+      </c>
+      <c r="P31" s="4">
+        <f t="shared" si="3"/>
+        <v>9.8825113733479505E-2</v>
+      </c>
+      <c r="Q31" s="3">
         <f t="shared" si="0"/>
-        <v>1043.93</v>
-      </c>
-      <c r="P31" s="4">
+        <v>10439300000</v>
+      </c>
+      <c r="R31" s="3">
         <f t="shared" si="1"/>
-        <v>9.8825113733479505E-2</v>
-      </c>
-      <c r="Q31" s="3">
-        <f>O31*10000000</f>
-        <v>10439300000</v>
-      </c>
-      <c r="R31" s="3">
-        <f>Q31/B31</f>
         <v>21348261.758691207</v>
       </c>
       <c r="S31" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>1176682498.7924771</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1200696427.3392625</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="10"/>
         <v>1011202176.3711673</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1074921447.7263105</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1177839458.6788297</v>
       </c>
       <c r="V31" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1083853488.2271538</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1163716376.8333652</v>
       </c>
       <c r="W31" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1150483909.72509</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1241611348.1191568</v>
       </c>
       <c r="X31" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1021668431.1431526</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1067075916.971737</v>
       </c>
       <c r="Y31" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1275331150.8135536</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>1299169116.249321</v>
       </c>
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.35">
@@ -3517,48 +3517,48 @@
         <v>0.20788298833444338</v>
       </c>
       <c r="O32" s="3">
+        <f t="shared" si="2"/>
+        <v>1235.22</v>
+      </c>
+      <c r="P32" s="4">
+        <f t="shared" si="3"/>
+        <v>0.20332030494175923</v>
+      </c>
+      <c r="Q32" s="3">
         <f t="shared" si="0"/>
-        <v>1235.22</v>
-      </c>
-      <c r="P32" s="4">
+        <v>12352200000</v>
+      </c>
+      <c r="R32" s="3">
         <f t="shared" si="1"/>
-        <v>0.20332030494175923</v>
-      </c>
-      <c r="Q32" s="3">
-        <f>O32*10000000</f>
-        <v>12352200000</v>
-      </c>
-      <c r="R32" s="3">
-        <f>Q32/B32</f>
         <v>2771415.7505048239</v>
       </c>
       <c r="S32" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>1520162211.8786354</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1562783582.3051393</v>
       </c>
       <c r="T32" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>1435794145.9260986</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1302850243.5255337</v>
       </c>
       <c r="U32" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1326013321.2315769</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1488382299.3415663</v>
       </c>
       <c r="V32" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1484952617.11008</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1322957786.1526165</v>
       </c>
       <c r="W32" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1361298875.375385</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1442168115.496695</v>
       </c>
       <c r="X32" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1396927093.5549221</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1208879215.576375</v>
       </c>
       <c r="Y32" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1325683894.7838666</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>1480817116.5138938</v>
       </c>
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.35">
@@ -3602,48 +3602,48 @@
         <v>0.42901385493072536</v>
       </c>
       <c r="O33" s="3">
+        <f t="shared" si="2"/>
+        <v>117.94000000000003</v>
+      </c>
+      <c r="P33" s="4">
+        <f t="shared" si="3"/>
+        <v>0.18244835713295438</v>
+      </c>
+      <c r="Q33" s="3">
         <f t="shared" si="0"/>
-        <v>117.94000000000003</v>
-      </c>
-      <c r="P33" s="4">
+        <v>1179400000.0000002</v>
+      </c>
+      <c r="R33" s="3">
         <f t="shared" si="1"/>
-        <v>0.18244835713295438</v>
-      </c>
-      <c r="Q33" s="3">
-        <f>O33*10000000</f>
-        <v>1179400000.0000002</v>
-      </c>
-      <c r="R33" s="3">
-        <f>Q33/B33</f>
         <v>2620888.8888888895</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>135650988.7065154</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>147859577.6901018</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>135821652.16367272</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>121858678.57675308</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>142112181.13724226</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>131776749.78180642</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>130184144.43550172</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>119872529.03466989</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>138986518.38403806</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>117109010.86062466</v>
       </c>
       <c r="X33" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>141074946.75135285</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>115424956.43292505</v>
       </c>
       <c r="Y33" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>140043280.16410002</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>148122700.17356735</v>
       </c>
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.35">
@@ -3687,48 +3687,48 @@
         <v>0.20019159440937337</v>
       </c>
       <c r="O34" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>735.51</v>
       </c>
       <c r="P34" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.18141144784142638</v>
       </c>
       <c r="Q34" s="3">
-        <f>O34*10000000</f>
+        <f t="shared" ref="Q34:Q52" si="11">O34*10000000</f>
         <v>7355100000</v>
       </c>
       <c r="R34" s="3">
-        <f>Q34/B34</f>
+        <f t="shared" ref="R34:R65" si="12">Q34/B34</f>
         <v>3937419.7002141327</v>
       </c>
       <c r="S34" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>845961155.70229888</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>905178436.60145986</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>759948081.05806041</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>870773842.87902772</v>
       </c>
       <c r="U34" s="3">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" ca="1" si="5"/>
         <v>749288430.35653949</v>
       </c>
       <c r="V34" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>779715041.13975716</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>868136334.46488428</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>810583487.82188547</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>866762541.43330336</v>
       </c>
       <c r="X34" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>791807958.93317568</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>847794380.27188516</v>
       </c>
       <c r="Y34" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>797774221.44100583</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>915340948.81125951</v>
       </c>
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.35">
@@ -3772,48 +3772,48 @@
         <v>0.28455945661532572</v>
       </c>
       <c r="O35" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4771.3999999999996</v>
       </c>
       <c r="P35" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.33276464830093694</v>
       </c>
       <c r="Q35" s="3">
-        <f>O35*10000000</f>
+        <f t="shared" si="11"/>
         <v>47714000000</v>
       </c>
       <c r="R35" s="3">
-        <f>Q35/B35</f>
+        <f t="shared" si="12"/>
         <v>5368965.9052548669</v>
       </c>
       <c r="S35" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>5378160293.0641193</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>6036710533.0311546</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>5135348649.7470427</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5648883514.7217474</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5331181820.4927168</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5435714797.3651228</v>
       </c>
       <c r="V35" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5631773471.8300886</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>4745290610.5235004</v>
       </c>
       <c r="W35" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5362543745.0314264</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4789844898.4746723</v>
       </c>
       <c r="X35" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5032846061.1830559</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5707351203.4034662</v>
       </c>
       <c r="Y35" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>4902935132.2501669</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5883522158.7002001</v>
       </c>
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.35">
@@ -3857,48 +3857,48 @@
         <v>0.22157690926038165</v>
       </c>
       <c r="O36" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>10676.71</v>
       </c>
       <c r="P36" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.11593732482008999</v>
       </c>
       <c r="Q36" s="3">
-        <f>O36*10000000</f>
+        <f t="shared" si="11"/>
         <v>106767099999.99998</v>
       </c>
       <c r="R36" s="3">
-        <f>Q36/B36</f>
+        <f t="shared" si="12"/>
         <v>4448629.166666666</v>
       </c>
       <c r="S36" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>12157225750.011974</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>12525626530.315369</v>
       </c>
       <c r="T36" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>10571810793.406858</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>12065653622.910002</v>
       </c>
       <c r="U36" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>11929304240.825081</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>11578442351.389048</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>12835291249.028803</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>10968339794.624613</v>
       </c>
       <c r="W36" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>12465480432.963131</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>11649981713.049654</v>
       </c>
       <c r="X36" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11958336161.465189</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>11261734054.972071</v>
       </c>
       <c r="Y36" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>13043346633.58901</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>13165247069.416945</v>
       </c>
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.35">
@@ -3942,48 +3942,48 @@
         <v>1.1416145691764065E-2</v>
       </c>
       <c r="O37" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>295.25999999999993</v>
       </c>
       <c r="P37" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.6783216783216787E-2</v>
       </c>
       <c r="Q37" s="3">
-        <f>O37*10000000</f>
+        <f t="shared" si="11"/>
         <v>2952599999.9999995</v>
       </c>
       <c r="R37" s="3">
-        <f>Q37/B37</f>
+        <f t="shared" si="12"/>
         <v>3034532.3741007191</v>
       </c>
       <c r="S37" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>370162954.96675801</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>373558945.37929708</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>314603766.58864665</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>305070319.11626339</v>
       </c>
       <c r="U37" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>313728408.31628299</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>355774483.65764052</v>
       </c>
       <c r="V37" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>338820368.55732602</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>351727811.16903365</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>351171215.16352832</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>341505952.36086237</v>
       </c>
       <c r="X37" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>301806476.7226491</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>292174355.12511772</v>
       </c>
       <c r="Y37" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>306770659.13681227</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>370821675.87966323</v>
       </c>
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.35">
@@ -4030,48 +4030,48 @@
         <v>116</v>
       </c>
       <c r="O38" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>630.82000000000005</v>
       </c>
       <c r="P38" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-5.7411535947164617E-2</v>
       </c>
       <c r="Q38" s="3">
-        <f>O38*10000000</f>
+        <f t="shared" si="11"/>
         <v>6308200000.000001</v>
       </c>
       <c r="R38" s="3">
-        <f>Q38/B38</f>
+        <f t="shared" si="12"/>
         <v>3781894.4844124704</v>
       </c>
       <c r="S38" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>682016917.87428689</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>754571909.13750899</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>712883989.3941195</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>719673360.72168255</v>
       </c>
       <c r="U38" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>677187645.35815775</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>746288425.49674535</v>
       </c>
       <c r="V38" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>716992131.19370413</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>737674596.51659942</v>
       </c>
       <c r="W38" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>743390499.6355679</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>626375328.39663589</v>
       </c>
       <c r="X38" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>679104698.31032348</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>658525768.05849552</v>
       </c>
       <c r="Y38" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>691424077.37794375</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>720233413.93535805</v>
       </c>
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.35">
@@ -4115,48 +4115,48 @@
         <v>0.12416576036893748</v>
       </c>
       <c r="O39" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>944.1099999999999</v>
       </c>
       <c r="P39" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.18119926455283425</v>
       </c>
       <c r="Q39" s="3">
-        <f>O39*10000000</f>
+        <f t="shared" si="11"/>
         <v>9441099999.9999981</v>
       </c>
       <c r="R39" s="3">
-        <f>Q39/B39</f>
+        <f t="shared" si="12"/>
         <v>13682753.623188403</v>
       </c>
       <c r="S39" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>1161898565.3217552</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1031592184.164175</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>1066930191.2223486</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>944995312.22550869</v>
       </c>
       <c r="U39" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>992821851.48181999</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>972138062.90928209</v>
       </c>
       <c r="V39" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1000852153.5947245</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1021488280.4729663</v>
       </c>
       <c r="W39" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1091983962.2143662</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>999268342.78107095</v>
       </c>
       <c r="X39" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1108772483.8177598</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1036907600.6073493</v>
       </c>
       <c r="Y39" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1121046813.9369886</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>1131826110.2248442</v>
       </c>
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.35">
@@ -4200,48 +4200,48 @@
         <v>6.4673316498821382E-2</v>
       </c>
       <c r="O40" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>5078</v>
       </c>
       <c r="P40" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>9.5978010083459145E-2</v>
       </c>
       <c r="Q40" s="3">
-        <f>O40*10000000</f>
+        <f t="shared" si="11"/>
         <v>50780000000</v>
       </c>
       <c r="R40" s="3">
-        <f>Q40/B40</f>
+        <f t="shared" si="12"/>
         <v>2954558.6780706346</v>
       </c>
       <c r="S40" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>5723749416.9802561</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5490126991.7973881</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>5902562031.8750734</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>6011868736.1690559</v>
       </c>
       <c r="U40" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5729377229.4800386</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5117501991.380229</v>
       </c>
       <c r="V40" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5938162393.5691509</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5771671859.1700153</v>
       </c>
       <c r="W40" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5485493290.2998667</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5263857197.7624979</v>
       </c>
       <c r="X40" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5301026996.9262848</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5411465059.3622494</v>
       </c>
       <c r="Y40" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>6203607122.9212933</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>6145629486.2584772</v>
       </c>
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.35">
@@ -4285,48 +4285,48 @@
         <v>0.17573897593280569</v>
       </c>
       <c r="O41" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>791.04000000000008</v>
       </c>
       <c r="P41" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.1209103840682788</v>
       </c>
       <c r="Q41" s="3">
-        <f>O41*10000000</f>
+        <f t="shared" si="11"/>
         <v>7910400000.000001</v>
       </c>
       <c r="R41" s="3">
-        <f>Q41/B41</f>
+        <f t="shared" si="12"/>
         <v>3472519.7541703251</v>
       </c>
       <c r="S41" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>827945361.0041188</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>864338563.6856184</v>
       </c>
       <c r="T41" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>868405817.95989001</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>842864470.37283444</v>
       </c>
       <c r="U41" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>901175301.44354022</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>892510154.31427538</v>
       </c>
       <c r="V41" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>838582461.34409249</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>855872821.37180579</v>
       </c>
       <c r="W41" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>776834940.80683291</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>794097939.49142921</v>
       </c>
       <c r="X41" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>834384572.29287946</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>929005503.17145348</v>
       </c>
       <c r="Y41" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>930258144.87842548</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>821878555.1838516</v>
       </c>
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.35">
@@ -4370,48 +4370,48 @@
         <v>7.7620430171238966E-3</v>
       </c>
       <c r="O42" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>96.179999999999993</v>
       </c>
       <c r="P42" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>1.3437275618012105E-2</v>
       </c>
       <c r="Q42" s="3">
-        <f>O42*10000000</f>
+        <f t="shared" si="11"/>
         <v>961799999.99999988</v>
       </c>
       <c r="R42" s="3">
-        <f>Q42/B42</f>
+        <f t="shared" si="12"/>
         <v>2368965.5172413792</v>
       </c>
       <c r="S42" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>103985902.73160157</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>119473164.84056351</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>107656986.7246463</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>99375680.053519666</v>
       </c>
       <c r="U42" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>113785264.8366839</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>100088890.36560157</v>
       </c>
       <c r="V42" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>110369650.63958414</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>100909394.87047693</v>
       </c>
       <c r="W42" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>95502328.850049824</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>108096042.54456188</v>
       </c>
       <c r="X42" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>106679514.59228894</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>115046535.34462534</v>
       </c>
       <c r="Y42" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>112008957.78090227</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>104322068.52142859</v>
       </c>
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.35">
@@ -4455,48 +4455,48 @@
         <v>0.24893607043624044</v>
       </c>
       <c r="O43" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>9803.34</v>
       </c>
       <c r="P43" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>4.1520295736902878E-2</v>
       </c>
       <c r="Q43" s="3">
-        <f>O43*10000000</f>
+        <f t="shared" si="11"/>
         <v>98033400000</v>
       </c>
       <c r="R43" s="3">
-        <f>Q43/B43</f>
+        <f t="shared" si="12"/>
         <v>14263553.033609778</v>
       </c>
       <c r="S43" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>12290297713.689014</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>11501012539.415407</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>10762132751.111078</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>11395199383.529379</v>
       </c>
       <c r="U43" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>10094374551.314024</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>10201761514.625875</v>
       </c>
       <c r="V43" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>10606811620.988924</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>11785346245.543249</v>
       </c>
       <c r="W43" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>9734267004.6667442</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>10803966675.509243</v>
       </c>
       <c r="X43" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11086730504.145586</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>11193333682.070063</v>
       </c>
       <c r="Y43" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>12312168827.535522</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>10073592677.074518</v>
       </c>
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.35">
@@ -4543,48 +4543,48 @@
         <v>115</v>
       </c>
       <c r="O44" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>328.12</v>
       </c>
       <c r="P44" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>-0.10597276526897667</v>
       </c>
       <c r="Q44" s="3">
-        <f>O44*10000000</f>
+        <f t="shared" si="11"/>
         <v>3281200000</v>
       </c>
       <c r="R44" s="3">
-        <f>Q44/B44</f>
+        <f t="shared" si="12"/>
         <v>5191772.1518987343</v>
       </c>
       <c r="S44" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>347202121.59768766</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>384941482.64091456</v>
       </c>
       <c r="T44" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>328427685.17167914</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>363742490.02884895</v>
       </c>
       <c r="U44" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>363020853.15722501</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>348643789.66584975</v>
       </c>
       <c r="V44" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>333496474.70625639</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>329910491.1072644</v>
       </c>
       <c r="W44" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>325808111.27342844</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>361611200.42435467</v>
       </c>
       <c r="X44" s="3">
-        <f t="shared" ca="1" si="7"/>
+        <f t="shared" ca="1" si="8"/>
         <v>342531110.32521719</v>
       </c>
       <c r="Y44" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>408344784.05997264</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>382120807.10199273</v>
       </c>
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.35">
@@ -4628,48 +4628,48 @@
         <v>0.22363983441270735</v>
       </c>
       <c r="O45" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3560.66</v>
       </c>
       <c r="P45" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.12470193759003328</v>
       </c>
       <c r="Q45" s="3">
-        <f>O45*10000000</f>
+        <f t="shared" si="11"/>
         <v>35606600000</v>
       </c>
       <c r="R45" s="3">
-        <f>Q45/B45</f>
+        <f t="shared" si="12"/>
         <v>34502519.379844964</v>
       </c>
       <c r="S45" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>4341084215.8267384</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4463945089.8595715</v>
       </c>
       <c r="T45" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>3908902027.4285269</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3640644045.1540198</v>
       </c>
       <c r="U45" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>3627362432.0992451</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3861385814.8153257</v>
       </c>
       <c r="V45" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>4124886158.5036216</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>3580089873.4182377</v>
       </c>
       <c r="W45" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>3613276956.510036</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4157211122.0061707</v>
       </c>
       <c r="X45" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>3794483493.1604548</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>3523448957.9347081</v>
       </c>
       <c r="Y45" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>3780778773.8604617</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>3902739379.4688635</v>
       </c>
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.35">
@@ -4713,48 +4713,48 @@
         <v>0.27445838403334316</v>
       </c>
       <c r="O46" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>3123.42</v>
       </c>
       <c r="P46" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.20083615634179042</v>
       </c>
       <c r="Q46" s="3">
-        <f>O46*10000000</f>
+        <f t="shared" si="11"/>
         <v>31234200000</v>
       </c>
       <c r="R46" s="3">
-        <f>Q46/B46</f>
+        <f t="shared" si="12"/>
         <v>2402630.769230769</v>
       </c>
       <c r="S46" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>3664311610.7225571</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3592462363.4534874</v>
       </c>
       <c r="T46" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>3630598720.2834268</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3025498933.5695224</v>
       </c>
       <c r="U46" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>3729360625.5906448</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3660931990.2587066</v>
       </c>
       <c r="V46" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>3174599411.8828945</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>3072192979.2415109</v>
       </c>
       <c r="W46" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>3578553241.2402544</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>3646716160.1210213</v>
       </c>
       <c r="X46" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>3362495159.9448814</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>3328530562.3696809</v>
       </c>
       <c r="Y46" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>3423492900.9286585</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>3887090897.9294147</v>
       </c>
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.35">
@@ -4798,48 +4798,48 @@
         <v>0.18912281878069631</v>
       </c>
       <c r="O47" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4619.6899999999996</v>
       </c>
       <c r="P47" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.12780744018849688</v>
       </c>
       <c r="Q47" s="3">
-        <f>O47*10000000</f>
+        <f t="shared" si="11"/>
         <v>46196899999.999992</v>
       </c>
       <c r="R47" s="3">
-        <f>Q47/B47</f>
+        <f t="shared" si="12"/>
         <v>3655396.4234847282</v>
       </c>
       <c r="S47" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>5100889396.1073246</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4835218073.3934021</v>
       </c>
       <c r="T47" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>5419552646.2018299</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4624021982.539175</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5566510277.0722933</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4908649971.6001129</v>
       </c>
       <c r="V47" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>4745874868.3657589</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>4644898807.3367004</v>
       </c>
       <c r="W47" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5544894861.9897137</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4738364700.2457542</v>
       </c>
       <c r="X47" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5525881980.3099623</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>4671882037.8984222</v>
       </c>
       <c r="Y47" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5801941298.6673479</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5590961615.0794449</v>
       </c>
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.35">
@@ -4883,48 +4883,48 @@
         <v>0.45887728459530025</v>
       </c>
       <c r="O48" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>217687</v>
       </c>
       <c r="P48" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.18437824329235622</v>
       </c>
       <c r="Q48" s="3">
-        <f>O48*10000000</f>
+        <f t="shared" si="11"/>
         <v>2176870000000</v>
       </c>
       <c r="R48" s="3">
-        <f>Q48/B48</f>
+        <f t="shared" si="12"/>
         <v>3418274.4926848956</v>
       </c>
       <c r="S48" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>262895791228.44647</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>275414638429.80109</v>
       </c>
       <c r="T48" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>257720691132.4209</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>217891129775.59219</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>214611257940.86792</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>245610661865.65994</v>
       </c>
       <c r="V48" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>254560999796.94519</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>221253953094.54114</v>
       </c>
       <c r="W48" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>232780376893.74979</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>223279137020.53549</v>
       </c>
       <c r="X48" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>224880700793.84473</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>231982196608.38718</v>
       </c>
       <c r="Y48" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>268425679708.46515</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>228658912344.24808</v>
       </c>
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.35">
@@ -4968,48 +4968,48 @@
         <v>0.15538256309047385</v>
       </c>
       <c r="O49" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>49600.800000000003</v>
       </c>
       <c r="P49" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>7.8947417287655308E-2</v>
       </c>
       <c r="Q49" s="3">
-        <f>O49*10000000</f>
+        <f t="shared" si="11"/>
         <v>496008000000</v>
       </c>
       <c r="R49" s="3">
-        <f>Q49/B49</f>
+        <f t="shared" si="12"/>
         <v>3351405.4054054054</v>
       </c>
       <c r="S49" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>51344393798.293327</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>53626366855.995247</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>55519574413.930519</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>53918048228.913292</v>
       </c>
       <c r="U49" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>57049977398.829361</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>54333311808.40892</v>
       </c>
       <c r="V49" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>53666030337.65506</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>52039786994.089752</v>
       </c>
       <c r="W49" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>50874989409.235184</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>49792542826.059967</v>
       </c>
       <c r="X49" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>50161176742.463692</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>57172954136.571526</v>
       </c>
       <c r="Y49" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>54932356159.264374</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>57763920909.74192</v>
       </c>
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.35">
@@ -5053,48 +5053,48 @@
         <v>0.15858091605910354</v>
       </c>
       <c r="O50" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>79862.399999999994</v>
       </c>
       <c r="P50" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0.14124420147573385</v>
       </c>
       <c r="Q50" s="3">
-        <f>O50*10000000</f>
+        <f t="shared" si="11"/>
         <v>798624000000</v>
       </c>
       <c r="R50" s="3">
-        <f>Q50/B50</f>
+        <f t="shared" si="12"/>
         <v>3412923.076923077</v>
       </c>
       <c r="S50" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>87262530476.949738</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>99203718858.006027</v>
       </c>
       <c r="T50" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>90251777550.789322</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>80796829426.420914</v>
       </c>
       <c r="U50" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>91856343345.596649</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>82233297852.248428</v>
       </c>
       <c r="V50" s="3">
-        <f t="shared" ca="1" si="5"/>
+        <f t="shared" ca="1" si="6"/>
         <v>81171001041.024414</v>
       </c>
       <c r="W50" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>90628229065.195847</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>81913976270.465469</v>
       </c>
       <c r="X50" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>89449036815.779175</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>85975287813.224655</v>
       </c>
       <c r="Y50" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>82975821608.913361</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>92094043763.738998</v>
       </c>
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.35">
@@ -5138,48 +5138,48 @@
         <v>5.012325390304026E-2</v>
       </c>
       <c r="O51" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>226.92999999999998</v>
       </c>
       <c r="P51" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>3.8758048119281602E-2</v>
       </c>
       <c r="Q51" s="3">
-        <f>O51*10000000</f>
+        <f t="shared" si="11"/>
         <v>2269300000</v>
       </c>
       <c r="R51" s="3">
-        <f>Q51/B51</f>
+        <f t="shared" si="12"/>
         <v>4141058.3941605841</v>
       </c>
       <c r="S51" s="3">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v>247957562.52171493</v>
       </c>
       <c r="T51" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>239354775.47582567</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>241797171.14394632</v>
       </c>
       <c r="U51" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>236152754.11380711</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>238638572.57816297</v>
       </c>
       <c r="V51" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>240568767.63857061</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>223208134.92238513</v>
       </c>
       <c r="W51" s="3">
-        <f t="shared" ca="1" si="6"/>
+        <f t="shared" ca="1" si="7"/>
         <v>240188076.63016862</v>
       </c>
       <c r="X51" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>224558444.78948376</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>264041248.26895344</v>
       </c>
       <c r="Y51" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>251322550.91091001</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>266868275.70952302</v>
       </c>
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.35">
@@ -5223,7 +5223,7 @@
         <v>0.15966778878049978</v>
       </c>
       <c r="O52" s="3">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>4791</v>
       </c>
       <c r="P52" s="4">
@@ -5231,40 +5231,40 @@
         <v>0.1194309660344067</v>
       </c>
       <c r="Q52" s="3">
-        <f>O52*10000000</f>
+        <f t="shared" si="11"/>
         <v>47910000000</v>
       </c>
       <c r="R52" s="3">
-        <f>Q52/B52</f>
+        <f t="shared" si="12"/>
         <v>4839393.9393939395</v>
       </c>
       <c r="S52" s="3">
-        <f t="shared" ca="1" si="2"/>
-        <v>5841089707.5334082</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5510461988.2390642</v>
       </c>
       <c r="T52" s="3">
-        <f t="shared" ca="1" si="3"/>
-        <v>5362701428.5483522</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5517394738.9872475</v>
       </c>
       <c r="U52" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>4880750594.6053495</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5300600108.1197882</v>
       </c>
       <c r="V52" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>4764783358.1376724</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>4974224384.8689985</v>
       </c>
       <c r="W52" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5123185057.894846</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4809520666.5951614</v>
       </c>
       <c r="X52" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4688833019.0787163</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5730795912.2073202</v>
       </c>
       <c r="Y52" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5634186352.2862759</v>
+        <f t="shared" ca="1" si="9"/>
+        <v>5798288867.4014101</v>
       </c>
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.35">

--- a/Excel Files/Dataset.xlsx
+++ b/Excel Files/Dataset.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Me\Code\Code\Python\Data_Project\Excel Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A1B18FB-D990-4AB8-8D1C-4FDD50DAC32E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF60F28B-D9BE-4240-BD4A-C5D5BFEB9904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13695" xr2:uid="{369E4836-92E2-44AD-8257-2B7A8DF32B0E}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="125">
   <si>
     <t>Company Name</t>
   </si>
@@ -387,12 +387,6 @@
   </si>
   <si>
     <t>Total Cost</t>
-  </si>
-  <si>
-    <t>LOSS</t>
-  </si>
-  <si>
-    <t>LOss</t>
   </si>
   <si>
     <t>Profit margin</t>
@@ -475,7 +469,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -805,7 +807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9A97D36-5AA9-4706-BACB-2B8DE34E5D88}">
-  <dimension ref="A1:AI69"/>
+  <dimension ref="A1:AH69"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="19.609375" bestFit="1" customWidth="1"/>
@@ -820,24 +822,25 @@
     <col min="11" max="11" width="22.0546875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="29.27734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.0546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.0546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.1640625" customWidth="1"/>
-    <col min="17" max="17" width="19.5" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="27" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.38671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.0546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.1640625" customWidth="1"/>
+    <col min="16" max="16" width="19.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="26" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="15.38671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
       <c r="D1" t="s">
         <v>59</v>
       </c>
@@ -868,62 +871,62 @@
       <c r="M1" t="s">
         <v>51</v>
       </c>
+      <c r="N1" t="s">
+        <v>114</v>
+      </c>
       <c r="O1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q1" t="s">
         <v>117</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>118</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
+        <v>123</v>
+      </c>
+      <c r="T1" t="s">
         <v>119</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>120</v>
       </c>
-      <c r="T1" t="s">
-        <v>125</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
+        <v>124</v>
+      </c>
+      <c r="W1" t="s">
         <v>121</v>
       </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>122</v>
       </c>
-      <c r="W1" t="s">
-        <v>126</v>
-      </c>
-      <c r="X1" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>124</v>
+      <c r="AB1">
+        <v>0.11501694819952127</v>
       </c>
       <c r="AC1">
-        <v>0.11501694819952127</v>
+        <v>0.10762771198698586</v>
       </c>
       <c r="AD1">
-        <v>0.10762771198698586</v>
+        <v>0.10954120056210569</v>
       </c>
       <c r="AE1">
-        <v>0.10954120056210569</v>
+        <v>0.10928878456028296</v>
       </c>
       <c r="AF1">
-        <v>0.10928878456028296</v>
+        <v>0.10911583917751494</v>
       </c>
       <c r="AG1">
-        <v>0.10911583917751494</v>
+        <v>0.10874169204013813</v>
       </c>
       <c r="AH1">
-        <v>0.10874169204013813</v>
-      </c>
-      <c r="AI1">
         <v>0.11417415648447385</v>
       </c>
     </row>
-    <row r="2" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>29</v>
       </c>
@@ -963,55 +966,52 @@
       <c r="M2" s="3">
         <v>-9.7149082985291454E-3</v>
       </c>
-      <c r="N2" t="s">
-        <v>115</v>
-      </c>
-      <c r="O2" s="3">
-        <f>E2-F2</f>
+      <c r="N2" s="3">
+        <f t="shared" ref="N2:N33" si="0">E2-F2</f>
         <v>300.51000000000005</v>
       </c>
-      <c r="P2" s="4">
-        <f>F2/E2</f>
+      <c r="O2" s="4">
+        <f t="shared" ref="O2:O33" si="1">F2/E2</f>
         <v>-0.12407421261315178</v>
       </c>
+      <c r="P2" s="3">
+        <f t="shared" ref="P2:P33" si="2">N2*10000000</f>
+        <v>3005100000.0000005</v>
+      </c>
       <c r="Q2" s="3">
-        <f t="shared" ref="Q2:Q33" si="0">O2*10000000</f>
-        <v>3005100000.0000005</v>
+        <f t="shared" ref="Q2:Q33" si="3">P2/B2</f>
+        <v>7121090.0473933658</v>
       </c>
       <c r="R2" s="3">
-        <f t="shared" ref="R2:R33" si="1">Q2/B2</f>
-        <v>7121090.0473933658</v>
+        <f ca="1">P2*$AB$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>352550179.65506905</v>
       </c>
       <c r="S2" s="3">
-        <f ca="1">Q2*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>324899185.17231846</v>
+        <f ca="1">P2*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>320197716.91917032</v>
       </c>
       <c r="T2" s="3">
-        <f ca="1">Q2*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>323432037.29209125</v>
+        <f ca="1">P2*(1 + RANDBETWEEN(-10,10)/100)*$AD$1</f>
+        <v>362100487.99010229</v>
       </c>
       <c r="U2" s="3">
-        <f ca="1">Q2*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>358808665.37201047</v>
+        <f ca="1">P2*$AE$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>295581353.83389574</v>
       </c>
       <c r="V2" s="3">
-        <f ca="1">Q2*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>357981861.86549598</v>
+        <f ca="1">P2*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>337741128.56172073</v>
       </c>
       <c r="W2" s="3">
-        <f ca="1">Q2*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>357415369.06046176</v>
+        <f ca="1">P2*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>330047455.33731735</v>
       </c>
       <c r="X2" s="3">
-        <f ca="1">Q2*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>320244065.57482278</v>
-      </c>
-      <c r="Y2" s="3">
-        <f ca="1">Q2*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>360259995.53406703</v>
-      </c>
-    </row>
-    <row r="3" spans="1:35" x14ac:dyDescent="0.35">
+        <f ca="1">P2*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>367122090.68709689</v>
+      </c>
+    </row>
+    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>42</v>
       </c>
@@ -1051,52 +1051,52 @@
       <c r="M3" s="3">
         <v>6.1343678062920966E-2</v>
       </c>
-      <c r="O3" s="3">
-        <f t="shared" ref="O3:O52" si="2">E3-F3</f>
+      <c r="N3" s="3">
+        <f t="shared" si="0"/>
         <v>90.45</v>
       </c>
-      <c r="P3" s="4">
-        <f t="shared" ref="P3:P51" si="3">F3/E3</f>
+      <c r="O3" s="4">
+        <f t="shared" si="1"/>
         <v>0.13725677222434185</v>
       </c>
+      <c r="P3" s="3">
+        <f t="shared" si="2"/>
+        <v>904500000</v>
+      </c>
       <c r="Q3" s="3">
-        <f t="shared" si="0"/>
-        <v>904500000</v>
+        <f t="shared" si="3"/>
+        <v>1612299.4652406417</v>
       </c>
       <c r="R3" s="3">
-        <f t="shared" si="1"/>
-        <v>1612299.4652406417</v>
+        <f t="shared" ref="R3:R52" ca="1" si="4">P3*$AB$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>110274799.42525502</v>
       </c>
       <c r="S3" s="3">
-        <f t="shared" ref="S3:S52" ca="1" si="4">Q3*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>94669874.978284955</v>
+        <f ca="1">P3*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>105137206.73160701</v>
       </c>
       <c r="T3" s="3">
-        <f ca="1">Q3*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>94428787.527461842</v>
+        <f t="shared" ref="T3:T52" ca="1" si="5">P3*(1 + RANDBETWEEN(-10,10)/100)*$AD$1</f>
+        <v>108988017.49926707</v>
       </c>
       <c r="U3" s="3">
-        <f t="shared" ref="U3:U52" ca="1" si="5">Q3*(1 + RANDBETWEEN(-10,10)/100)*$AE$1</f>
-        <v>95116815.272087604</v>
+        <f t="shared" ref="U3:U52" ca="1" si="6">P3*$AE$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>97863188.578428179</v>
       </c>
       <c r="V3" s="3">
-        <f t="shared" ref="V3:V52" ca="1" si="6">Q3*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>90943569.183993861</v>
+        <f t="shared" ref="V3:V52" ca="1" si="7">P3*$AF$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>105603945.89358662</v>
       </c>
       <c r="W3" s="3">
-        <f t="shared" ref="W3:W52" ca="1" si="7">Q3*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>104616993.128226</v>
+        <f t="shared" ref="W3:W52" ca="1" si="8">P3*$AG$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>102291134.86831714</v>
       </c>
       <c r="X3" s="3">
-        <f t="shared" ref="X3:X52" ca="1" si="8">Q3*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>106225409.28632934</v>
-      </c>
-      <c r="Y3" s="3">
-        <f t="shared" ref="Y3:Y52" ca="1" si="9">Q3*$AI$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <f t="shared" ref="X3:X52" ca="1" si="9">P3*$AH$1*(1 + RANDBETWEEN(-10,10)/100)</f>
         <v>102237819.29480453</v>
       </c>
     </row>
-    <row r="4" spans="1:35" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -1136,52 +1136,52 @@
       <c r="M4" s="3">
         <v>0.4646355517142034</v>
       </c>
-      <c r="O4" s="3">
+      <c r="N4" s="3">
+        <f t="shared" si="0"/>
+        <v>411.37</v>
+      </c>
+      <c r="O4" s="4">
+        <f t="shared" si="1"/>
+        <v>0.23875349284775813</v>
+      </c>
+      <c r="P4" s="3">
         <f t="shared" si="2"/>
-        <v>411.37</v>
-      </c>
-      <c r="P4" s="4">
+        <v>4113700000</v>
+      </c>
+      <c r="Q4" s="3">
         <f t="shared" si="3"/>
-        <v>0.23875349284775813</v>
-      </c>
-      <c r="Q4" s="3">
-        <f t="shared" si="0"/>
-        <v>4113700000</v>
+        <v>3201322.9571984434</v>
       </c>
       <c r="R4" s="3">
-        <f t="shared" si="1"/>
-        <v>3201322.9571984434</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>520459741.78920776</v>
       </c>
       <c r="S4" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>506265385.1949566</v>
+        <f t="shared" ref="S4:S52" ca="1" si="10">P4*$AC$1*(1 + RANDBETWEEN(-10,10)/100)</f>
+        <v>442748118.80086368</v>
       </c>
       <c r="T4" s="3">
-        <f t="shared" ref="T3:T52" ca="1" si="10">Q4*$AD$1*(1 + RANDBETWEEN(-10,10)/100)</f>
-        <v>469313005.9289155</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>482163011.32499754</v>
       </c>
       <c r="U4" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>446113440.38481081</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>449581273.045636</v>
       </c>
       <c r="V4" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>476556149.42837417</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>412960241.41457975</v>
       </c>
       <c r="W4" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>480290715.55826122</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>411544242.66187495</v>
       </c>
       <c r="X4" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>407070935.67641979</v>
-      </c>
-      <c r="Y4" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>502555703.45729274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.35">
+        <v>464981445.25487828</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -1221,52 +1221,52 @@
       <c r="M5" s="3">
         <v>0.12960298120456412</v>
       </c>
-      <c r="O5" s="3">
+      <c r="N5" s="3">
+        <f t="shared" si="0"/>
+        <v>1978.21</v>
+      </c>
+      <c r="O5" s="4">
+        <f t="shared" si="1"/>
+        <v>0.16180383715806246</v>
+      </c>
+      <c r="P5" s="3">
         <f t="shared" si="2"/>
-        <v>1978.21</v>
-      </c>
-      <c r="P5" s="4">
+        <v>19782100000</v>
+      </c>
+      <c r="Q5" s="3">
         <f t="shared" si="3"/>
-        <v>0.16180383715806246</v>
-      </c>
-      <c r="Q5" s="3">
-        <f t="shared" si="0"/>
-        <v>19782100000</v>
+        <v>32009870.550161812</v>
       </c>
       <c r="R5" s="3">
-        <f t="shared" si="1"/>
-        <v>32009870.550161812</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2047749093.8799748</v>
       </c>
       <c r="S5" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2366287841.8168597</v>
-      </c>
-      <c r="T5" s="3">
         <f t="shared" ca="1" si="10"/>
         <v>2150393182.9107304</v>
       </c>
+      <c r="T5" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>2275302732.8216124</v>
+      </c>
       <c r="U5" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2253633182.9852161</v>
-      </c>
-      <c r="V5" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>2378157831.5549712</v>
       </c>
+      <c r="V5" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>2244882059.881259</v>
+      </c>
       <c r="W5" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2374394486.4128704</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2000559294.279711</v>
       </c>
       <c r="X5" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2366252928.7179384</v>
-      </c>
-      <c r="Y5" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>2168260397.7518497</v>
-      </c>
-    </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.35">
+        <v>2461878993.280746</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -1306,52 +1306,52 @@
       <c r="M6" s="3">
         <v>0.15884454672076548</v>
       </c>
-      <c r="O6" s="3">
+      <c r="N6" s="3">
+        <f t="shared" si="0"/>
+        <v>271</v>
+      </c>
+      <c r="O6" s="4">
+        <f t="shared" si="1"/>
+        <v>8.8248157992127305E-2</v>
+      </c>
+      <c r="P6" s="3">
         <f t="shared" si="2"/>
-        <v>271</v>
-      </c>
-      <c r="P6" s="4">
+        <v>2710000000</v>
+      </c>
+      <c r="Q6" s="3">
         <f t="shared" si="3"/>
-        <v>8.8248157992127305E-2</v>
-      </c>
-      <c r="Q6" s="3">
-        <f t="shared" si="0"/>
-        <v>2710000000</v>
+        <v>1477644.4929116685</v>
       </c>
       <c r="R6" s="3">
-        <f t="shared" si="1"/>
-        <v>1477644.4929116685</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>336631603.99035883</v>
       </c>
       <c r="S6" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>342865522.58277291</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>320838209.43320489</v>
       </c>
       <c r="T6" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>280004255.50534242</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>317636619.26993787</v>
       </c>
       <c r="U6" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>314668052.73470479</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>266555345.54253012</v>
       </c>
       <c r="V6" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>287287427.97361577</v>
-      </c>
-      <c r="W6" s="3">
         <f t="shared" ca="1" si="7"/>
         <v>289789845.68764418</v>
       </c>
+      <c r="W6" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>271114786.59447241</v>
+      </c>
       <c r="X6" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>324158983.97165179</v>
-      </c>
-      <c r="Y6" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>340353160.48021656</v>
-      </c>
-    </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.35">
+        <v>321788442.63584113</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -1391,52 +1391,52 @@
       <c r="M7" s="3">
         <v>0.12384417865173024</v>
       </c>
-      <c r="O7" s="3">
+      <c r="N7" s="3">
+        <f t="shared" si="0"/>
+        <v>1006.9700000000001</v>
+      </c>
+      <c r="O7" s="4">
+        <f t="shared" si="1"/>
+        <v>0.15603365908443265</v>
+      </c>
+      <c r="P7" s="3">
         <f t="shared" si="2"/>
-        <v>1006.9700000000001</v>
-      </c>
-      <c r="P7" s="4">
+        <v>10069700000.000002</v>
+      </c>
+      <c r="Q7" s="3">
         <f t="shared" si="3"/>
-        <v>0.15603365908443265</v>
-      </c>
-      <c r="Q7" s="3">
-        <f t="shared" si="0"/>
-        <v>10069700000.000002</v>
+        <v>3356566.6666666674</v>
       </c>
       <c r="R7" s="3">
-        <f t="shared" si="1"/>
-        <v>3356566.6666666674</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1204513609.8161082</v>
       </c>
       <c r="S7" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1181349886.5504138</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1072940983.6813982</v>
       </c>
       <c r="T7" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>1192156648.5348868</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1147168908.3922453</v>
       </c>
       <c r="U7" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1213351730.0302596</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1133520432.103282</v>
       </c>
       <c r="V7" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1001459799.2368803</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1054813215.1351895</v>
       </c>
       <c r="W7" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1087776128.1081641</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>996446556.86628699</v>
       </c>
       <c r="X7" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1040246405.5197501</v>
-      </c>
-      <c r="Y7" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>1115208518.4451554</v>
-      </c>
-    </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.35">
+        <v>1207184478.7292919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1476,52 +1476,52 @@
       <c r="M8" s="3">
         <v>0.14856981855713969</v>
       </c>
-      <c r="O8" s="3">
+      <c r="N8" s="3">
+        <f t="shared" si="0"/>
+        <v>4966.9599999999991</v>
+      </c>
+      <c r="O8" s="4">
+        <f t="shared" si="1"/>
+        <v>9.4235300124732857E-2</v>
+      </c>
+      <c r="P8" s="3">
         <f t="shared" si="2"/>
-        <v>4966.9599999999991</v>
-      </c>
-      <c r="P8" s="4">
+        <v>49669599999.999992</v>
+      </c>
+      <c r="Q8" s="3">
         <f t="shared" si="3"/>
-        <v>9.4235300124732857E-2</v>
-      </c>
-      <c r="Q8" s="3">
-        <f t="shared" si="0"/>
-        <v>49669599999.999992</v>
+        <v>4139133.3333333326</v>
       </c>
       <c r="R8" s="3">
-        <f t="shared" si="1"/>
-        <v>4139133.3333333326</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5598588894.0851212</v>
       </c>
       <c r="S8" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>6284130391.320035</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5506200165.4080563</v>
       </c>
       <c r="T8" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>5880407943.6396713</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5386458939.2851677</v>
       </c>
       <c r="U8" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5604093643.902751</v>
-      </c>
-      <c r="V8" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>5211197005.0516119</v>
       </c>
+      <c r="V8" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>5419740085.611495</v>
+      </c>
       <c r="W8" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4986160878.7625761</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>4915052275.7307281</v>
       </c>
       <c r="X8" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5563191037.36555</v>
-      </c>
-      <c r="Y8" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>5500855142.4335852</v>
-      </c>
-    </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.35">
+        <v>5217305908.2875242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>58</v>
       </c>
@@ -1561,52 +1561,52 @@
       <c r="M9" s="3">
         <v>0.26989482563196882</v>
       </c>
-      <c r="O9" s="3">
+      <c r="N9" s="3">
+        <f t="shared" si="0"/>
+        <v>5693.92</v>
+      </c>
+      <c r="O9" s="4">
+        <f t="shared" si="1"/>
+        <v>3.4716123891704954E-2</v>
+      </c>
+      <c r="P9" s="3">
         <f t="shared" si="2"/>
-        <v>5693.92</v>
-      </c>
-      <c r="P9" s="4">
+        <v>56939200000</v>
+      </c>
+      <c r="Q9" s="3">
         <f t="shared" si="3"/>
-        <v>3.4716123891704954E-2</v>
-      </c>
-      <c r="Q9" s="3">
-        <f t="shared" si="0"/>
-        <v>56939200000</v>
+        <v>16571362.048894063</v>
       </c>
       <c r="R9" s="3">
-        <f t="shared" si="1"/>
-        <v>16571362.048894063</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5894075715.2299633</v>
       </c>
       <c r="S9" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>7138380588.445178</v>
-      </c>
-      <c r="T9" s="3">
         <f t="shared" ca="1" si="10"/>
         <v>6741059400.2063236</v>
       </c>
+      <c r="T9" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>6860907159.7504339</v>
+      </c>
       <c r="U9" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>6112444560.5049314</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>6596184919.5449562</v>
       </c>
       <c r="V9" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>6845097558.0183506</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>6088709218.2944307</v>
       </c>
       <c r="W9" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5778060788.7896128</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5758248404.8130045</v>
       </c>
       <c r="X9" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5572498456.2706499</v>
-      </c>
-      <c r="Y9" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>7021063941.3728142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.35">
+        <v>7086073792.6818209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>26</v>
       </c>
@@ -1646,52 +1646,52 @@
       <c r="M10" s="3">
         <v>0.18614209474669297</v>
       </c>
-      <c r="O10" s="3">
+      <c r="N10" s="3">
+        <f t="shared" si="0"/>
+        <v>368.50000000000006</v>
+      </c>
+      <c r="O10" s="4">
+        <f t="shared" si="1"/>
+        <v>0.28542341329093057</v>
+      </c>
+      <c r="P10" s="3">
         <f t="shared" si="2"/>
-        <v>368.50000000000006</v>
-      </c>
-      <c r="P10" s="4">
+        <v>3685000000.0000005</v>
+      </c>
+      <c r="Q10" s="3">
         <f t="shared" si="3"/>
-        <v>0.28542341329093057</v>
-      </c>
-      <c r="Q10" s="3">
-        <f t="shared" si="0"/>
-        <v>3685000000.0000005</v>
+        <v>3941176.4705882357</v>
       </c>
       <c r="R10" s="3">
-        <f t="shared" si="1"/>
-        <v>3941176.4705882357</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>415360705.03293121</v>
       </c>
       <c r="S10" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>381453708.70371234</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>368845550.36499989</v>
       </c>
       <c r="T10" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>432302849.35252678</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>407695917.31207311</v>
       </c>
       <c r="U10" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>439988663.23778188</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>410783754.5267356</v>
       </c>
       <c r="V10" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>362456253.99417847</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>394050030.02175975</v>
       </c>
       <c r="W10" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>410133704.71652544</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>404720266.51958817</v>
       </c>
       <c r="X10" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>360641821.65111816</v>
-      </c>
-      <c r="Y10" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>441768354.97755051</v>
-      </c>
-    </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.35">
+        <v>445975672.64400339</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>30</v>
       </c>
@@ -1731,52 +1731,52 @@
       <c r="M11" s="3">
         <v>0.15353986598038263</v>
       </c>
-      <c r="O11" s="3">
+      <c r="N11" s="3">
+        <f t="shared" si="0"/>
+        <v>377.11</v>
+      </c>
+      <c r="O11" s="4">
+        <f t="shared" si="1"/>
+        <v>0.14361303508572726</v>
+      </c>
+      <c r="P11" s="3">
         <f t="shared" si="2"/>
-        <v>377.11</v>
-      </c>
-      <c r="P11" s="4">
+        <v>3771100000</v>
+      </c>
+      <c r="Q11" s="3">
         <f t="shared" si="3"/>
-        <v>0.14361303508572726</v>
-      </c>
-      <c r="Q11" s="3">
-        <f t="shared" si="0"/>
-        <v>3771100000</v>
+        <v>1508440</v>
       </c>
       <c r="R11" s="3">
-        <f t="shared" si="1"/>
-        <v>1508440</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>399041180.28679752</v>
       </c>
       <c r="S11" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>477114454.69073617</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>422109859.26108724</v>
       </c>
       <c r="T11" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>369346126.85345131</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>417221729.6541543</v>
       </c>
       <c r="U11" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>392436280.36776894</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>395653378.0370717</v>
       </c>
       <c r="V11" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>436867271.58260006</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>448520547.82333606</v>
       </c>
       <c r="W11" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>423831343.35599643</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>430579584.59519321</v>
       </c>
       <c r="X11" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>426478826.64666754</v>
-      </c>
-      <c r="Y11" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>456395891.20971531</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.35">
+        <v>417645296.67304134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1816,52 +1816,52 @@
       <c r="M12" s="3">
         <v>0.1273043641835967</v>
       </c>
-      <c r="O12" s="3">
+      <c r="N12" s="3">
+        <f t="shared" si="0"/>
+        <v>11375.9</v>
+      </c>
+      <c r="O12" s="4">
+        <f t="shared" si="1"/>
+        <v>6.6631112569740733E-2</v>
+      </c>
+      <c r="P12" s="3">
         <f t="shared" si="2"/>
-        <v>11375.9</v>
-      </c>
-      <c r="P12" s="4">
+        <v>113759000000</v>
+      </c>
+      <c r="Q12" s="3">
         <f t="shared" si="3"/>
-        <v>6.6631112569740733E-2</v>
-      </c>
-      <c r="Q12" s="3">
-        <f t="shared" si="0"/>
-        <v>113759000000</v>
+        <v>325025.71428571426</v>
       </c>
       <c r="R12" s="3">
-        <f t="shared" si="1"/>
-        <v>325025.71428571426</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>12299160229.615578</v>
       </c>
       <c r="S12" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>14000107920.945395</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>12121184679.048248</v>
       </c>
       <c r="T12" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>12855801932.323902</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>13333588255.176701</v>
       </c>
       <c r="U12" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>13208975280.829256</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>12681234499.649096</v>
       </c>
       <c r="V12" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>12432582842.79323</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>12785296011.464771</v>
       </c>
       <c r="W12" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11916392399.035126</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>12370346144.794073</v>
       </c>
       <c r="X12" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>11504421914.658487</v>
-      </c>
-      <c r="Y12" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>12468804352.81657</v>
-      </c>
-    </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.35">
+        <v>12728571110.166916</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1901,52 +1901,52 @@
       <c r="M13" s="3">
         <v>0.11596195498634523</v>
       </c>
-      <c r="O13" s="3">
+      <c r="N13" s="3">
+        <f t="shared" si="0"/>
+        <v>6841.3</v>
+      </c>
+      <c r="O13" s="4">
+        <f t="shared" si="1"/>
+        <v>8.2566715837468163E-2</v>
+      </c>
+      <c r="P13" s="3">
         <f t="shared" si="2"/>
-        <v>6841.3</v>
-      </c>
-      <c r="P13" s="4">
+        <v>68413000000</v>
+      </c>
+      <c r="Q13" s="3">
         <f t="shared" si="3"/>
-        <v>8.2566715837468163E-2</v>
-      </c>
-      <c r="Q13" s="3">
-        <f t="shared" si="0"/>
-        <v>68413000000</v>
+        <v>5690650.4741307599</v>
       </c>
       <c r="R13" s="3">
-        <f t="shared" si="1"/>
-        <v>5690650.4741307599</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>7317848663.771678</v>
       </c>
       <c r="S13" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>8655519924.8912334</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>7068609273.759037</v>
       </c>
       <c r="T13" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>6626821194.1490974</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>7119340046.3525696</v>
       </c>
       <c r="U13" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>8168505947.9203167</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>7925380035.2099962</v>
       </c>
       <c r="V13" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>7327238145.7601852</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>6867746553.1992235</v>
       </c>
       <c r="W13" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>7763539581.8773832</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>7513738831.3173904</v>
       </c>
       <c r="X13" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>6918591201.1140318</v>
-      </c>
-      <c r="Y13" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>7186116842.1665249</v>
-      </c>
-    </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.35">
+        <v>8201546395.9509249</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -1986,52 +1986,52 @@
       <c r="M14" s="3">
         <v>0.12586295429908143</v>
       </c>
-      <c r="O14" s="3">
+      <c r="N14" s="3">
+        <f t="shared" si="0"/>
+        <v>2622.6000000000004</v>
+      </c>
+      <c r="O14" s="4">
+        <f t="shared" si="1"/>
+        <v>7.7588632526730442E-2</v>
+      </c>
+      <c r="P14" s="3">
         <f t="shared" si="2"/>
-        <v>2622.6000000000004</v>
-      </c>
-      <c r="P14" s="4">
+        <v>26226000000.000004</v>
+      </c>
+      <c r="Q14" s="3">
         <f t="shared" si="3"/>
-        <v>7.7588632526730442E-2</v>
-      </c>
-      <c r="Q14" s="3">
-        <f t="shared" si="0"/>
-        <v>26226000000.000004</v>
+        <v>4521724.1379310349</v>
       </c>
       <c r="R14" s="3">
-        <f t="shared" si="1"/>
-        <v>4521724.1379310349</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2865612759.306613</v>
       </c>
       <c r="S14" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2775119724.8021936</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2681512155.8421569</v>
       </c>
       <c r="T14" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>2907323705.8078122</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2987740626.9794555</v>
       </c>
       <c r="U14" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>3016468902.2388735</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2808883510.6004214</v>
       </c>
       <c r="V14" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2636911050.7677426</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2804438558.3041172</v>
       </c>
       <c r="W14" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2575504798.4425569</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2965934000.0624495</v>
       </c>
       <c r="X14" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2680748038.517983</v>
-      </c>
-      <c r="Y14" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>2754784913.7248669</v>
-      </c>
-    </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.35">
+        <v>2694898285.1656303</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>25</v>
       </c>
@@ -2071,52 +2071,52 @@
       <c r="M15" s="3">
         <v>0.11727571796923625</v>
       </c>
-      <c r="O15" s="3">
+      <c r="N15" s="3">
+        <f t="shared" si="0"/>
+        <v>1965.3999999999999</v>
+      </c>
+      <c r="O15" s="4">
+        <f t="shared" si="1"/>
+        <v>8.5885975275108606E-2</v>
+      </c>
+      <c r="P15" s="3">
         <f t="shared" si="2"/>
-        <v>1965.3999999999999</v>
-      </c>
-      <c r="P15" s="4">
+        <v>19654000000</v>
+      </c>
+      <c r="Q15" s="3">
         <f t="shared" si="3"/>
-        <v>8.5885975275108606E-2</v>
-      </c>
-      <c r="Q15" s="3">
-        <f t="shared" si="0"/>
-        <v>19654000000</v>
+        <v>3855237.3479796001</v>
       </c>
       <c r="R15" s="3">
-        <f t="shared" si="1"/>
-        <v>3855237.3479796001</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2373570254.909061</v>
       </c>
       <c r="S15" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2260543099.9133911</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2263387104.9896755</v>
       </c>
       <c r="T15" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>1903783546.2529981</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2066805845.6137202</v>
       </c>
       <c r="U15" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2002218162.9382913</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2062043300.8778892</v>
       </c>
       <c r="V15" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2212400624.9002352</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2208899584.2907248</v>
       </c>
       <c r="W15" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2144562703.1948786</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2265441768.2782874</v>
       </c>
       <c r="X15" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2073092938.8961685</v>
-      </c>
-      <c r="Y15" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>2042020773.1067226</v>
-      </c>
-    </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.35">
+        <v>2176659505.3994732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -2156,52 +2156,52 @@
       <c r="M16" s="3">
         <v>0.24965903380948962</v>
       </c>
-      <c r="O16" s="3">
+      <c r="N16" s="3">
+        <f t="shared" si="0"/>
+        <v>102150</v>
+      </c>
+      <c r="O16" s="4">
+        <f t="shared" si="1"/>
+        <v>0.14547431821984272</v>
+      </c>
+      <c r="P16" s="3">
         <f t="shared" si="2"/>
-        <v>102150</v>
-      </c>
-      <c r="P16" s="4">
+        <v>1021500000000</v>
+      </c>
+      <c r="Q16" s="3">
         <f t="shared" si="3"/>
-        <v>0.14547431821984272</v>
-      </c>
-      <c r="Q16" s="3">
-        <f t="shared" si="0"/>
-        <v>1021500000000</v>
+        <v>45119257.950530037</v>
       </c>
       <c r="R16" s="3">
-        <f t="shared" si="1"/>
-        <v>45119257.950530037</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>124539201340.95964</v>
       </c>
       <c r="S16" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>118664710711.66908</v>
-      </c>
-      <c r="T16" s="3">
         <f t="shared" ca="1" si="10"/>
         <v>104444622404.97075</v>
       </c>
+      <c r="T16" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>111896336374.19096</v>
+      </c>
       <c r="U16" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>119729079920.38434</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>113871263296.89563</v>
       </c>
       <c r="V16" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>111638493428.32904</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>113691066314.22815</v>
       </c>
       <c r="W16" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>117034921205.82309</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>106636452882.24106</v>
       </c>
       <c r="X16" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>109968842034.81108</v>
-      </c>
-      <c r="Y16" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>104966010764.00102</v>
-      </c>
-    </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+        <v>121294056882.84564</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2241,52 +2241,52 @@
       <c r="M17" s="3">
         <v>0.21678963868393555</v>
       </c>
-      <c r="O17" s="3">
+      <c r="N17" s="3">
+        <f t="shared" si="0"/>
+        <v>12338.4</v>
+      </c>
+      <c r="O17" s="4">
+        <f t="shared" si="1"/>
+        <v>9.9886194519828414E-2</v>
+      </c>
+      <c r="P17" s="3">
         <f t="shared" si="2"/>
-        <v>12338.4</v>
-      </c>
-      <c r="P17" s="4">
+        <v>123384000000</v>
+      </c>
+      <c r="Q17" s="3">
         <f t="shared" si="3"/>
-        <v>9.9886194519828414E-2</v>
-      </c>
-      <c r="Q17" s="3">
-        <f t="shared" si="0"/>
-        <v>123384000000</v>
+        <v>3650414.2011834318</v>
       </c>
       <c r="R17" s="3">
-        <f t="shared" si="1"/>
-        <v>3650414.2011834318</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>15468463738.94821</v>
       </c>
       <c r="S17" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>12772126022.98476</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>14209105248.908422</v>
       </c>
       <c r="T17" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>12084379230.38006</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>14732038324.268785</v>
       </c>
       <c r="U17" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>12569537285.844007</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>12945107898.418514</v>
       </c>
       <c r="V17" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>14023866889.953392</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>14270937623.143213</v>
       </c>
       <c r="W17" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>12924622753.035362</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>12209456286.919167</v>
       </c>
       <c r="X17" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>13953664327.907619</v>
-      </c>
-      <c r="Y17" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>14791627329.864338</v>
-      </c>
-    </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+        <v>13101155635.022697</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>33</v>
       </c>
@@ -2326,52 +2326,52 @@
       <c r="M18" s="3">
         <v>0.11428829425398067</v>
       </c>
-      <c r="O18" s="3">
+      <c r="N18" s="3">
+        <f t="shared" si="0"/>
+        <v>370.23</v>
+      </c>
+      <c r="O18" s="4">
+        <f t="shared" si="1"/>
+        <v>9.3018128368446834E-2</v>
+      </c>
+      <c r="P18" s="3">
         <f t="shared" si="2"/>
-        <v>370.23</v>
-      </c>
-      <c r="P18" s="4">
+        <v>3702300000</v>
+      </c>
+      <c r="Q18" s="3">
         <f t="shared" si="3"/>
-        <v>9.3018128368446834E-2</v>
-      </c>
-      <c r="Q18" s="3">
-        <f t="shared" si="0"/>
-        <v>3702300000</v>
+        <v>3098158.9958158997</v>
       </c>
       <c r="R18" s="3">
-        <f t="shared" si="1"/>
-        <v>3098158.9958158997</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>391761067.53356057</v>
       </c>
       <c r="S18" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>421568974.84589666</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>386515975.74673522</v>
       </c>
       <c r="T18" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>390500676.52762938</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>373110035.89379716</v>
       </c>
       <c r="U18" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>409609930.70949471</v>
-      </c>
-      <c r="V18" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>396527469.73598486</v>
       </c>
+      <c r="V18" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>412059162.81465179</v>
+      </c>
       <c r="W18" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>375701001.38982958</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>382464648.11819321</v>
       </c>
       <c r="X18" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>374412760.78938913</v>
-      </c>
-      <c r="Y18" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>426934049.34799218</v>
-      </c>
-    </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+        <v>405798700.37036884</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -2411,52 +2411,52 @@
       <c r="M19" s="3">
         <v>0.27878895405873633</v>
       </c>
-      <c r="O19" s="3">
+      <c r="N19" s="3">
+        <f t="shared" si="0"/>
+        <v>139877</v>
+      </c>
+      <c r="O19" s="4">
+        <f t="shared" si="1"/>
+        <v>0.16035176181043279</v>
+      </c>
+      <c r="P19" s="3">
         <f t="shared" si="2"/>
-        <v>139877</v>
-      </c>
-      <c r="P19" s="4">
+        <v>1398770000000</v>
+      </c>
+      <c r="Q19" s="3">
         <f t="shared" si="3"/>
-        <v>0.16035176181043279</v>
-      </c>
-      <c r="Q19" s="3">
-        <f t="shared" si="0"/>
-        <v>1398770000000</v>
+        <v>4150652.8189910981</v>
       </c>
       <c r="R19" s="3">
-        <f t="shared" si="1"/>
-        <v>4150652.8189910981</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>149620498668.73126</v>
       </c>
       <c r="S19" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>175361659730.01837</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>155062807136.9173</v>
       </c>
       <c r="T19" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>138502701520.3533</v>
-      </c>
-      <c r="U19" s="3">
         <f t="shared" ca="1" si="5"/>
         <v>167013010170.17966</v>
       </c>
+      <c r="U19" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>157455969374.76862</v>
+      </c>
       <c r="V19" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>155927270642.97473</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>143470284624.35263</v>
       </c>
       <c r="W19" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>160259360484.64923</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>150583570409.23416</v>
       </c>
       <c r="X19" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>136894154917.48561</v>
-      </c>
-      <c r="Y19" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>158106351017.12961</v>
-      </c>
-    </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+        <v>150121181773.84021</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>20</v>
       </c>
@@ -2496,52 +2496,52 @@
       <c r="M20" s="3">
         <v>0.11945050684892169</v>
       </c>
-      <c r="O20" s="3">
+      <c r="N20" s="3">
+        <f t="shared" si="0"/>
+        <v>2244.2600000000002</v>
+      </c>
+      <c r="O20" s="4">
+        <f t="shared" si="1"/>
+        <v>0.12912926896466084</v>
+      </c>
+      <c r="P20" s="3">
         <f t="shared" si="2"/>
-        <v>2244.2600000000002</v>
-      </c>
-      <c r="P20" s="4">
+        <v>22442600000.000004</v>
+      </c>
+      <c r="Q20" s="3">
         <f t="shared" si="3"/>
-        <v>0.12912926896466084</v>
-      </c>
-      <c r="Q20" s="3">
-        <f t="shared" si="0"/>
-        <v>22442600000.000004</v>
+        <v>3803830.5084745768</v>
       </c>
       <c r="R20" s="3">
-        <f t="shared" si="1"/>
-        <v>3803830.5084745768</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2787781710.595583</v>
       </c>
       <c r="S20" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2736156123.3623314</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2487909059.7103033</v>
       </c>
       <c r="T20" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>2367136775.2583466</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2556724921.6445179</v>
       </c>
       <c r="U20" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2605892708.5992203</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2330088252.5539765</v>
       </c>
       <c r="V20" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2256506518.2627983</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2375377838.3555384</v>
       </c>
       <c r="W20" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2620262151.5880685</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2464850760.7578044</v>
       </c>
       <c r="X20" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2416041834.8022046</v>
-      </c>
-      <c r="Y20" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>2382999379.6161613</v>
-      </c>
-    </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2536741275.0752687</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -2581,52 +2581,52 @@
       <c r="M21" s="3">
         <v>0.2715889343964597</v>
       </c>
-      <c r="O21" s="3">
+      <c r="N21" s="3">
+        <f t="shared" si="0"/>
+        <v>2216.9299999999998</v>
+      </c>
+      <c r="O21" s="4">
+        <f t="shared" si="1"/>
+        <v>0.17982308480608514</v>
+      </c>
+      <c r="P21" s="3">
         <f t="shared" si="2"/>
-        <v>2216.9299999999998</v>
-      </c>
-      <c r="P21" s="4">
+        <v>22169300000</v>
+      </c>
+      <c r="Q21" s="3">
         <f t="shared" si="3"/>
-        <v>0.17982308480608514</v>
-      </c>
-      <c r="Q21" s="3">
-        <f t="shared" si="0"/>
-        <v>22169300000</v>
+        <v>2944130.1460823375</v>
       </c>
       <c r="R21" s="3">
-        <f t="shared" si="1"/>
-        <v>2944130.1460823375</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>2728334395.8000226</v>
       </c>
       <c r="S21" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>2626340586.6112366</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>2481472276.7672091</v>
       </c>
       <c r="T21" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>2266729483.5854311</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>2622727876.6312089</v>
       </c>
       <c r="U21" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>2428451737.6214895</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>2325941617.4901896</v>
       </c>
       <c r="V21" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>2374398734.5212355</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>2491592426.6824245</v>
       </c>
       <c r="W21" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>2612543515.356329</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>2507156281.0792518</v>
       </c>
       <c r="X21" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>2193761745.944345</v>
-      </c>
-      <c r="Y21" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>2505849516.0777335</v>
-      </c>
-    </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+        <v>2303356625.8896337</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>43</v>
       </c>
@@ -2666,52 +2666,52 @@
       <c r="M22" s="3">
         <v>0.17214955740520543</v>
       </c>
-      <c r="O22" s="3">
+      <c r="N22" s="3">
+        <f t="shared" si="0"/>
+        <v>115.47999999999999</v>
+      </c>
+      <c r="O22" s="4">
+        <f t="shared" si="1"/>
+        <v>0.10139288771301845</v>
+      </c>
+      <c r="P22" s="3">
         <f t="shared" si="2"/>
-        <v>115.47999999999999</v>
-      </c>
-      <c r="P22" s="4">
+        <v>1154800000</v>
+      </c>
+      <c r="Q22" s="3">
         <f t="shared" si="3"/>
-        <v>0.10139288771301845</v>
-      </c>
-      <c r="Q22" s="3">
-        <f t="shared" si="0"/>
-        <v>1154800000</v>
+        <v>2295825.0497017894</v>
       </c>
       <c r="R22" s="3">
-        <f t="shared" si="1"/>
-        <v>2295825.0497017894</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>122195846.0383426</v>
       </c>
       <c r="S22" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>140790866.0876556</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>118074057.7124427</v>
       </c>
       <c r="T22" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>136717329.98282841</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>129028141.97730204</v>
       </c>
       <c r="U22" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>121438251.27275486</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>135041156.59892982</v>
       </c>
       <c r="V22" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>131254955.94662336</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>117186483.10644065</v>
       </c>
       <c r="W22" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>114666343.68479678</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>131853651.26634909</v>
       </c>
       <c r="X22" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>114273164.43083587</v>
-      </c>
-      <c r="Y22" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>126574383.27193958</v>
-      </c>
-    </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+        <v>139759214.86276662</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>16</v>
       </c>
@@ -2751,52 +2751,52 @@
       <c r="M23" s="3">
         <v>0.28830833470688427</v>
       </c>
-      <c r="O23" s="3">
+      <c r="N23" s="3">
+        <f t="shared" si="0"/>
+        <v>5172.87</v>
+      </c>
+      <c r="O23" s="4">
+        <f t="shared" si="1"/>
+        <v>0.1396431084063621</v>
+      </c>
+      <c r="P23" s="3">
         <f t="shared" si="2"/>
-        <v>5172.87</v>
-      </c>
-      <c r="P23" s="4">
+        <v>51728700000</v>
+      </c>
+      <c r="Q23" s="3">
         <f t="shared" si="3"/>
-        <v>0.1396431084063621</v>
-      </c>
-      <c r="Q23" s="3">
-        <f t="shared" si="0"/>
-        <v>51728700000</v>
+        <v>3694907.1428571427</v>
       </c>
       <c r="R23" s="3">
-        <f t="shared" si="1"/>
-        <v>3694907.1428571427</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>6306657840.8282909</v>
       </c>
       <c r="S23" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5473703031.6622906</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5790139290.0636435</v>
       </c>
       <c r="T23" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>5122046295.0563002</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5949745096.5928459</v>
       </c>
       <c r="U23" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5836416618.5625067</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5201097409.892828</v>
       </c>
       <c r="V23" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5936035087.3776846</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5644420510.0619173</v>
       </c>
       <c r="W23" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>6208862561.0681095</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5175061055.8337584</v>
       </c>
       <c r="X23" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5118810392.1833916</v>
-      </c>
-      <c r="Y23" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>5492655040.3407145</v>
-      </c>
-    </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+        <v>6319506336.7360907</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -2836,52 +2836,52 @@
       <c r="M24" s="3">
         <v>1.6531791907514453</v>
       </c>
-      <c r="O24" s="3">
+      <c r="N24" s="3">
+        <f t="shared" si="0"/>
+        <v>103.56</v>
+      </c>
+      <c r="O24" s="4">
+        <f t="shared" si="1"/>
+        <v>0.24891209747606616</v>
+      </c>
+      <c r="P24" s="3">
         <f t="shared" si="2"/>
-        <v>103.56</v>
-      </c>
-      <c r="P24" s="4">
+        <v>1035600000</v>
+      </c>
+      <c r="Q24" s="3">
         <f t="shared" si="3"/>
-        <v>0.24891209747606616</v>
-      </c>
-      <c r="Q24" s="3">
-        <f t="shared" si="0"/>
-        <v>1035600000</v>
+        <v>1603095.9752321981</v>
       </c>
       <c r="R24" s="3">
-        <f t="shared" si="1"/>
-        <v>1603095.9752321981</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>127449360.16430393</v>
       </c>
       <c r="S24" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>110773742.94654453</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>105886295.60703641</v>
       </c>
       <c r="T24" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>117032221.46040869</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>116844093.32118015</v>
       </c>
       <c r="U24" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>112306458.62909548</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>105256902.72028498</v>
       </c>
       <c r="V24" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>115443054.59644161</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>118650381.2048462</v>
       </c>
       <c r="W24" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>105090337.63857806</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>102477735.61185801</v>
       </c>
       <c r="X24" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>114865154.20230238</v>
-      </c>
-      <c r="Y24" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>124150694.27808718</v>
-      </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+        <v>120603531.58442754</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>52</v>
       </c>
@@ -2921,52 +2921,52 @@
       <c r="M25" s="3">
         <v>0.20833881578947369</v>
       </c>
-      <c r="O25" s="3">
+      <c r="N25" s="3">
+        <f t="shared" si="0"/>
+        <v>9613.4</v>
+      </c>
+      <c r="O25" s="4">
+        <f t="shared" si="1"/>
+        <v>0.11642356228343489</v>
+      </c>
+      <c r="P25" s="3">
         <f t="shared" si="2"/>
-        <v>9613.4</v>
-      </c>
-      <c r="P25" s="4">
+        <v>96134000000</v>
+      </c>
+      <c r="Q25" s="3">
         <f t="shared" si="3"/>
-        <v>0.11642356228343489</v>
-      </c>
-      <c r="Q25" s="3">
-        <f t="shared" si="0"/>
-        <v>96134000000</v>
+        <v>5198961.6570223356</v>
       </c>
       <c r="R25" s="3">
-        <f t="shared" si="1"/>
-        <v>5198961.6570223356</v>
-      </c>
-      <c r="S25" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>10725328119.266394</v>
       </c>
+      <c r="S25" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>9518947867.0243473</v>
+      </c>
       <c r="T25" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>9725881516.3074837</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>10951859125.830967</v>
       </c>
       <c r="U25" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>11057165463.579342</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>9665858573.7247829</v>
       </c>
       <c r="V25" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>10611431695.067425</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>9860357558.4817467</v>
       </c>
       <c r="W25" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11433818871.00543</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>9722009655.0055733</v>
       </c>
       <c r="X25" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>10453773822.586639</v>
-      </c>
-      <c r="Y25" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>10317457257.909704</v>
-      </c>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+        <v>12073620195.42625</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>24</v>
       </c>
@@ -3006,52 +3006,52 @@
       <c r="M26" s="3">
         <v>0.11611845175397661</v>
       </c>
-      <c r="O26" s="3">
+      <c r="N26" s="3">
+        <f t="shared" si="0"/>
+        <v>742.59999999999991</v>
+      </c>
+      <c r="O26" s="4">
+        <f t="shared" si="1"/>
+        <v>0.18999105565130131</v>
+      </c>
+      <c r="P26" s="3">
         <f t="shared" si="2"/>
-        <v>742.59999999999991</v>
-      </c>
-      <c r="P26" s="4">
+        <v>7425999999.999999</v>
+      </c>
+      <c r="Q26" s="3">
         <f t="shared" si="3"/>
-        <v>0.18999105565130131</v>
-      </c>
-      <c r="Q26" s="3">
-        <f t="shared" si="0"/>
-        <v>7425999999.999999</v>
+        <v>6336177.4744027294</v>
       </c>
       <c r="R26" s="3">
-        <f t="shared" si="1"/>
-        <v>6336177.4744027294</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>888280491.62283063</v>
       </c>
       <c r="S26" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>854115857.3296448</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>847197992.56827831</v>
       </c>
       <c r="T26" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>783258521.4310497</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>797183896.26671278</v>
       </c>
       <c r="U26" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>780914837.1592288</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>738536447.87164176</v>
       </c>
       <c r="V26" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>884620580.41768074</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>745470683.99364781</v>
       </c>
       <c r="W26" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>785985395.08025908</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>831741279.24276757</v>
       </c>
       <c r="X26" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>726764224.5810591</v>
-      </c>
-      <c r="Y26" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>924164441.79853606</v>
-      </c>
-    </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+        <v>898728723.21692491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>6</v>
       </c>
@@ -3091,52 +3091,52 @@
       <c r="M27" s="3">
         <v>0.20260107585149548</v>
       </c>
-      <c r="O27" s="3">
+      <c r="N27" s="3">
+        <f t="shared" si="0"/>
+        <v>34399.1</v>
+      </c>
+      <c r="O27" s="4">
+        <f t="shared" si="1"/>
+        <v>0.11792203662770721</v>
+      </c>
+      <c r="P27" s="3">
         <f t="shared" si="2"/>
-        <v>34399.1</v>
-      </c>
-      <c r="P27" s="4">
+        <v>343991000000</v>
+      </c>
+      <c r="Q27" s="3">
         <f t="shared" si="3"/>
-        <v>0.11792203662770721</v>
-      </c>
-      <c r="Q27" s="3">
-        <f t="shared" si="0"/>
-        <v>343991000000</v>
+        <v>3822122.222222222</v>
       </c>
       <c r="R27" s="3">
-        <f t="shared" si="1"/>
-        <v>3822122.222222222</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>40751738878.944572</v>
       </c>
       <c r="S27" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>37190907326.415428</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>37022964274.11525</v>
       </c>
       <c r="T27" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>38133653202.338707</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>39565246478.687263</v>
       </c>
       <c r="U27" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>40318870221.138451</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>38346245455.469818</v>
       </c>
       <c r="V27" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>34586809626.50219</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>39036261299.893044</v>
       </c>
       <c r="W27" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>34156728637.406414</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>38902409922.04232</v>
       </c>
       <c r="X27" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>36283978484.981781</v>
-      </c>
-      <c r="Y27" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>37311138150.088104</v>
-      </c>
-    </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+        <v>41238626376.413177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -3176,52 +3176,52 @@
       <c r="M28" s="3">
         <v>0.19844628674126036</v>
       </c>
-      <c r="O28" s="3">
+      <c r="N28" s="3">
+        <f t="shared" si="0"/>
+        <v>501.47000000000008</v>
+      </c>
+      <c r="O28" s="4">
+        <f t="shared" si="1"/>
+        <v>0.16997153072033896</v>
+      </c>
+      <c r="P28" s="3">
         <f t="shared" si="2"/>
-        <v>501.47000000000008</v>
-      </c>
-      <c r="P28" s="4">
+        <v>5014700000.000001</v>
+      </c>
+      <c r="Q28" s="3">
         <f t="shared" si="3"/>
-        <v>0.16997153072033896</v>
-      </c>
-      <c r="Q28" s="3">
-        <f t="shared" si="0"/>
-        <v>5014700000.000001</v>
+        <v>15970382.165605098</v>
       </c>
       <c r="R28" s="3">
-        <f t="shared" si="1"/>
-        <v>15970382.165605098</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>559472225.43205523</v>
       </c>
       <c r="S28" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>628685284.24839199</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>507337446.06306976</v>
       </c>
       <c r="T28" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>566706721.66619492</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>538329933.28961563</v>
       </c>
       <c r="U28" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>494384632.61291236</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>580933496.01051819</v>
       </c>
       <c r="V28" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>515167439.85838401</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>569070526.67242372</v>
       </c>
       <c r="W28" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>552655030.71071911</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>507135475.65852308</v>
       </c>
       <c r="X28" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>539853893.44294393</v>
-      </c>
-      <c r="Y28" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>612627582.4992795</v>
-      </c>
-    </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+        <v>578274633.94791806</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>40</v>
       </c>
@@ -3261,52 +3261,52 @@
       <c r="M29" s="3">
         <v>0.11035438069952673</v>
       </c>
-      <c r="O29" s="3">
+      <c r="N29" s="3">
+        <f t="shared" si="0"/>
+        <v>401.55</v>
+      </c>
+      <c r="O29" s="4">
+        <f t="shared" si="1"/>
+        <v>6.6662017990377243E-2</v>
+      </c>
+      <c r="P29" s="3">
         <f t="shared" si="2"/>
-        <v>401.55</v>
-      </c>
-      <c r="P29" s="4">
+        <v>4015500000</v>
+      </c>
+      <c r="Q29" s="3">
         <f t="shared" si="3"/>
-        <v>6.6662017990377243E-2</v>
-      </c>
-      <c r="Q29" s="3">
-        <f t="shared" si="0"/>
-        <v>4015500000</v>
+        <v>5853498.5422740523</v>
       </c>
       <c r="R29" s="3">
-        <f t="shared" si="1"/>
-        <v>5853498.5422740523</v>
-      </c>
-      <c r="S29" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>498798599.93479186</v>
       </c>
+      <c r="S29" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>393282960.51020497</v>
+      </c>
       <c r="T29" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>471075194.45727849</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>413470929.40570724</v>
       </c>
       <c r="U29" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>435464063.94856405</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>399352694.10565281</v>
       </c>
       <c r="V29" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>394964202.96163464</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>416246919.60644567</v>
       </c>
       <c r="W29" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>407483826.56209946</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>480317490.82589215</v>
       </c>
       <c r="X29" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>392987037.94845718</v>
-      </c>
-      <c r="Y29" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>435543009.09523451</v>
-      </c>
-    </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+        <v>426373682.58796638</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>7</v>
       </c>
@@ -3346,52 +3346,52 @@
       <c r="M30" s="3">
         <v>0.17678344977716942</v>
       </c>
-      <c r="O30" s="3">
+      <c r="N30" s="3">
+        <f t="shared" si="0"/>
+        <v>12782.85</v>
+      </c>
+      <c r="O30" s="4">
+        <f t="shared" si="1"/>
+        <v>0.11751060925827357</v>
+      </c>
+      <c r="P30" s="3">
         <f t="shared" si="2"/>
-        <v>12782.85</v>
-      </c>
-      <c r="P30" s="4">
+        <v>127828500000</v>
+      </c>
+      <c r="Q30" s="3">
         <f t="shared" si="3"/>
-        <v>0.11751060925827357</v>
-      </c>
-      <c r="Q30" s="3">
-        <f t="shared" si="0"/>
-        <v>127828500000</v>
+        <v>4260950</v>
       </c>
       <c r="R30" s="3">
-        <f t="shared" si="1"/>
-        <v>4260950</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>13673272885.517929</v>
       </c>
       <c r="S30" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>15290541721.439405</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>13207573422.459286</v>
       </c>
       <c r="T30" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>13895467871.545706</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>13582412735.371532</v>
       </c>
       <c r="U30" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>15262711218.097908</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>12573199257.447716</v>
       </c>
       <c r="V30" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>12852603685.390999</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>12832264924.438732</v>
       </c>
       <c r="W30" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>13948114048.302969</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>14873307497.619493</v>
       </c>
       <c r="X30" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>14456298876.190908</v>
-      </c>
-      <c r="Y30" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>14740658273.797321</v>
-      </c>
-    </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+        <v>15908235166.771368</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>57</v>
       </c>
@@ -3431,52 +3431,52 @@
       <c r="M31" s="3">
         <v>0.2158655931212641</v>
       </c>
-      <c r="O31" s="3">
+      <c r="N31" s="3">
+        <f t="shared" si="0"/>
+        <v>1043.93</v>
+      </c>
+      <c r="O31" s="4">
+        <f t="shared" si="1"/>
+        <v>9.8825113733479505E-2</v>
+      </c>
+      <c r="P31" s="3">
         <f t="shared" si="2"/>
-        <v>1043.93</v>
-      </c>
-      <c r="P31" s="4">
+        <v>10439300000</v>
+      </c>
+      <c r="Q31" s="3">
         <f t="shared" si="3"/>
-        <v>9.8825113733479505E-2</v>
-      </c>
-      <c r="Q31" s="3">
-        <f t="shared" si="0"/>
-        <v>10439300000</v>
+        <v>21348261.758691207</v>
       </c>
       <c r="R31" s="3">
-        <f t="shared" si="1"/>
-        <v>21348261.758691207</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1224710355.8860478</v>
       </c>
       <c r="S31" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1200696427.3392625</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1089851234.5333691</v>
       </c>
       <c r="T31" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>1011202176.3711673</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1052050778.6257507</v>
       </c>
       <c r="U31" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1177839458.6788297</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1038217551.8807474</v>
       </c>
       <c r="V31" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1163716376.8333652</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1127702050.1265736</v>
       </c>
       <c r="W31" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1241611348.1191568</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1021668431.1431526</v>
       </c>
       <c r="X31" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1067075916.971737</v>
-      </c>
-      <c r="Y31" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>1299169116.249321</v>
-      </c>
-    </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1239574202.6599026</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>22</v>
       </c>
@@ -3516,52 +3516,52 @@
       <c r="M32" s="3">
         <v>0.20788298833444338</v>
       </c>
-      <c r="O32" s="3">
+      <c r="N32" s="3">
+        <f t="shared" si="0"/>
+        <v>1235.22</v>
+      </c>
+      <c r="O32" s="4">
+        <f t="shared" si="1"/>
+        <v>0.20332030494175923</v>
+      </c>
+      <c r="P32" s="3">
         <f t="shared" si="2"/>
-        <v>1235.22</v>
-      </c>
-      <c r="P32" s="4">
+        <v>12352200000</v>
+      </c>
+      <c r="Q32" s="3">
         <f t="shared" si="3"/>
-        <v>0.20332030494175923</v>
-      </c>
-      <c r="Q32" s="3">
-        <f t="shared" si="0"/>
-        <v>12352200000</v>
+        <v>2771415.7505048239</v>
       </c>
       <c r="R32" s="3">
-        <f t="shared" si="1"/>
-        <v>2771415.7505048239</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1307055359.7461164</v>
       </c>
       <c r="S32" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1562783582.3051393</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1196495121.605082</v>
       </c>
       <c r="T32" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>1302850243.5255337</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1339544069.4074094</v>
       </c>
       <c r="U32" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>1488382299.3415663</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1214961232.1809745</v>
       </c>
       <c r="V32" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1322957786.1526165</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1253473221.8803048</v>
       </c>
       <c r="W32" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>1442168115.496695</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1410359084.8391042</v>
       </c>
       <c r="X32" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1208879215.576375</v>
-      </c>
-      <c r="Y32" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>1480817116.5138938</v>
-      </c>
-    </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1537229197.1429946</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>39</v>
       </c>
@@ -3601,52 +3601,52 @@
       <c r="M33" s="3">
         <v>0.42901385493072536</v>
       </c>
-      <c r="O33" s="3">
+      <c r="N33" s="3">
+        <f t="shared" si="0"/>
+        <v>117.94000000000003</v>
+      </c>
+      <c r="O33" s="4">
+        <f t="shared" si="1"/>
+        <v>0.18244835713295438</v>
+      </c>
+      <c r="P33" s="3">
         <f t="shared" si="2"/>
-        <v>117.94000000000003</v>
-      </c>
-      <c r="P33" s="4">
+        <v>1179400000.0000002</v>
+      </c>
+      <c r="Q33" s="3">
         <f t="shared" si="3"/>
-        <v>0.18244835713295438</v>
-      </c>
-      <c r="Q33" s="3">
-        <f t="shared" si="0"/>
-        <v>1179400000.0000002</v>
+        <v>2620888.8888888895</v>
       </c>
       <c r="R33" s="3">
-        <f t="shared" si="1"/>
-        <v>2620888.8888888895</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>141077028.25477603</v>
       </c>
       <c r="S33" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>147859577.6901018</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>125666762.28227663</v>
       </c>
       <c r="T33" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>121858678.57675308</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>116273602.74865273</v>
       </c>
       <c r="U33" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>131776749.78180642</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>134051000.21081366</v>
       </c>
       <c r="V33" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>119872529.03466989</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>123543571.89692269</v>
       </c>
       <c r="W33" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>117109010.86062466</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>139792447.23543143</v>
       </c>
       <c r="X33" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>115424956.43292505</v>
-      </c>
-      <c r="Y33" s="3">
         <f t="shared" ca="1" si="9"/>
         <v>148122700.17356735</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>31</v>
       </c>
@@ -3686,52 +3686,52 @@
       <c r="M34" s="3">
         <v>0.20019159440937337</v>
       </c>
-      <c r="O34" s="3">
-        <f t="shared" si="2"/>
+      <c r="N34" s="3">
+        <f t="shared" ref="N34:N52" si="11">E34-F34</f>
         <v>735.51</v>
       </c>
-      <c r="P34" s="4">
-        <f t="shared" si="3"/>
+      <c r="O34" s="4">
+        <f t="shared" ref="O34:O52" si="12">F34/E34</f>
         <v>0.18141144784142638</v>
       </c>
+      <c r="P34" s="3">
+        <f t="shared" ref="P34:P52" si="13">N34*10000000</f>
+        <v>7355100000</v>
+      </c>
       <c r="Q34" s="3">
-        <f t="shared" ref="Q34:Q52" si="11">O34*10000000</f>
-        <v>7355100000</v>
+        <f t="shared" ref="Q34:Q65" si="14">P34/B34</f>
+        <v>3937419.7002141327</v>
       </c>
       <c r="R34" s="3">
-        <f t="shared" ref="R34:R65" si="12">Q34/B34</f>
-        <v>3937419.7002141327</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>896718825.04443681</v>
       </c>
       <c r="S34" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>905178436.60145986</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>752031955.21370566</v>
       </c>
       <c r="T34" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>870773842.87902772</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>789572754.56925666</v>
       </c>
       <c r="U34" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>749288430.35653949</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>811868238.71253061</v>
       </c>
       <c r="V34" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>868136334.46488428</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>762430013.29781306</v>
       </c>
       <c r="W34" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>866762541.43330336</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>759815718.16819894</v>
       </c>
       <c r="X34" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>847794380.27188516</v>
-      </c>
-      <c r="Y34" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>915340948.81125951</v>
-      </c>
-    </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+        <v>780978974.67382681</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>14</v>
       </c>
@@ -3771,52 +3771,52 @@
       <c r="M35" s="3">
         <v>0.28455945661532572</v>
       </c>
-      <c r="O35" s="3">
-        <f t="shared" si="2"/>
+      <c r="N35" s="3">
+        <f t="shared" si="11"/>
         <v>4771.3999999999996</v>
       </c>
-      <c r="P35" s="4">
-        <f t="shared" si="3"/>
+      <c r="O35" s="4">
+        <f t="shared" si="12"/>
         <v>0.33276464830093694</v>
       </c>
+      <c r="P35" s="3">
+        <f t="shared" si="13"/>
+        <v>47714000000</v>
+      </c>
       <c r="Q35" s="3">
-        <f t="shared" si="11"/>
-        <v>47714000000</v>
+        <f t="shared" si="14"/>
+        <v>5368965.9052548669</v>
       </c>
       <c r="R35" s="3">
-        <f t="shared" si="12"/>
-        <v>5368965.9052548669</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5981831346.3672352</v>
       </c>
       <c r="S35" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>6036710533.0311546</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4775874244.2647495</v>
       </c>
       <c r="T35" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>5648883514.7217474</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4860783424.5668888</v>
       </c>
       <c r="U35" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5435714797.3651228</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5475335319.8348083</v>
       </c>
       <c r="V35" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>4745290610.5235004</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5570797871.0520649</v>
       </c>
       <c r="W35" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4789844898.4746723</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>4877191028.3629618</v>
       </c>
       <c r="X35" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5707351203.4034662</v>
-      </c>
-      <c r="Y35" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>5883522158.7002001</v>
-      </c>
-    </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+        <v>5611136873.5751905</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -3856,52 +3856,52 @@
       <c r="M36" s="3">
         <v>0.22157690926038165</v>
       </c>
-      <c r="O36" s="3">
-        <f t="shared" si="2"/>
+      <c r="N36" s="3">
+        <f t="shared" si="11"/>
         <v>10676.71</v>
       </c>
-      <c r="P36" s="4">
-        <f t="shared" si="3"/>
+      <c r="O36" s="4">
+        <f t="shared" si="12"/>
         <v>0.11593732482008999</v>
       </c>
+      <c r="P36" s="3">
+        <f t="shared" si="13"/>
+        <v>106767099999.99998</v>
+      </c>
       <c r="Q36" s="3">
-        <f t="shared" si="11"/>
-        <v>106767099999.99998</v>
+        <f t="shared" si="14"/>
+        <v>4448629.166666666</v>
       </c>
       <c r="R36" s="3">
-        <f t="shared" si="12"/>
-        <v>4448629.166666666</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>12280026010.113106</v>
       </c>
       <c r="S36" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>12525626530.315369</v>
-      </c>
-      <c r="T36" s="3">
         <f t="shared" ca="1" si="10"/>
         <v>12065653622.910002</v>
       </c>
+      <c r="T36" s="3">
+        <f t="shared" ca="1" si="5"/>
+        <v>12747981982.842487</v>
+      </c>
       <c r="U36" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>11578442351.389048</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>10618286396.923828</v>
       </c>
       <c r="V36" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>10968339794.624613</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>12115980981.57164</v>
       </c>
       <c r="W36" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>11649981713.049654</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>11726135459.300816</v>
       </c>
       <c r="X36" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>11261734054.972071</v>
-      </c>
-      <c r="Y36" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>13165247069.416945</v>
-      </c>
-    </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+        <v>12921446197.761076</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>37</v>
       </c>
@@ -3941,52 +3941,52 @@
       <c r="M37" s="3">
         <v>1.1416145691764065E-2</v>
       </c>
-      <c r="O37" s="3">
-        <f t="shared" si="2"/>
+      <c r="N37" s="3">
+        <f t="shared" si="11"/>
         <v>295.25999999999993</v>
       </c>
-      <c r="P37" s="4">
-        <f t="shared" si="3"/>
+      <c r="O37" s="4">
+        <f t="shared" si="12"/>
         <v>1.6783216783216787E-2</v>
       </c>
+      <c r="P37" s="3">
+        <f t="shared" si="13"/>
+        <v>2952599999.9999995</v>
+      </c>
       <c r="Q37" s="3">
-        <f t="shared" si="11"/>
-        <v>2952599999.9999995</v>
+        <f t="shared" si="14"/>
+        <v>3034532.3741007191</v>
       </c>
       <c r="R37" s="3">
-        <f t="shared" si="12"/>
-        <v>3034532.3741007191</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>359974983.72914082</v>
       </c>
       <c r="S37" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>373558945.37929708</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>346381924.82992411</v>
       </c>
       <c r="T37" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>305070319.11626339</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>307259781.34068954</v>
       </c>
       <c r="U37" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>355774483.65764052</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>316232343.98683757</v>
       </c>
       <c r="V37" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>351727811.16903365</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>328618935.29064113</v>
       </c>
       <c r="W37" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>341505952.36086237</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>298595769.52347195</v>
       </c>
       <c r="X37" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>292174355.12511772</v>
-      </c>
-      <c r="Y37" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>370821675.87966323</v>
-      </c>
-    </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+        <v>303399552.99245173</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>35</v>
       </c>
@@ -4026,55 +4026,52 @@
       <c r="M38" s="3">
         <v>-0.10846158718094877</v>
       </c>
-      <c r="N38" t="s">
-        <v>116</v>
-      </c>
-      <c r="O38" s="3">
-        <f t="shared" si="2"/>
+      <c r="N38" s="3">
+        <f t="shared" si="11"/>
         <v>630.82000000000005</v>
       </c>
-      <c r="P38" s="4">
-        <f t="shared" si="3"/>
+      <c r="O38" s="4">
+        <f t="shared" si="12"/>
         <v>-5.7411535947164617E-2</v>
       </c>
+      <c r="P38" s="3">
+        <f t="shared" si="13"/>
+        <v>6308200000.000001</v>
+      </c>
       <c r="Q38" s="3">
-        <f t="shared" si="11"/>
-        <v>6308200000.000001</v>
+        <f t="shared" si="14"/>
+        <v>3781894.4844124704</v>
       </c>
       <c r="R38" s="3">
-        <f t="shared" si="12"/>
-        <v>3781894.4844124704</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>776338406.51647556</v>
       </c>
       <c r="S38" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>754571909.13750899</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>651779647.44605207</v>
       </c>
       <c r="T38" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>719673360.72168255</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>732468269.46902776</v>
       </c>
       <c r="U38" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>746288425.49674535</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>723886286.30133593</v>
       </c>
       <c r="V38" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>737674596.51659942</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>743390499.6355679</v>
       </c>
       <c r="W38" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>626375328.39663589</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>679104698.31032348</v>
       </c>
       <c r="X38" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>658525768.05849552</v>
-      </c>
-      <c r="Y38" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>720233413.93535805</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+        <v>727435748.07471168</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>21</v>
       </c>
@@ -4114,52 +4111,52 @@
       <c r="M39" s="3">
         <v>0.12416576036893748</v>
       </c>
-      <c r="O39" s="3">
-        <f t="shared" si="2"/>
+      <c r="N39" s="3">
+        <f t="shared" si="11"/>
         <v>944.1099999999999</v>
       </c>
-      <c r="P39" s="4">
-        <f t="shared" si="3"/>
+      <c r="O39" s="4">
+        <f t="shared" si="12"/>
         <v>0.18119926455283425</v>
       </c>
+      <c r="P39" s="3">
+        <f t="shared" si="13"/>
+        <v>9441099999.9999981</v>
+      </c>
       <c r="Q39" s="3">
-        <f t="shared" si="11"/>
-        <v>9441099999.9999981</v>
+        <f t="shared" si="14"/>
+        <v>13682753.623188403</v>
       </c>
       <c r="R39" s="3">
-        <f t="shared" si="12"/>
-        <v>13682753.623188403</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>1042451049.26064</v>
       </c>
       <c r="S39" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>1031592184.164175</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>1117736390.8043652</v>
       </c>
       <c r="T39" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>944995312.22550869</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>1003163745.7680889</v>
       </c>
       <c r="U39" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>972138062.90928209</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>1124668914.8641751</v>
       </c>
       <c r="V39" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>1021488280.4729663</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>1091983962.2143662</v>
       </c>
       <c r="W39" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>999268342.78107095</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>1098506071.9305582</v>
       </c>
       <c r="X39" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>1036907600.6073493</v>
-      </c>
-      <c r="Y39" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>1131826110.2248442</v>
-      </c>
-    </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+        <v>1002474554.7705761</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -4199,52 +4196,52 @@
       <c r="M40" s="3">
         <v>6.4673316498821382E-2</v>
       </c>
-      <c r="O40" s="3">
-        <f t="shared" si="2"/>
+      <c r="N40" s="3">
+        <f t="shared" si="11"/>
         <v>5078</v>
       </c>
-      <c r="P40" s="4">
-        <f t="shared" si="3"/>
+      <c r="O40" s="4">
+        <f t="shared" si="12"/>
         <v>9.5978010083459145E-2</v>
       </c>
+      <c r="P40" s="3">
+        <f t="shared" si="13"/>
+        <v>50780000000</v>
+      </c>
       <c r="Q40" s="3">
-        <f t="shared" si="11"/>
-        <v>50780000000</v>
+        <f t="shared" si="14"/>
+        <v>2954558.6780706346</v>
       </c>
       <c r="R40" s="3">
-        <f t="shared" si="12"/>
-        <v>2954558.6780706346</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>6132588661.0502739</v>
       </c>
       <c r="S40" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5490126991.7973881</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5629295271.1401157</v>
       </c>
       <c r="T40" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>6011868736.1690559</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5451252121.2528524</v>
       </c>
       <c r="U40" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>5117501991.380229</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5438690790.3717451</v>
       </c>
       <c r="V40" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>5771671859.1700153</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4986812082.0907879</v>
       </c>
       <c r="W40" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>5263857197.7624979</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5687560215.4521608</v>
       </c>
       <c r="X40" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5411465059.3622494</v>
-      </c>
-      <c r="Y40" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>6145629486.2584772</v>
-      </c>
-    </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+        <v>5449897846.3046865</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>32</v>
       </c>
@@ -4284,52 +4281,52 @@
       <c r="M41" s="3">
         <v>0.17573897593280569</v>
       </c>
-      <c r="O41" s="3">
-        <f t="shared" si="2"/>
+      <c r="N41" s="3">
+        <f t="shared" si="11"/>
         <v>791.04000000000008</v>
       </c>
-      <c r="P41" s="4">
-        <f t="shared" si="3"/>
+      <c r="O41" s="4">
+        <f t="shared" si="12"/>
         <v>0.1209103840682788</v>
       </c>
+      <c r="P41" s="3">
+        <f t="shared" si="13"/>
+        <v>7910400000.000001</v>
+      </c>
       <c r="Q41" s="3">
-        <f t="shared" si="11"/>
-        <v>7910400000.000001</v>
+        <f t="shared" si="14"/>
+        <v>3472519.7541703251</v>
       </c>
       <c r="R41" s="3">
-        <f t="shared" si="12"/>
-        <v>3472519.7541703251</v>
-      </c>
-      <c r="S41" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>864338563.6856184</v>
       </c>
+      <c r="S41" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>902460948.07596421</v>
+      </c>
       <c r="T41" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>842864470.37283444</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>831854124.40942168</v>
       </c>
       <c r="U41" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>892510154.31427538</v>
-      </c>
-      <c r="V41" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>855872821.37180579</v>
       </c>
+      <c r="V41" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>940833428.31049764</v>
+      </c>
       <c r="W41" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>794097939.49142921</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>868792183.52145183</v>
       </c>
       <c r="X41" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>929005503.17145348</v>
-      </c>
-      <c r="Y41" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>821878555.1838516</v>
-      </c>
-    </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+        <v>885099982.5056864</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -4369,52 +4366,52 @@
       <c r="M42" s="3">
         <v>7.7620430171238966E-3</v>
       </c>
-      <c r="O42" s="3">
-        <f t="shared" si="2"/>
+      <c r="N42" s="3">
+        <f t="shared" si="11"/>
         <v>96.179999999999993</v>
       </c>
-      <c r="P42" s="4">
-        <f t="shared" si="3"/>
+      <c r="O42" s="4">
+        <f t="shared" si="12"/>
         <v>1.3437275618012105E-2</v>
       </c>
+      <c r="P42" s="3">
+        <f t="shared" si="13"/>
+        <v>961799999.99999988</v>
+      </c>
       <c r="Q42" s="3">
-        <f t="shared" si="11"/>
-        <v>961799999.99999988</v>
+        <f t="shared" si="14"/>
+        <v>2368965.5172413792</v>
       </c>
       <c r="R42" s="3">
-        <f t="shared" si="12"/>
-        <v>2368965.5172413792</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>100667203.70825258</v>
       </c>
       <c r="S42" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>119473164.84056351</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>104551496.72297381</v>
       </c>
       <c r="T42" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>99375680.053519666</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>105356726.70063324</v>
       </c>
       <c r="U42" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>100088890.36560157</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>101960534.40037772</v>
       </c>
       <c r="V42" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>100909394.87047693</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>99700233.41488716</v>
       </c>
       <c r="W42" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>108096042.54456188</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>108771269.78037304</v>
       </c>
       <c r="X42" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>115046535.34462534</v>
-      </c>
-      <c r="Y42" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>104322068.52142859</v>
-      </c>
-    </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+        <v>102125814.44729324</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -4454,52 +4451,52 @@
       <c r="M43" s="3">
         <v>0.24893607043624044</v>
       </c>
-      <c r="O43" s="3">
-        <f t="shared" si="2"/>
+      <c r="N43" s="3">
+        <f t="shared" si="11"/>
         <v>9803.34</v>
       </c>
-      <c r="P43" s="4">
-        <f t="shared" si="3"/>
+      <c r="O43" s="4">
+        <f t="shared" si="12"/>
         <v>4.1520295736902878E-2</v>
       </c>
+      <c r="P43" s="3">
+        <f t="shared" si="13"/>
+        <v>98033400000</v>
+      </c>
       <c r="Q43" s="3">
-        <f t="shared" si="11"/>
-        <v>98033400000</v>
+        <f t="shared" si="14"/>
+        <v>14263553.033609778</v>
       </c>
       <c r="R43" s="3">
-        <f t="shared" si="12"/>
-        <v>14263553.033609778</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>12177542688.792784</v>
       </c>
       <c r="S43" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>11501012539.415407</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>10867643856.51413</v>
       </c>
       <c r="T43" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>11395199383.529379</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>10523922404.561428</v>
       </c>
       <c r="U43" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>10201761514.625875</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>10392532598.342682</v>
       </c>
       <c r="V43" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>11785346245.543249</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>11124876576.761993</v>
       </c>
       <c r="W43" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>10803966675.509243</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>10340508258.674248</v>
       </c>
       <c r="X43" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>11193333682.070063</v>
-      </c>
-      <c r="Y43" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>10073592677.074518</v>
-      </c>
-    </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+        <v>10409379099.643667</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -4539,55 +4536,52 @@
       <c r="M44" s="3">
         <v>-0.10325801366263794</v>
       </c>
-      <c r="N44" t="s">
-        <v>115</v>
-      </c>
-      <c r="O44" s="3">
-        <f t="shared" si="2"/>
+      <c r="N44" s="3">
+        <f t="shared" si="11"/>
         <v>328.12</v>
       </c>
-      <c r="P44" s="4">
-        <f t="shared" si="3"/>
+      <c r="O44" s="4">
+        <f t="shared" si="12"/>
         <v>-0.10597276526897667</v>
       </c>
+      <c r="P44" s="3">
+        <f t="shared" si="13"/>
+        <v>3281200000</v>
+      </c>
       <c r="Q44" s="3">
-        <f t="shared" si="11"/>
-        <v>3281200000</v>
+        <f t="shared" si="14"/>
+        <v>5191772.1518987343</v>
       </c>
       <c r="R44" s="3">
-        <f t="shared" si="12"/>
-        <v>5191772.1518987343</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>362297866.01497835</v>
       </c>
       <c r="S44" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>384941482.64091456</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>360211009.54313195</v>
       </c>
       <c r="T44" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>363742490.02884895</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>380992182.52144402</v>
       </c>
       <c r="U44" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>348643789.66584975</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>355012376.30020845</v>
       </c>
       <c r="V44" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>329910491.1072644</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>368771818.25453991</v>
       </c>
       <c r="W44" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>361611200.42435467</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>381779466.71664834</v>
       </c>
       <c r="X44" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>342531110.32521719</v>
-      </c>
-      <c r="Y44" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>382120807.10199273</v>
-      </c>
-    </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+        <v>337165418.03117007</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>23</v>
       </c>
@@ -4627,52 +4621,52 @@
       <c r="M45" s="3">
         <v>0.22363983441270735</v>
       </c>
-      <c r="O45" s="3">
-        <f t="shared" si="2"/>
+      <c r="N45" s="3">
+        <f t="shared" si="11"/>
         <v>3560.66</v>
       </c>
-      <c r="P45" s="4">
-        <f t="shared" si="3"/>
+      <c r="O45" s="4">
+        <f t="shared" si="12"/>
         <v>0.12470193759003328</v>
       </c>
+      <c r="P45" s="3">
+        <f t="shared" si="13"/>
+        <v>35606600000</v>
+      </c>
       <c r="Q45" s="3">
-        <f t="shared" si="11"/>
-        <v>35606600000</v>
+        <f t="shared" si="14"/>
+        <v>34502519.379844964</v>
       </c>
       <c r="R45" s="3">
-        <f t="shared" si="12"/>
-        <v>34502519.379844964</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4218223341.7939062</v>
       </c>
       <c r="S45" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>4463945089.8595715</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4215482578.5993919</v>
       </c>
       <c r="T45" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>3640644045.1540198</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>4212420888.8894463</v>
       </c>
       <c r="U45" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>3861385814.8153257</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>4202714199.2301049</v>
       </c>
       <c r="V45" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>3580089873.4182377</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4079506241.2210088</v>
       </c>
       <c r="W45" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4157211122.0061707</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>3871921931.7963824</v>
       </c>
       <c r="X45" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>3523448957.9347081</v>
-      </c>
-      <c r="Y45" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>3902739379.4688635</v>
-      </c>
-    </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4268621196.2940698</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>11</v>
       </c>
@@ -4712,52 +4706,52 @@
       <c r="M46" s="3">
         <v>0.27445838403334316</v>
       </c>
-      <c r="O46" s="3">
-        <f t="shared" si="2"/>
+      <c r="N46" s="3">
+        <f t="shared" si="11"/>
         <v>3123.42</v>
       </c>
-      <c r="P46" s="4">
-        <f t="shared" si="3"/>
+      <c r="O46" s="4">
+        <f t="shared" si="12"/>
         <v>0.20083615634179042</v>
       </c>
+      <c r="P46" s="3">
+        <f t="shared" si="13"/>
+        <v>31234200000</v>
+      </c>
       <c r="Q46" s="3">
-        <f t="shared" si="11"/>
-        <v>31234200000</v>
+        <f t="shared" si="14"/>
+        <v>2402630.769230769</v>
       </c>
       <c r="R46" s="3">
-        <f t="shared" si="12"/>
-        <v>2402630.769230769</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>3879859352.5297666</v>
       </c>
       <c r="S46" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>3592462363.4534874</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>3563365410.6485486</v>
       </c>
       <c r="T46" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>3025498933.5695224</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>3421431766.5969214</v>
       </c>
       <c r="U46" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>3660931990.2587066</v>
-      </c>
-      <c r="V46" s="3">
         <f t="shared" ca="1" si="6"/>
         <v>3072192979.2415109</v>
       </c>
+      <c r="V46" s="3">
+        <f t="shared" ca="1" si="7"/>
+        <v>3067331349.6345034</v>
+      </c>
       <c r="W46" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>3646716160.1210213</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>3260601367.2192793</v>
       </c>
       <c r="X46" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>3328530562.3696809</v>
-      </c>
-      <c r="Y46" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>3887090897.9294147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+        <v>3423492900.9286585</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -4797,52 +4791,52 @@
       <c r="M47" s="3">
         <v>0.18912281878069631</v>
       </c>
-      <c r="O47" s="3">
-        <f t="shared" si="2"/>
+      <c r="N47" s="3">
+        <f t="shared" si="11"/>
         <v>4619.6899999999996</v>
       </c>
-      <c r="P47" s="4">
-        <f t="shared" si="3"/>
+      <c r="O47" s="4">
+        <f t="shared" si="12"/>
         <v>0.12780744018849688</v>
       </c>
+      <c r="P47" s="3">
+        <f t="shared" si="13"/>
+        <v>46196899999.999992</v>
+      </c>
       <c r="Q47" s="3">
-        <f t="shared" si="11"/>
-        <v>46196899999.999992</v>
+        <f t="shared" si="14"/>
+        <v>3655396.4234847282</v>
       </c>
       <c r="R47" s="3">
-        <f t="shared" si="12"/>
-        <v>3655396.4234847282</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>4888352337.9361868</v>
       </c>
       <c r="S47" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>4835218073.3934021</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>4972066647.8915863</v>
       </c>
       <c r="T47" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>4624021982.539175</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>5161673166.0124903</v>
       </c>
       <c r="U47" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>4908649971.6001129</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>5402219265.0546408</v>
       </c>
       <c r="V47" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>4644898807.3367004</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>5091221646.0087366</v>
       </c>
       <c r="W47" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4738364700.2457542</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>5174234945.1993275</v>
       </c>
       <c r="X47" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>4671882037.8984222</v>
-      </c>
-      <c r="Y47" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>5590961615.0794449</v>
-      </c>
-    </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+        <v>4852532722.5217819</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>2</v>
       </c>
@@ -4882,52 +4876,52 @@
       <c r="M48" s="3">
         <v>0.45887728459530025</v>
       </c>
-      <c r="O48" s="3">
-        <f t="shared" si="2"/>
+      <c r="N48" s="3">
+        <f t="shared" si="11"/>
         <v>217687</v>
       </c>
-      <c r="P48" s="4">
-        <f t="shared" si="3"/>
+      <c r="O48" s="4">
+        <f t="shared" si="12"/>
         <v>0.18437824329235622</v>
       </c>
+      <c r="P48" s="3">
+        <f t="shared" si="13"/>
+        <v>2176870000000</v>
+      </c>
       <c r="Q48" s="3">
-        <f t="shared" si="11"/>
-        <v>2176870000000</v>
+        <f t="shared" si="14"/>
+        <v>3418274.4926848956</v>
       </c>
       <c r="R48" s="3">
-        <f t="shared" si="12"/>
-        <v>3418274.4926848956</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>255384482907.6337</v>
       </c>
       <c r="S48" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>275414638429.80109</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>248349029636.6965</v>
       </c>
       <c r="T48" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>217891129775.59219</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>236072383734.95468</v>
       </c>
       <c r="U48" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>245610661865.65994</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>228391177387.91342</v>
       </c>
       <c r="V48" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>221253953094.54114</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>235155686862.05338</v>
       </c>
       <c r="W48" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>223279137020.53549</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>227247866065.35886</v>
       </c>
       <c r="X48" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>231982196608.38718</v>
-      </c>
-      <c r="Y48" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>228658912344.24808</v>
-      </c>
-    </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+        <v>226173489383.9845</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>5</v>
       </c>
@@ -4967,52 +4961,52 @@
       <c r="M49" s="3">
         <v>0.15538256309047385</v>
       </c>
-      <c r="O49" s="3">
-        <f t="shared" si="2"/>
+      <c r="N49" s="3">
+        <f t="shared" si="11"/>
         <v>49600.800000000003</v>
       </c>
-      <c r="P49" s="4">
-        <f t="shared" si="3"/>
+      <c r="O49" s="4">
+        <f t="shared" si="12"/>
         <v>7.8947417287655308E-2</v>
       </c>
+      <c r="P49" s="3">
+        <f t="shared" si="13"/>
+        <v>496008000000</v>
+      </c>
       <c r="Q49" s="3">
-        <f t="shared" si="11"/>
-        <v>496008000000</v>
+        <f t="shared" si="14"/>
+        <v>3351405.4054054054</v>
       </c>
       <c r="R49" s="3">
-        <f t="shared" si="12"/>
-        <v>3351405.4054054054</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>58760806235.824585</v>
       </c>
       <c r="S49" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>53626366855.995247</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>57654942660.620155</v>
       </c>
       <c r="T49" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>53918048228.913292</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>57049977398.829361</v>
       </c>
       <c r="U49" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>54333311808.40892</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>54208111452.176826</v>
       </c>
       <c r="V49" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>52039786994.089752</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>55745999033.523659</v>
       </c>
       <c r="W49" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>49792542826.059967</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>50161176742.463692</v>
       </c>
       <c r="X49" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>57172954136.571526</v>
-      </c>
-      <c r="Y49" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>57763920909.74192</v>
-      </c>
-    </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+        <v>51534478458.691322</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>3</v>
       </c>
@@ -5052,52 +5046,52 @@
       <c r="M50" s="3">
         <v>0.15858091605910354</v>
       </c>
-      <c r="O50" s="3">
-        <f t="shared" si="2"/>
+      <c r="N50" s="3">
+        <f t="shared" si="11"/>
         <v>79862.399999999994</v>
       </c>
-      <c r="P50" s="4">
-        <f t="shared" si="3"/>
+      <c r="O50" s="4">
+        <f t="shared" si="12"/>
         <v>0.14124420147573385</v>
       </c>
+      <c r="P50" s="3">
+        <f t="shared" si="13"/>
+        <v>798624000000</v>
+      </c>
       <c r="Q50" s="3">
-        <f t="shared" si="11"/>
-        <v>798624000000</v>
+        <f t="shared" si="14"/>
+        <v>3412923.076923077</v>
       </c>
       <c r="R50" s="3">
-        <f t="shared" si="12"/>
-        <v>3412923.076923077</v>
-      </c>
-      <c r="S50" s="3">
         <f t="shared" ca="1" si="4"/>
         <v>99203718858.006027</v>
       </c>
+      <c r="S50" s="3">
+        <f t="shared" ca="1" si="10"/>
+        <v>78218207210.684082</v>
+      </c>
       <c r="T50" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>80796829426.420914</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>88357054075.288208</v>
       </c>
       <c r="U50" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>82233297852.248428</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>89026259206.284851</v>
       </c>
       <c r="V50" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>81171001041.024414</v>
-      </c>
-      <c r="W50" s="3">
         <f t="shared" ca="1" si="7"/>
         <v>81913976270.465469</v>
       </c>
+      <c r="W50" s="3">
+        <f t="shared" ca="1" si="8"/>
+        <v>86843725063.863281</v>
+      </c>
       <c r="X50" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>85975287813.224655</v>
-      </c>
-      <c r="Y50" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>92094043763.738998</v>
-      </c>
-    </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+        <v>94829510410.186707</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>45</v>
       </c>
@@ -5137,52 +5131,52 @@
       <c r="M51" s="3">
         <v>5.012325390304026E-2</v>
       </c>
-      <c r="O51" s="3">
-        <f t="shared" si="2"/>
+      <c r="N51" s="3">
+        <f t="shared" si="11"/>
         <v>226.92999999999998</v>
       </c>
-      <c r="P51" s="4">
-        <f t="shared" si="3"/>
+      <c r="O51" s="4">
+        <f t="shared" si="12"/>
         <v>3.8758048119281602E-2</v>
       </c>
+      <c r="P51" s="3">
+        <f t="shared" si="13"/>
+        <v>2269300000</v>
+      </c>
       <c r="Q51" s="3">
-        <f t="shared" si="11"/>
-        <v>2269300000</v>
+        <f t="shared" si="14"/>
+        <v>4141058.3941605841</v>
       </c>
       <c r="R51" s="3">
-        <f t="shared" si="12"/>
-        <v>4141058.3941605841</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>255787801.33819014</v>
       </c>
       <c r="S51" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>247957562.52171493</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>224700401.46710166</v>
       </c>
       <c r="T51" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>241797171.14394632</v>
+        <f t="shared" ca="1" si="5"/>
+        <v>273440031.07914507</v>
       </c>
       <c r="U51" s="3">
-        <f t="shared" ca="1" si="5"/>
-        <v>238638572.57816297</v>
+        <f t="shared" ca="1" si="6"/>
+        <v>265369671.51883563</v>
       </c>
       <c r="V51" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>223208134.92238513</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>272378231.23008811</v>
       </c>
       <c r="W51" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>240188076.63016862</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>271444273.921354</v>
       </c>
       <c r="X51" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>264041248.26895344</v>
-      </c>
-      <c r="Y51" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>266868275.70952302</v>
-      </c>
-    </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+        <v>259095413.31021652</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -5222,85 +5216,85 @@
       <c r="M52" s="3">
         <v>0.15966778878049978</v>
       </c>
-      <c r="O52" s="3">
-        <f t="shared" si="2"/>
+      <c r="N52" s="3">
+        <f t="shared" si="11"/>
         <v>4791</v>
       </c>
-      <c r="P52" s="4">
-        <f>F52/E52</f>
+      <c r="O52" s="4">
+        <f t="shared" si="12"/>
         <v>0.1194309660344067</v>
       </c>
+      <c r="P52" s="3">
+        <f t="shared" si="13"/>
+        <v>47910000000</v>
+      </c>
       <c r="Q52" s="3">
-        <f t="shared" si="11"/>
-        <v>47910000000</v>
+        <f t="shared" si="14"/>
+        <v>4839393.9393939395</v>
       </c>
       <c r="R52" s="3">
-        <f t="shared" si="12"/>
-        <v>4839393.9393939395</v>
+        <f t="shared" ca="1" si="4"/>
+        <v>5290043508.7095013</v>
       </c>
       <c r="S52" s="3">
-        <f t="shared" ca="1" si="4"/>
-        <v>5510461988.2390642</v>
+        <f t="shared" ca="1" si="10"/>
+        <v>5104879244.4835272</v>
       </c>
       <c r="T52" s="3">
-        <f t="shared" ca="1" si="10"/>
-        <v>5517394738.9872475</v>
-      </c>
-      <c r="U52" s="3">
         <f t="shared" ca="1" si="5"/>
         <v>5300600108.1197882</v>
       </c>
+      <c r="U52" s="3">
+        <f t="shared" ca="1" si="6"/>
+        <v>4869503871.503335</v>
+      </c>
       <c r="V52" s="3">
-        <f t="shared" ca="1" si="6"/>
-        <v>4974224384.8689985</v>
+        <f t="shared" ca="1" si="7"/>
+        <v>4704965869.4952669</v>
       </c>
       <c r="W52" s="3">
-        <f t="shared" ca="1" si="7"/>
-        <v>4809520666.5951614</v>
+        <f t="shared" ca="1" si="8"/>
+        <v>4740931163.7351465</v>
       </c>
       <c r="X52" s="3">
-        <f t="shared" ca="1" si="8"/>
-        <v>5730795912.2073202</v>
-      </c>
-      <c r="Y52" s="3">
         <f t="shared" ca="1" si="9"/>
-        <v>5798288867.4014101</v>
-      </c>
-    </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+        <v>5962391382.5165443</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C53" s="2"/>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C54" s="2"/>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C55" s="2"/>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C56" s="2"/>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C57" s="2"/>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C58" s="2"/>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C59" s="2"/>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C60" s="2"/>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C61" s="1"/>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C62" s="1"/>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C63" s="1"/>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:24" x14ac:dyDescent="0.35">
       <c r="C64" s="1"/>
       <c r="D64"/>
     </row>
@@ -5321,10 +5315,14 @@
       <c r="D69"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C69" xr:uid="{B9A97D36-5AA9-4706-BACB-2B8DE34E5D88}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:C69">
     <sortCondition ref="B1:B69"/>
   </sortState>
+  <conditionalFormatting sqref="M1:M1048576">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>